--- a/tools/excel/canada/itsp.10.171.xlsx
+++ b/tools/excel/canada/itsp.10.171.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tarkadia\projects\intuitem\ciso-assistant-community\tools\excel\canada\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tarkadia\projects\intuitem\ciso-assistant-community\tools\excel\canada\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99F72A2-87C7-419F-9D9D-6ECD7F154F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9F151FFB0F9ECD63A45548C2E0A0FD9285D4CB66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="-15870" windowWidth="25440" windowHeight="15990" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="816" yWindow="1044" windowWidth="21084" windowHeight="11868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -149,7 +149,7 @@
 Le présent document n’intègre pas tous les ensembles de contrôles et d’activités associés à la protection de la vie privée décrits dans l’ITSP.10.033. Il présente plutôt un sous-ensemble des contrôles associés à la protection de la vie privée qui sont communs avec les contrôles de confidentialité.</t>
   </si>
   <si>
-    <t>[1] Système utilisé ou exploité par un ministère ou un organisme du &lt;abbr title="gouvernement du Canada"&gt;GC&lt;/abbr&gt;, par une entrepreneure ou un entrepreneur, ou par une autre organisation au nom d’un ministère ou d’un organisme. Le terme « système », tel qu’il est utilisé dans cette publication, comprend les personnes, les processus et les technologies qui interviennent dans la gestion, le traitement, le stockage ou la transmission d’information désignée. Les systèmes peuvent inclure les technologies opérationnelles (TO), les technologies de l’information (TI), les dispositifs de l’Internet des objets &lt;abbr title="Internet des objets&amp;#10;Réseau formé par les dispositifs Web utilisés couramment, qui peuvent se connecter les uns aux autres et qui peuvent se transmettre de l&amp;#x27;information."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; (IdO), les dispositifs de l’Internet industriel des objets (IIdO), les systèmes spécialisés, les cybersystèmes physiques, les systèmes embarqués et les capteurs.</t>
+    <t>[1] Système utilisé ou exploité par un ministère ou un organisme du &lt;abbr title="gouvernement du Canada"&gt;GC&lt;/abbr&gt;, par une entrepreneure ou un entrepreneur, ou par une autre organisation au nom d’un ministère ou d’un organisme. Le terme « système », tel qu’il est utilisé dans cette publication, comprend les personnes, les processus et les technologies qui interviennent dans la gestion, le traitement, le stockage ou la transmission d’information désignée. Les systèmes peuvent inclure les technologies opérationnelles (TO), les technologies de l’information (TI), les dispositifs de l’Internet des objets &lt;abbr title="Internet des objets&amp;#10;Réseau formé par les dispositifs Web utilisés couramment, qui peuvent se connecter les uns aux autres et qui peuvent se transmettre de l&amp;#x27;information."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; (IdO), les dispositifs de l’Internet industriel des objets (IIdO), les systèmes spécialisés, les cybersystèmes physiques, les systèmes embarqués et les capteurs.</t>
   </si>
   <si>
     <t>This publication is a Canadian version of [NIST SP 800-171 Protecting Controlled Unclassified Information in Nonfederal Systems and Organizations](https://csrc.nist.gov/pubs/sp/800/171/r3/final). There are no substantial technical changes between this publication and NIST SP 800-171. The primary modifications arise from differences in laws, policies, directives, standards and guidelines. In other words, the changes reflect the distinct Canadian regulatory and compliance landscape; there are no changes to the underlying technical context.
@@ -172,7 +172,7 @@
   <si>
     <t>La présente publication présente aux ministères et aux organismes du &lt;abbr title="gouvernement du Canada"&gt;GC&lt;/abbr&gt; des exigences de sécurité recommandées visant à protéger la confidentialité de l’information désignée lorsque l’information se trouve dans des systèmes et des organisations ne relevant pas du &lt;abbr title="gouvernement du Canada"&gt;GC&lt;/abbr&gt; et lorsqu’il n’existe pas d’autres exigences de protection particulières imposées par des lois, des réglementations ou des politiques s’appliquant à l’échelle gouvernementale pour la catégorie d’information désignée.
 Les exigences de sécurité dans la présente publication ne s’appliquent qu’aux composants[2] des systèmes ne relevant pas du &lt;abbr title="gouvernement du Canada"&gt;GC&lt;/abbr&gt; qui gèrent, traitent, stockent ou transmettent de l’information désignée ou qui protègent de tels composants. Ces exigences serviront aux ministères et aux organismes du &lt;abbr title="gouvernement du Canada"&gt;GC&lt;/abbr&gt; dans le cadre de contrats ou d’autres ententes établies avec des organisations ne relevant pas du &lt;abbr title="gouvernement du Canada"&gt;GC&lt;/abbr&gt;.
-Il est important d’établir adéquatement la portée des exigences imposées aux organisations ne relevant pas du &lt;abbr title="gouvernement du Canada"&gt;GC&lt;/abbr&gt; lors des décisions d’investissement en matière de protection et de la gestion des risques liés à la sécurité. Dans le cadre des activités de conception associées aux composants système pour la gestion, le traitement, le stockage ou la transmission d’information désignée, les organisations ne relevant pas du &lt;abbr title="gouvernement du Canada"&gt;GC&lt;/abbr&gt; peuvent limiter la portée des exigences de sécurité qui s’appliquent grâce à l’isolation des composants système dans un domaine de sécurité séparé. L’isolation est possible grâce à des concepts architecturaux et de conception (par exemple, la mise en œuvre de sous-réseaux dotés de pare-feu ou d’autres dispositifs de protection de périmètre &lt;abbr title="Périmètre&amp;#10;Frontière entre deux zones de sécurité réseau à travers laquelle le trafic est acheminé."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; et l’utilisation de mécanismes de contrôle de flux d’information). Les domaines de sécurité peuvent utiliser une séparation physique, une séparation logique ou une combinaison des deux. Une telle approche peut fournir une sécurité adéquate pour l’information désignée, tout en évitant d’augmenter la posture de sécurité d’une organisation ne relevant pas du &lt;abbr title="gouvernement du Canada"&gt;GC&lt;/abbr&gt; au-delà du niveau requis afin de protéger ses missions, ses opérations et ses actifs.</t>
+Il est important d’établir adéquatement la portée des exigences imposées aux organisations ne relevant pas du &lt;abbr title="gouvernement du Canada"&gt;GC&lt;/abbr&gt; lors des décisions d’investissement en matière de protection et de la gestion des risques liés à la sécurité. Dans le cadre des activités de conception associées aux composants système pour la gestion, le traitement, le stockage ou la transmission d’information désignée, les organisations ne relevant pas du &lt;abbr title="gouvernement du Canada"&gt;GC&lt;/abbr&gt; peuvent limiter la portée des exigences de sécurité qui s’appliquent grâce à l’isolation des composants système dans un domaine de sécurité séparé. L’isolation est possible grâce à des concepts architecturaux et de conception (par exemple, la mise en œuvre de sous-réseaux dotés de pare-feu ou d’autres dispositifs de protection de périmètre &lt;abbr title="Périmètre&amp;#10;Frontière entre deux zones de sécurité réseau à travers laquelle le trafic est acheminé."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; et l’utilisation de mécanismes de contrôle de flux d’information). Les domaines de sécurité peuvent utiliser une séparation physique, une séparation logique ou une combinaison des deux. Une telle approche peut fournir une sécurité adéquate pour l’information désignée, tout en évitant d’augmenter la posture de sécurité d’une organisation ne relevant pas du &lt;abbr title="gouvernement du Canada"&gt;GC&lt;/abbr&gt; au-delà du niveau requis afin de protéger ses missions, ses opérations et ses actifs.</t>
   </si>
   <si>
     <t>[2] Les composants incluent les postes de travail, les serveurs, les ordinateurs blocs-notes, les téléphones intelligents, les tablettes, les dispositifs d’entrée-sortie, les composants réseau, les systèmes d’exploitation, les machines virtuelles, les systèmes de gestion de base de données et les applications.</t>
@@ -287,7 +287,7 @@
     <t>Méthodologie d’élaboration des exigences de sécurité</t>
   </si>
   <si>
-    <t>En commençant par les contrôles de l’ITSP.10.033 dans le profil confidentialité moyenne, intégrité &lt;abbr title="Intégrité&amp;#10;Aptitude à protéger l&amp;#x27;information contre les modifications ou les suppressions non intentionnelles ou inopportunes. L&amp;#x27;intégrité permet de savoir si l&amp;#x27;information est conforme à ce qu&amp;#x27;elle est censée être. L&amp;#x27;intégrité s&amp;#x27;applique également aux processus opérationnels, à la logique des applications logicielles, au matériel ainsi qu&amp;#x27;au personnel."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; moyenne, disponibilité &lt;abbr title="Disponibilité&amp;#10;Caractéristique de l&amp;#x27;information ou des systèmes qui sont accessibles aux personnes autorisées au moment où celles-ci en ont besoin. La disponibilité est un attribut des actifs informationnels, logiciels, et matériels (l&amp;#x27;infrastructure et ses composantes). Il est également entendu que la disponibilité comprend la protection des actifs contre les accès non autorisés ou les compromissions."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; moyenne (impact moyen) de l’ITSP.10.033-01, les contrôles ont été adaptés afin d’éliminer les contrôles ou les parties de contrôles qui :
+    <t>En commençant par les contrôles de l’ITSP.10.033 dans le profil confidentialité moyenne, intégrité &lt;abbr title="Intégrité&amp;#10;Aptitude à protéger l&amp;#x27;information contre les modifications ou les suppressions non intentionnelles ou inopportunes. L&amp;#x27;intégrité permet de savoir si l&amp;#x27;information est conforme à ce qu&amp;#x27;elle est censée être. L&amp;#x27;intégrité s&amp;#x27;applique également aux processus opérationnels, à la logique des applications logicielles, au matériel ainsi qu&amp;#x27;au personnel."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; moyenne, disponibilité &lt;abbr title="Disponibilité&amp;#10;Caractéristique de l&amp;#x27;information ou des systèmes qui sont accessibles aux personnes autorisées au moment où celles-ci en ont besoin. La disponibilité est un attribut des actifs informationnels, logiciels, et matériels (l&amp;#x27;infrastructure et ses composantes). Il est également entendu que la disponibilité comprend la protection des actifs contre les accès non autorisés ou les compromissions."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; moyenne (impact moyen) de l’ITSP.10.033-01, les contrôles ont été adaptés afin d’éliminer les contrôles ou les parties de contrôles qui :
 • relèvent principalement du &lt;abbr title="gouvernement du Canada"&gt;GC&lt;/abbr&gt; ;
 • ne sont pas directement liés à la protection de la confidentialité de l’information désignée;
 • sont déjà abordés adéquatement par d’autres contrôles;
@@ -328,7 +328,7 @@
 • not directly related to protecting the confidentiality of specified information
 • adequately addressed by other related controls
 • not applicable
-ITSP.10.171 security requirements represent a subset of the controls that are necessary to protect the confidentiality of specified information. The security requirements are organized into 17 families, as illustrated in Table 1. Each family contains the requirements related to its general security topic. Certain families from ITSP.10.033 are not included because they do not directly contribute to confidentiality. For example, the Personal information handling and transparency (PT) family is not included because it is about handling personal information (PI), not about the confidentiality of the &lt;abbr title="personal information"&gt;PI&lt;/abbr&gt;. The Program management (PM) family is not included because it is not related to confidentiality. Finally, the Contingency planning (CP) family is not included because it addresses availability &lt;abbr title="Availability&amp;#10;The ability for the right people to access the right information or systems when needed. Availability is applied to information assets, software, and hardware (infrastructure and its components). Implied in its definition is that availability includes the protection of assets from unauthorized access and compromise."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt;.
+ITSP.10.171 security requirements represent a subset of the controls that are necessary to protect the confidentiality of specified information. The security requirements are organized into 17 families, as illustrated in Table 1. Each family contains the requirements related to its general security topic. Certain families from ITSP.10.033 are not included because they do not directly contribute to confidentiality. For example, the Personal information handling and transparency (PT) family is not included because it is about handling personal information (PI), not about the confidentiality of the &lt;abbr title="personal information"&gt;PI&lt;/abbr&gt;. The Program management (PM) family is not included because it is not related to confidentiality. Finally, the Contingency planning (CP) family is not included because it addresses availability &lt;abbr title="Availability&amp;#10;The ability for the right people to access the right information or systems when needed. Availability is applied to information assets, software, and hardware (infrastructure and its components). Implied in its definition is that availability includes the protection of assets from unauthorized access and compromise."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt;.
 The following are the security requirements families:
 • Access control
 • Awareness and training
@@ -353,7 +353,7 @@
 Because this is the first iteration of the Canadian publication, controls that were withdrawn in NIST SP 800-171 Revision 3 have been labelled as “not allocated” to keep the same numbering for interoperability purposes.
 The structure and content of a typical security requirement is provided in the example below.
 The term “organization” is used in many security requirements, and its meaning depends on context. For example, in a security requirement with an &lt;abbr title="organization-defined parameter"&gt;ODP&lt;/abbr&gt;, an organization can refer to either the &lt;abbr title="Government of Canada"&gt;GC&lt;/abbr&gt; department or agency or to the non-&lt;abbr title="Government of Canada"&gt;GC&lt;/abbr&gt; organization establishing the parameter values for the requirement.
-Annex A describes the security control &lt;abbr title="Security control&amp;#10;A management, operational, or technical high-level security requirement needed for an information system to protect the confidentiality, integrity, and availability of its IT assets. Security controls can be applied by using a variety of security solutions that can include security products, security policies, security practices, and security procedures."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; tailoring criteria used to develop the security requirements and the results of the tailoring process. It provides a list of controls and activities from ITSP.10.033 that support the requirements and the controls and activities that have been eliminated from the Medium impact profile in accordance with the tailoring criteria.</t>
+Annex A describes the security control &lt;abbr title="Security control&amp;#10;A management, operational, or technical high-level security requirement needed for an information system to protect the confidentiality, integrity, and availability of its IT assets. Security controls can be applied by using a variety of security solutions that can include security products, security policies, security practices, and security procedures."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; tailoring criteria used to develop the security requirements and the results of the tailoring process. It provides a list of controls and activities from ITSP.10.033 that support the requirements and the controls and activities that have been eliminated from the Medium impact profile in accordance with the tailoring criteria.</t>
   </si>
   <si>
     <t>3</t>
@@ -387,7 +387,7 @@
     <t>Access control</t>
   </si>
   <si>
-    <t>The controls in the Access control &lt;abbr title="Access control&amp;#10;Certifying that only authorized access is given to assets (both physical and electronic). For physical assets, access control may be required for a facility or restricted area (e.g. screening visitors and materials at entry points, escorting visitors). For IT assets, access controls may be required for networks, systems, and information (e.g. restricting users on specific systems, limiting account privileges)."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; family support the ability to permit or deny user access to resources within the system.</t>
+    <t>The controls in the Access control &lt;abbr title="Access control&amp;#10;Certifying that only authorized access is given to assets (both physical and electronic). For physical assets, access control may be required for a facility or restricted area (e.g. screening visitors and materials at entry points, escorting visitors). For IT assets, access controls may be required for networks, systems, and information (e.g. restricting users on specific systems, limiting account privileges)."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; family support the ability to permit or deny user access to resources within the system.</t>
   </si>
   <si>
     <t>03.01.01</t>
@@ -603,7 +603,7 @@
 La fermeture de session en cas d’inactivité peut être basée sur des comportements ou sur des stratégies, et nécessite que les utilisatrices et utilisateurs effectuent une opération physique afin de fermer leur session s’ils prévoient d’être inactifs sur le système pendant une période dépassant la période définie. L’application automatique de la fermeture de session en cas d’inactivité est abordée dans l’exigence **Verrouillage d'appareil 03.01.10**.</t>
   </si>
   <si>
-    <t>This requirement focuses on account management for systems and applications. The definition and enforcement of access authorizations other than those determined by account type (e.g., privileged access or non-privileged access) are addressed in **Access enforcement 03.01.02**. System account types include individual, group, temporary, system, guest, anonymous, emergency, developer, and service accounts. Users who require administrative privileges &lt;abbr title="Administrative privileges&amp;#10;The permissions that allow a user to perform certain functions on a system or network, such as installing software and changing configuration settings."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; on system accounts receive additional scrutiny by organizational personnel responsible for approving such accounts and privileged access. Types of accounts that organizations may prohibit due to increased risk include group, emergency, guest, anonymous, and temporary accounts.
+    <t>This requirement focuses on account management for systems and applications. The definition and enforcement of access authorizations other than those determined by account type (e.g., privileged access or non-privileged access) are addressed in **Access enforcement 03.01.02**. System account types include individual, group, temporary, system, guest, anonymous, emergency, developer, and service accounts. Users who require administrative privileges &lt;abbr title="Administrative privileges&amp;#10;The permissions that allow a user to perform certain functions on a system or network, such as installing software and changing configuration settings."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; on system accounts receive additional scrutiny by organizational personnel responsible for approving such accounts and privileged access. Types of accounts that organizations may prohibit due to increased risk include group, emergency, guest, anonymous, and temporary accounts.
 Organizations may choose to define access privileges or other attributes by account, type of account, or a combination of both. Other attributes required for authorizing access include restrictions on time-of-day, day-of-week, and point of origin. In defining other account attributes, organizations consider system requirements (e.g., system upgrades, scheduled maintenance) and mission and business requirements (e.g., time zone differences, remote access to facilitate travel requirements).
 Users who pose a significant security and/or privacy risk include individuals for whom reliable evidence indicates either the intention to use authorized access to the system to cause harm or that adversaries will cause harm through them. Close coordination among human resource managers, mission/business owners, system administrators, and legal staff is essential when disabling system accounts for high-risk individuals. Time periods for the notification of organizational personnel or roles may vary.
 Inactivity logout is behaviour- or policy-based and requires users to take physical action to log out when they are expecting inactivity longer than the defined period. Automatic enforcement of inactivity logout is addressed by **Device lock 03.01.10**.</t>
@@ -697,10 +697,10 @@
     <t>03.01.04.disc</t>
   </si>
   <si>
-    <t>La séparation des tâches &lt;abbr title="Séparation des tâches&amp;#10;Principe de sécurité selon lequel il convient de répartir les responsabilités de nature sensible ou essentielle entre plusieurs entités (comme le personnel ou les processus) plutôt que les attribuer à une seule, afin de prévenir les infractions à la sécurité."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; permet d’éliminer l’abus possible des privilèges autorisés et réduit le risque d’activités malveillantes sans collusion. Les mécanismes de séparation des tâches comprennent notamment : la division des fonctions liées à la mission et des fonctions de soutien entre les personnes ou rôles, l’exécution de fonctions de soutien liées au système par différentes personnes ou différents rôles (par exemple, l’assurance de la qualité, la gestion de la configuration, la gestion du système, les évaluations, la programmation et la sécurité réseau) et l’assurance que le personnel qui administre les fonctions de contrôle d’accès n’administre pas également les fonctions de vérification. Puisque les violations de séparation des tâches peuvent s’étendre sur plusieurs systèmes et domaines d’application, les organisations doivent prendre en considération l’ensemble de leurs systèmes et de leurs composants de système lors de l’élaboration des stratégies sur la séparation des tâches. Cette exigence est appliquée par l’exigence **Application de l'accès 03.01.02**.</t>
-  </si>
-  <si>
-    <t>Separation of duties &lt;abbr title="Separation of duties&amp;#10;A security principle stating that sensitive or critical responsibilities should be shared by multiple entities (e.g. staff or processes), rather than a single entity, to prevent a security breach."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; addresses the potential for abuse of authorized privileges and reduces the risk of malicious activity without collusion. Separation of duties includes dividing mission functions and support functions among different individuals or roles, conducting system support functions with different individuals or roles (e.g., quality assurance, configuration management, system management, assessments, programming, and network security), and ensuring that personnel who administer access control functions do not also administer audit functions. Because separation of duty violations can span systems and application domains, organizations consider the entirety of their systems and system components when developing policies on separation of duties. This requirement is enforced by **Access enforcement 03.01.02**.</t>
+    <t>La séparation des tâches &lt;abbr title="Séparation des tâches&amp;#10;Principe de sécurité selon lequel il convient de répartir les responsabilités de nature sensible ou essentielle entre plusieurs entités (comme le personnel ou les processus) plutôt que les attribuer à une seule, afin de prévenir les infractions à la sécurité."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; permet d’éliminer l’abus possible des privilèges autorisés et réduit le risque d’activités malveillantes sans collusion. Les mécanismes de séparation des tâches comprennent notamment : la division des fonctions liées à la mission et des fonctions de soutien entre les personnes ou rôles, l’exécution de fonctions de soutien liées au système par différentes personnes ou différents rôles (par exemple, l’assurance de la qualité, la gestion de la configuration, la gestion du système, les évaluations, la programmation et la sécurité réseau) et l’assurance que le personnel qui administre les fonctions de contrôle d’accès n’administre pas également les fonctions de vérification. Puisque les violations de séparation des tâches peuvent s’étendre sur plusieurs systèmes et domaines d’application, les organisations doivent prendre en considération l’ensemble de leurs systèmes et de leurs composants de système lors de l’élaboration des stratégies sur la séparation des tâches. Cette exigence est appliquée par l’exigence **Application de l'accès 03.01.02**.</t>
+  </si>
+  <si>
+    <t>Separation of duties &lt;abbr title="Separation of duties&amp;#10;A security principle stating that sensitive or critical responsibilities should be shared by multiple entities (e.g. staff or processes), rather than a single entity, to prevent a security breach."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; addresses the potential for abuse of authorized privileges and reduces the risk of malicious activity without collusion. Separation of duties includes dividing mission functions and support functions among different individuals or roles, conducting system support functions with different individuals or roles (e.g., quality assurance, configuration management, system management, assessments, programming, and network security), and ensuring that personnel who administer access control functions do not also administer audit functions. Because separation of duty violations can span systems and application domains, organizations consider the entirety of their systems and system components when developing policies on separation of duties. This requirement is enforced by **Access enforcement 03.01.02**.</t>
   </si>
   <si>
     <t>03.01.05</t>
@@ -751,10 +751,10 @@
     <t>03.01.05.disc</t>
   </si>
   <si>
-    <t>Les organisations doivent avoir recours au principe de droit d’accès minimal &lt;abbr title="Droit d’accès minimal&amp;#10;Principe selon lequel il convient de n&amp;#x27;accorder aux utilisateurs que les autorisations d&amp;#x27;accès dont ils ont besoin pour accomplir les tâches qui leur ont été dûment attribuées. Ce principe permet de limiter les dommages pouvant résulter d&amp;#x27;une utilisation non autorisée – abusive ou accidentelle – d&amp;#x27;un système d&amp;#x27;information."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; pour des tâches précises et les accès autorisés pour les utilisatrices et utilisateurs et les processus système. Le principe de droit d’accès minimal s’applique au développement, à la mise en œuvre et à l’exploitation du système. Les organisations doivent envisager de créer des processus, des rôles et des comptes système supplémentaires afin de répondre à ce principe. Les fonctions de sécurité comprennent notamment l’établissement de comptes système, l’attribution de privilèges, l’installation de logiciels, la configuration des autorisations d’accès, la configuration des paramètres pour les événements qui seront vérifiés, l’établissement des paramètres de balayage des vulnérabilités, l’établissement des paramètres de détection &lt;abbr title="Détection&amp;#10;Surveillance et analyse des événements d&amp;#x27;un système en vue de relever les tentatives d’accès non autorisées aux ressources du système."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; d’intrusion et la gestion de l’information de vérification. L’information liée à la sécurité comprend notamment l’information sur les menaces et les vulnérabilités, les règles de filtrage pour les routeurs et les pare-feu, les paramètres de configuration pour les services de sécurité, l’architecture de sécurité, l’information de gestion des clés &lt;abbr title="Gestion des clés&amp;#10;Procédures et mécanismes de génération, de distribution, de remplacement, de stockage, d&amp;#x27;archivage et de destruction des clés cryptographiques."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; cryptographiques, les listes de contrôle d’accès et l’information de vérification.</t>
-  </si>
-  <si>
-    <t>Organizations employ the principle of least privilege &lt;abbr title="Least privilege&amp;#10;The principle of giving an individual only the set of privileges that are essential to performing authorized tasks. This principle limits the damage that can result from the accidental, incorrect, or unauthorized use of an information system."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; for specific duties and authorized access for users and system processes. Least privilege is applied to the development, implementation, and operation of the system. Organizations consider creating additional processes, roles, and system accounts to achieve least privilege. Security functions include establishing system accounts and assigning privileges, installing software, configuring access authorizations, configuring settings for events to be audited, establishing vulnerability &lt;abbr title="Vulnerability&amp;#10;A flaw or weakness in the design or implementation of an information system or its environment that could be exploited to adversely affect an organization&amp;#x27;s assets or operations."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; scanning parameters, establishing intrusion detection &lt;abbr title="Intrusion detection&amp;#10;A security service that monitors and analyzes network or system events to warn of unauthorized access attempts. The findings are provided in real-time (or near real-time)."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; parameters, and managing audit information. Security-relevant information includes threat and vulnerability information, filtering rules for routers or firewalls, configuration parameters for security services, security architecture, cryptographic key &lt;abbr title="Cryptographic key&amp;#10;A numerical value used in cryptographic processes, such as encryption, decryption, signature generation, and signature verification."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; management information, access control lists, and audit information.</t>
+    <t>Les organisations doivent avoir recours au principe de droit d’accès minimal &lt;abbr title="Droit d’accès minimal&amp;#10;Principe selon lequel il convient de n&amp;#x27;accorder aux utilisateurs que les autorisations d&amp;#x27;accès dont ils ont besoin pour accomplir les tâches qui leur ont été dûment attribuées. Ce principe permet de limiter les dommages pouvant résulter d&amp;#x27;une utilisation non autorisée – abusive ou accidentelle – d&amp;#x27;un système d&amp;#x27;information."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; pour des tâches précises et les accès autorisés pour les utilisatrices et utilisateurs et les processus système. Le principe de droit d’accès minimal s’applique au développement, à la mise en œuvre et à l’exploitation du système. Les organisations doivent envisager de créer des processus, des rôles et des comptes système supplémentaires afin de répondre à ce principe. Les fonctions de sécurité comprennent notamment l’établissement de comptes système, l’attribution de privilèges, l’installation de logiciels, la configuration des autorisations d’accès, la configuration des paramètres pour les événements qui seront vérifiés, l’établissement des paramètres de balayage des vulnérabilités, l’établissement des paramètres de détection &lt;abbr title="Détection&amp;#10;Surveillance et analyse des événements d&amp;#x27;un système en vue de relever les tentatives d’accès non autorisées aux ressources du système."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; d’intrusion et la gestion de l’information de vérification. L’information liée à la sécurité comprend notamment l’information sur les menaces et les vulnérabilités, les règles de filtrage pour les routeurs et les pare-feu, les paramètres de configuration pour les services de sécurité, l’architecture de sécurité, l’information de gestion des clés &lt;abbr title="Gestion des clés&amp;#10;Procédures et mécanismes de génération, de distribution, de remplacement, de stockage, d&amp;#x27;archivage et de destruction des clés cryptographiques."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; cryptographiques, les listes de contrôle d’accès et l’information de vérification.</t>
+  </si>
+  <si>
+    <t>Organizations employ the principle of least privilege &lt;abbr title="Least privilege&amp;#10;The principle of giving an individual only the set of privileges that are essential to performing authorized tasks. This principle limits the damage that can result from the accidental, incorrect, or unauthorized use of an information system."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; for specific duties and authorized access for users and system processes. Least privilege is applied to the development, implementation, and operation of the system. Organizations consider creating additional processes, roles, and system accounts to achieve least privilege. Security functions include establishing system accounts and assigning privileges, installing software, configuring access authorizations, configuring settings for events to be audited, establishing vulnerability &lt;abbr title="Vulnerability&amp;#10;A flaw or weakness in the design or implementation of an information system or its environment that could be exploited to adversely affect an organization&amp;#x27;s assets or operations."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; scanning parameters, establishing intrusion detection &lt;abbr title="Intrusion detection&amp;#10;A security service that monitors and analyzes network or system events to warn of unauthorized access attempts. The findings are provided in real-time (or near real-time)."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; parameters, and managing audit information. Security-relevant information includes threat and vulnerability information, filtering rules for routers or firewalls, configuration parameters for security services, security architecture, cryptographic key &lt;abbr title="Cryptographic key&amp;#10;A numerical value used in cryptographic processes, such as encryption, decryption, signature generation, and signature verification."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; management information, access control lists, and audit information.</t>
   </si>
   <si>
     <t>03.01.06</t>
@@ -838,7 +838,7 @@
 Une mauvaise utilisation des fonctions privilégiées, qu’elle soit intentionnelle ou non, par des utilisatrices et utilisateurs autorisés ou par des entités externes non autorisées ayant compromis des comptes système est une préoccupation constante et sérieuse qui peut avoir des répercussions négatives importantes sur les organisations. La journalisation de l’utilisation des fonctions privilégiées est une méthode permettant de détecter les mauvaises utilisations et d’atténuer les risques liés aux menaces persistantes avancées et aux menaces internes.</t>
   </si>
   <si>
-    <t>Privileged functions include establishing system accounts, performing system integrity &lt;abbr title="Integrity&amp;#10;The ability to protect information from being modified or deleted unintentionally or when it’s not supposed to be. Integrity helps determine that information is what it claims to be. Integrity also applies to business processes, software application logic, hardware, and personnel."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; checks, conducting patching operations, or administering cryptographic key management activities. Non-privileged users do not possess the authorizations to execute privileged functions. Bypassing intrusion detection and prevention mechanisms or malicious code protection mechanisms are examples of privileged functions that require protection from non-privileged users. This requirement represents a condition to be achieved by the definition of authorized privileges in **Account management 03.01.01** and privilege enforcement in **Access enforcement 03.01.02**.
+    <t>Privileged functions include establishing system accounts, performing system integrity &lt;abbr title="Integrity&amp;#10;The ability to protect information from being modified or deleted unintentionally or when it’s not supposed to be. Integrity helps determine that information is what it claims to be. Integrity also applies to business processes, software application logic, hardware, and personnel."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; checks, conducting patching operations, or administering cryptographic key management activities. Non-privileged users do not possess the authorizations to execute privileged functions. Bypassing intrusion detection and prevention mechanisms or malicious code protection mechanisms are examples of privileged functions that require protection from non-privileged users. This requirement represents a condition to be achieved by the definition of authorized privileges in **Account management 03.01.01** and privilege enforcement in **Access enforcement 03.01.02**.
 The misuse of privileged functions – whether intentionally or unintentionally by authorized users or by unauthorized external entities that have compromised system accounts – is a serious and ongoing concern that can have significant adverse impacts on organizations. Logging the use of privileged functions is one way to detect such misuse and mitigate the risks from advanced persistent threats and insider threats.</t>
   </si>
   <si>
@@ -1028,7 +1028,7 @@
   </si>
   <si>
     <t>Un accès à distance (ou accès distant) est l’accès des utilisatrices et utilisateurs (ou des processus exécutés en leur nom) aux systèmes au moyen de réseaux externes, comme Internet. Les méthodes de surveillance et de contrôle d’accès à distance permettent aux organisations de détecter les attaques et d’assurer la conformité aux stratégies d’accès à distance. L’acheminement de l’accès distant au moyen de points de contrôle d’accès gérés améliore le contrôle explicite de telles connexions et réduit la probabilité d’accès non autorisé au système, ce qui réduit également la probabilité de divulgation non autorisée d’information désignée.
-L’accès distant à un système représente une vulnérabilité &lt;abbr title="Vulnérabilité&amp;#10;Défectuosité ou lacune inhérente à la conception ou à la mise en œuvre d’un système d’information ou à son environnement, qui pourrait être exploitée en vue de compromettre les biens ou les activités d’une organisation."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; potentielle importante pouvant être exploitée par des adversaires. La restriction des commandes et des accès privilégiés à l’information liée à la sécurité au moyen d’un accès à distance réduit l’exposition des organisations et leur vulnérabilité aux menaces provenant des adversaires. Une commande privilégiée est une commande lancée par un humain et exécutée sur un système impliquant le contrôle, la surveillance ou l’administration du système, y compris les fonctions de sécurité ou l’information liée à la sécurité. L’information liée à la sécurité constitue de l’information susceptible d’influer sur l’exécution des fonctions de sécurité ou la prestation des services de sécurité, de telle façon qu’elle nuirait à l’application des stratégies de sécurité du système ou à l’isolation du code et des données. Les commandes privilégiées permettent aux personnes d’exécuter des fonctions sensibles, essentielles à la sécurité ou liées à la sécurité du système.</t>
+L’accès distant à un système représente une vulnérabilité &lt;abbr title="Vulnérabilité&amp;#10;Défectuosité ou lacune inhérente à la conception ou à la mise en œuvre d’un système d’information ou à son environnement, qui pourrait être exploitée en vue de compromettre les biens ou les activités d’une organisation."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; potentielle importante pouvant être exploitée par des adversaires. La restriction des commandes et des accès privilégiés à l’information liée à la sécurité au moyen d’un accès à distance réduit l’exposition des organisations et leur vulnérabilité aux menaces provenant des adversaires. Une commande privilégiée est une commande lancée par un humain et exécutée sur un système impliquant le contrôle, la surveillance ou l’administration du système, y compris les fonctions de sécurité ou l’information liée à la sécurité. L’information liée à la sécurité constitue de l’information susceptible d’influer sur l’exécution des fonctions de sécurité ou la prestation des services de sécurité, de telle façon qu’elle nuirait à l’application des stratégies de sécurité du système ou à l’isolation du code et des données. Les commandes privilégiées permettent aux personnes d’exécuter des fonctions sensibles, essentielles à la sécurité ou liées à la sécurité du système.</t>
   </si>
   <si>
     <t>Remote access is access to systems (or processes acting on behalf of users) that communicate through external networks, such as the Internet. Monitoring and controlling remote access methods allows organizations to detect attacks and ensure compliance with remote access policies. Routing remote access through managed access control points enhances explicit control over such connections and reduces susceptibility to unauthorized access to the system, which could result in the unauthorized disclosure of specified information.
@@ -1083,10 +1083,10 @@
     <t>03.01.16.disc</t>
   </si>
   <si>
-    <t>Les capacités de réseau sans fil représentent une vulnérabilité potentielle importante pouvant être exploitée par des adversaires. L’établissement de restrictions d’utilisation ainsi que les exigences en matière de configuration et de connexion pour l’accès sans fil au système offrent des critères permettant d’appuyer les décisions d’autorisation d’accès. Ces restrictions et exigences réduisent la possibilité des accès système non autorisés par des technologies sans fil. Les réseaux sans fil utilisent des protocoles d’authentification &lt;abbr title="Authentification&amp;#10;Processus ou mesure permettant de vérifier l’identité d’un utilisateur."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; afin de fournir une protection au moyen de justificatifs d’identité et d’une authentification mutuelle. Les organisations authentifient les personnes et les dispositifs afin de protéger les accès sans fil au système. Une attention particulière doit être accordée à la variété des appareils dotés d’un accès sans fil au système, y compris les appareils mobiles de petite taille (par exemple, les téléphones intelligents, les tablettes et les montres intelligentes). Les capacités de réseau sans fil intégrées aux composants système représentent une vulnérabilité potentielle importante pouvant être exploitée par des adversaires. Un mécanisme rigoureux d’authentification des utilisatrices et utilisateurs et des appareils, un chiffrement &lt;abbr title="Chiffrement&amp;#10;Procédure par laquelle une information est convertie d’une forme à une autre afin d’en dissimuler le contenu et d&amp;#x27;en interdire l’accès aux entités non autorisées."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; robuste et la désactivation des capacités sans fil non nécessaires à la mission ou aux activités peuvent réduire sensiblement les menaces que font peser les adversaires exploitant des technologies sans fil.</t>
-  </si>
-  <si>
-    <t>Wireless networking capabilities represent a significant potential vulnerability that can be exploited by adversaries. Establishing usage restrictions, configuration requirements, and connection requirements for wireless access to the system provides criteria to support access authorization &lt;abbr title="Authorization&amp;#10;Access privileges granted to a user, program, or process."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; decisions. These restrictions and requirements reduce susceptibility to unauthorized system access through wireless technologies. Wireless networks use authentication &lt;abbr title="Authentication&amp;#10;A process or measure used to verify a users identity."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; protocols that provide credential protection and mutual authentication. Organizations authenticate individuals and devices to protect wireless access to the system. Special attention is given to the variety of devices with potential wireless access to the system, including small form factor mobile devices (e.g., smart phones, tablets, smart watches). Wireless networking capabilities that are embedded within system components represent a significant potential vulnerability that can be exploited by adversaries. Strong authentication of users and devices, strong encryption &lt;abbr title="Encryption&amp;#10;Converting information from one form to another to hide its content and prevent unauthorized access."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt;, and disabling wireless capabilities that are not needed for essential missions or business functions can reduce susceptibility to threats by adversaries involving wireless technologies.</t>
+    <t>Les capacités de réseau sans fil représentent une vulnérabilité potentielle importante pouvant être exploitée par des adversaires. L’établissement de restrictions d’utilisation ainsi que les exigences en matière de configuration et de connexion pour l’accès sans fil au système offrent des critères permettant d’appuyer les décisions d’autorisation d’accès. Ces restrictions et exigences réduisent la possibilité des accès système non autorisés par des technologies sans fil. Les réseaux sans fil utilisent des protocoles d’authentification &lt;abbr title="Authentification&amp;#10;Processus ou mesure permettant de vérifier l’identité d’un utilisateur."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; afin de fournir une protection au moyen de justificatifs d’identité et d’une authentification mutuelle. Les organisations authentifient les personnes et les dispositifs afin de protéger les accès sans fil au système. Une attention particulière doit être accordée à la variété des appareils dotés d’un accès sans fil au système, y compris les appareils mobiles de petite taille (par exemple, les téléphones intelligents, les tablettes et les montres intelligentes). Les capacités de réseau sans fil intégrées aux composants système représentent une vulnérabilité potentielle importante pouvant être exploitée par des adversaires. Un mécanisme rigoureux d’authentification des utilisatrices et utilisateurs et des appareils, un chiffrement &lt;abbr title="Chiffrement&amp;#10;Procédure par laquelle une information est convertie d’une forme à une autre afin d’en dissimuler le contenu et d&amp;#x27;en interdire l’accès aux entités non autorisées."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; robuste et la désactivation des capacités sans fil non nécessaires à la mission ou aux activités peuvent réduire sensiblement les menaces que font peser les adversaires exploitant des technologies sans fil.</t>
+  </si>
+  <si>
+    <t>Wireless networking capabilities represent a significant potential vulnerability that can be exploited by adversaries. Establishing usage restrictions, configuration requirements, and connection requirements for wireless access to the system provides criteria to support access authorization &lt;abbr title="Authorization&amp;#10;Access privileges granted to a user, program, or process."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; decisions. These restrictions and requirements reduce susceptibility to unauthorized system access through wireless technologies. Wireless networks use authentication &lt;abbr title="Authentication&amp;#10;A process or measure used to verify a users identity."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; protocols that provide credential protection and mutual authentication. Organizations authenticate individuals and devices to protect wireless access to the system. Special attention is given to the variety of devices with potential wireless access to the system, including small form factor mobile devices (e.g., smart phones, tablets, smart watches). Wireless networking capabilities that are embedded within system components represent a significant potential vulnerability that can be exploited by adversaries. Strong authentication of users and devices, strong encryption &lt;abbr title="Encryption&amp;#10;Converting information from one form to another to hide its content and prevent unauthorized access."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt;, and disabling wireless capabilities that are not needed for essential missions or business functions can reduce susceptibility to threats by adversaries involving wireless technologies.</t>
   </si>
   <si>
     <t>03.01.18</t>
@@ -1133,7 +1133,7 @@
   </si>
   <si>
     <t>A mobile device is a computing device that has a small form factor such that it can easily be carried by a single individual; is designed to operate without a physical connection; possesses local, non-removable, or removable data storage; and includes a self-contained power source. Mobile device functionality may also include voice communication capabilities, on-board sensors that allow the device to capture information, and/or built-in features for synchronizing local data with remote locations. Examples include smart phones, smart watches, and tablets. Mobile devices are typically associated with a single individual. The processing, storage, and transmission capabilities of mobile devices may be comparable to or a subset of notebook or desktop systems, depending on the nature and intended purpose of the device. The protection and control of mobile devices are behaviour- or policy-based and requires users to take physical action to protect and control such devices when outside of controlled areas. Controlled areas are spaces for which the organization provides physical or procedural controls to meet the requirements established for protecting specified information.
-Due to the large variety of mobile devices with different characteristics and capabilities, organizational restrictions may vary for the different classes or types of such devices. Usage restrictions, configuration requirements, and connection requirements for mobile devices include configuration management, device identification and authentication, implementing mandatory protective software, scanning devices for malicious code, updating virus &lt;abbr title="Virus&amp;#10;A computer program that can spread by making copies of itself. Computer viruses spread from one computer to another, usually without the knowledge of the user. Viruses can have harmful effects, ranging from displaying irritating messages to stealing data or giving other users control over the infected computer."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; protection software, scanning for critical software updates and patches, conducting primary operating system and possibly other software integrity checks, and disabling unnecessary hardware. On mobile devices, secure containers provide software-based data isolation designed to segment enterprise applications and information from personal apps and data. Containers may present multiple user interfaces, one of the most common being a mobile application that acts as a portal to a suite of business productivity apps, such as email, contacts, and calendar. Organizations can employ full-device encryption or container-based encryption to protect the confidentiality of specified information on mobile devices.</t>
+Due to the large variety of mobile devices with different characteristics and capabilities, organizational restrictions may vary for the different classes or types of such devices. Usage restrictions, configuration requirements, and connection requirements for mobile devices include configuration management, device identification and authentication, implementing mandatory protective software, scanning devices for malicious code, updating virus &lt;abbr title="Virus&amp;#10;A computer program that can spread by making copies of itself. Computer viruses spread from one computer to another, usually without the knowledge of the user. Viruses can have harmful effects, ranging from displaying irritating messages to stealing data or giving other users control over the infected computer."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; protection software, scanning for critical software updates and patches, conducting primary operating system and possibly other software integrity checks, and disabling unnecessary hardware. On mobile devices, secure containers provide software-based data isolation designed to segment enterprise applications and information from personal apps and data. Containers may present multiple user interfaces, one of the most common being a mobile application that acts as a portal to a suite of business productivity apps, such as email, contacts, and calendar. Organizations can employ full-device encryption or container-based encryption to protect the confidentiality of specified information on mobile devices.</t>
   </si>
   <si>
     <t>03.01.20</t>
@@ -1207,7 +1207,7 @@
   </si>
   <si>
     <t>External systems are systems that are used by but are not part of the organization. These systems include personally owned systems, system components, or devices; privately owned computing and communication devices in commercial or public facilities; systems owned or controlled by non-federal organizations; and systems managed by contractors. Organizations have the option to prohibit the use of any type of external system or specified types of external systems, (e.g., prohibit the use of external systems that are not organization-owned). Terms and conditions are consistent with the trust relationships established with the entities that own, operate, or maintain external systems and include descriptions of shared responsibilities.
-Authorized individuals include organizational personnel, contractors, or other individuals with authorized access to the organizational system and over whom the organization has the authority to impose specific rules of behaviour regarding system access. Restrictions that organizations impose on authorized individuals may vary depending on the trust relationships between the organization and external entities. Organizations need assurance that the external systems satisfy the necessary security requirements so as not to compromise &lt;abbr title="Compromise&amp;#10;The intentional or unintentional disclosure of information, which adversely impacts its confidentiality, integrity, or availability."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt;, damage, or harm the system. This requirement is related to **External system services 03.16.03**.</t>
+Authorized individuals include organizational personnel, contractors, or other individuals with authorized access to the organizational system and over whom the organization has the authority to impose specific rules of behaviour regarding system access. Restrictions that organizations impose on authorized individuals may vary depending on the trust relationships between the organization and external entities. Organizations need assurance that the external systems satisfy the necessary security requirements so as not to compromise &lt;abbr title="Compromise&amp;#10;The intentional or unintentional disclosure of information, which adversely impacts its confidentiality, integrity, or availability."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt;, damage, or harm the system. This requirement is related to **External system services 03.16.03**.</t>
   </si>
   <si>
     <t>03.01.22</t>
@@ -1318,16 +1318,16 @@
     <t>03.02.01.disc</t>
   </si>
   <si>
-    <t>Les organisations doivent fournir de la formation de base et avancée en matière de sécurité et de protection de la vie privée aux utilisatrices et utilisateurs du système (y compris les gestionnaires, la haute direction, les administratrices et administrateurs de système et les entrepreneures et entrepreneurs) ainsi que des mesures pour tester les connaissances des utilisatrices et utilisateurs. Les organisations doivent établir le contenu de la formation en fonction de leurs exigences organisationnelles particulières, des systèmes auxquels le personnel a accès et des environnements de travail (par exemple, le télétravail). Le contenu devrait comprendre une présentation des besoins de sécurité et les mesures que doivent prendre les utilisatrices et utilisateurs afin de maintenir la sécurité et d’intervenir en cas d’incident &lt;abbr title="Incident&amp;#10;Incident réel au cours duquel un agent de menace exploite une vulnérabilité d’un bien de TI de valeur."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt;. Le contenu devrait également inclure les mesures nécessaires en matière de sécurité opérationnelle et de traitement de l’information désignée.
+    <t>Les organisations doivent fournir de la formation de base et avancée en matière de sécurité et de protection de la vie privée aux utilisatrices et utilisateurs du système (y compris les gestionnaires, la haute direction, les administratrices et administrateurs de système et les entrepreneures et entrepreneurs) ainsi que des mesures pour tester les connaissances des utilisatrices et utilisateurs. Les organisations doivent établir le contenu de la formation en fonction de leurs exigences organisationnelles particulières, des systèmes auxquels le personnel a accès et des environnements de travail (par exemple, le télétravail). Le contenu devrait comprendre une présentation des besoins de sécurité et les mesures que doivent prendre les utilisatrices et utilisateurs afin de maintenir la sécurité et d’intervenir en cas d’incident &lt;abbr title="Incident&amp;#10;Incident réel au cours duquel un agent de menace exploite une vulnérabilité d’un bien de TI de valeur."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt;. Le contenu devrait également inclure les mesures nécessaires en matière de sécurité opérationnelle et de traitement de l’information désignée.
 Les techniques de sensibilisation à la sécurité et à la protection de la vie privée comprennent des affiches, des objets affichant des rappels de sécurité, des messages au moment de la connexion, des avis envoyés par courriel ou de la part des responsables de l’organisation et des événements de sensibilisation au moyen de balados, de vidéos ou de webinaires. La formation sur la sécurité et la protection de la vie privée doit être menée à une fréquence conforme aux lois, aux directives, aux réglementations et aux politiques applicables. La mise à jour périodique du contenu de formation permet de s’assurer que le contenu reste pertinent. Les événements qui peuvent précipiter une mise à jour du contenu de la formation comprennent les conclusions d’une évaluation ou d’une vérification, des incidents ou violations de sécurité, et des chargements apportés aux lois, aux décrets, aux directives, aux réglementations, aux politiques, aux normes et aux lignes directrices applicables.
 Les indicateurs potentiels et les possibles signes précurseurs de menace interne peuvent comprendre des comportements comme les suivants : des comportements excessifs, de l’insatisfaction de longue durée liée au travail, des tentatives d’accès à de l’information qui n’est pas nécessaire pour la réalisation du travail, un accès inexpliqué à des ressources financières, de l’intimidation ou du harcèlement sexuel envers des collègues, de la violence en milieu de travail et d’autres manquements graves aux politiques, aux procédures, aux règles, aux directives ou aux pratiques de l’organisation. Les organisations peuvent adapter le sujet de la sensibilisation aux menaces internes en fonction du rôle (par exemple, la formation des gestionnaires peut se concentrer sur les changements particuliers dans les comportements des membres de l’équipe, alors que la formation des employées et employés peut porter sur des observations plus générales).
-Le piratage psychologique &lt;abbr title="Piratage psychologique&amp;#10;Pratique qui a pour but d&amp;#x27;extorquer des informations confidentielles en manipulant les utilisateurs. Un pirate psychologique utilise souvent le téléphone ou l&amp;#x27;Internet pour tromper les individus et parvenir à obtenir leurs renseignements personnels. L&amp;#x27;hameçonnage est une forme de piratage psychologique."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; vise à tromper une personne pour l’inciter à révéler de l’information ou à faire une opération pouvant servir à s’introduire dans un système, à le compromettre ou à nuire à un système. Le piratage psychologique comprend l’hameçonnage &lt;abbr title="Hameçonnage&amp;#10;Procédé par lequel une tierce partie tente de solliciter de l’information confidentielle appartenant à un individu, à un groupe ou à une organisation en les mystifiant ou en imitant une marque commerciale connue dans le but de réaliser des gains financiers. En l’occurrence, les malfaiteurs incitent les utilisateurs à partager leurs renseignements personnels (numéros de carte de crédit, informations bancaires ou autres renseignements) afin de s’en servir pour commettre des actes frauduleux."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt;, le faux-semblant, l’usurpation d’identité, l’appâtage, l’arnaque de la contrepartie, le détournement de chaînes de courriels, l’exploitation des médias sociaux et le talonnage. L’exploration de données dans les médias sociaux vise à recueillir de l’information à propos de l’organisation qui pourrait servir à appuyer des attaques à venir. La formation en matière de sécurité et de protection de la vie privée porte notamment sur la façon dont les membres du personnel et de la direction peuvent communiquer leurs préoccupations concernant des indicateurs potentiels de menace interne et des instances réelles et potentielles de piratage psychologique et d’exploration de données, au moyen des voies de communication appropriées de l’organisation, conformément aux politiques et aux procédures établies.</t>
+Le piratage psychologique &lt;abbr title="Piratage psychologique&amp;#10;Pratique qui a pour but d&amp;#x27;extorquer des informations confidentielles en manipulant les utilisateurs. Un pirate psychologique utilise souvent le téléphone ou l&amp;#x27;Internet pour tromper les individus et parvenir à obtenir leurs renseignements personnels. L&amp;#x27;hameçonnage est une forme de piratage psychologique."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; vise à tromper une personne pour l’inciter à révéler de l’information ou à faire une opération pouvant servir à s’introduire dans un système, à le compromettre ou à nuire à un système. Le piratage psychologique comprend l’hameçonnage &lt;abbr title="Hameçonnage&amp;#10;Procédé par lequel une tierce partie tente de solliciter de l’information confidentielle appartenant à un individu, à un groupe ou à une organisation en les mystifiant ou en imitant une marque commerciale connue dans le but de réaliser des gains financiers. En l’occurrence, les malfaiteurs incitent les utilisateurs à partager leurs renseignements personnels (numéros de carte de crédit, informations bancaires ou autres renseignements) afin de s’en servir pour commettre des actes frauduleux."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt;, le faux-semblant, l’usurpation d’identité, l’appâtage, l’arnaque de la contrepartie, le détournement de chaînes de courriels, l’exploitation des médias sociaux et le talonnage. L’exploration de données dans les médias sociaux vise à recueillir de l’information à propos de l’organisation qui pourrait servir à appuyer des attaques à venir. La formation en matière de sécurité et de protection de la vie privée porte notamment sur la façon dont les membres du personnel et de la direction peuvent communiquer leurs préoccupations concernant des indicateurs potentiels de menace interne et des instances réelles et potentielles de piratage psychologique et d’exploration de données, au moyen des voies de communication appropriées de l’organisation, conformément aux politiques et aux procédures établies.</t>
   </si>
   <si>
     <t>Organizations provide basic and advanced levels of security and privacy literacy training to system users (including managers, senior executives, system administrators, and contractors) and measures to test the knowledge level of users. Organizations determine the content of literacy training based on specific organizational requirements, the systems to which personnel have authorized access, and work environments (e.g., telework). The content includes an understanding of the need for security and the actions required of users to maintain security and to respond to incidents. The content also addresses the need for operations security and the handling of specified information.
 Security and privacy awareness techniques include displaying posters, offering supplies inscribed with security reminders, displaying logon screen messages, generating email advisories or notices from organizational officials, and conducting awareness events using podcasts, videos, and webinars. Security and privacy literacy training is conducted at a frequency consistent with applicable laws, directives, regulations, and policies. Updating literacy training content on a regular basis ensures that the content remains relevant. Events that may precipitate an update to literacy training content include assessment or audit findings, security incidents or breaches, or changes in applicable laws, Orders in Council, directives, regulations, policies, standards, and guidelines.
 Potential indicators and possible precursors of insider threats include behaviours such as inordinate, long-term job dissatisfaction; attempts to gain access to information that is not required for job performance; unexplained access to financial resources; sexual harassment or bullying of fellow employees; workplace violence; and other serious violations of the policies, procedures, rules, directives, or practices of organizations. Organizations may consider tailoring insider threat awareness topics to the role (e.g., training for managers may be focused on specific changes in the behaviour of team members, while training for employees may be focused on more general observations).
-Social engineering &lt;abbr title="Social engineering&amp;#10;The practice of obtaining confidential information by manipulation of legitimate users. A social engineer will commonly use the telephone or internet to trick people into revealing sensitive information. For example, phishing is a type of social engineering."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; is an attempt to deceive an individual into revealing information or taking an action that can be used to breach, compromise, or otherwise adversely impact a system. Social engineering includes phishing &lt;abbr title="Phishing&amp;#10;An attempt by a third party to solicit confidential information from an individual, group, or organization by mimicking or spoofing a specific, usually well-known brand, usually for financial gain. Phishers attempt to trick users into disclosing personal data, such as credit card numbers, online banking credentials, and other sensitive information, which they may then use to commit fraudulent acts."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt;, pretexting, impersonation, baiting, quid pro quo, threadjacking, social media exploitation, and tailgating. Social mining is an attempt to gather information about the organization that may be used to support future attacks. Security and privacy literacy training includes how to communicate employee and management concerns regarding potential indicators of insider threat and potential and actual instances of social engineering and data mining through appropriate organizational channels in accordance with established policies and procedures.</t>
+Social engineering &lt;abbr title="Social engineering&amp;#10;The practice of obtaining confidential information by manipulation of legitimate users. A social engineer will commonly use the telephone or internet to trick people into revealing sensitive information. For example, phishing is a type of social engineering."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; is an attempt to deceive an individual into revealing information or taking an action that can be used to breach, compromise, or otherwise adversely impact a system. Social engineering includes phishing &lt;abbr title="Phishing&amp;#10;An attempt by a third party to solicit confidential information from an individual, group, or organization by mimicking or spoofing a specific, usually well-known brand, usually for financial gain. Phishers attempt to trick users into disclosing personal data, such as credit card numbers, online banking credentials, and other sensitive information, which they may then use to commit fraudulent acts."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt;, pretexting, impersonation, baiting, quid pro quo, threadjacking, social media exploitation, and tailgating. Social mining is an attempt to gather information about the organization that may be used to support future attacks. Security and privacy literacy training includes how to communicate employee and management concerns regarding potential indicators of insider threat and potential and actual instances of social engineering and data mining through appropriate organizational channels in accordance with established policies and procedures.</t>
   </si>
   <si>
     <t>03.02.02</t>
@@ -2177,7 +2177,7 @@
     <t>03.04.12.disc</t>
   </si>
   <si>
-    <t>Lorsque l’on sait qu’un système ou qu’un composant système se trouvera dans une zone à risque élevé, des exigences de sécurité supplémentaires peuvent être nécessaires afin de contrer les menaces accrues. Les organisations peuvent mettre en œuvre des mesures de protection sur les systèmes ou les composants système qui sont utilisés par des personnes qui partent en voyage et qui en reviennent. Les mesures comprennent déterminer les lieux préoccupants, définir les configurations requises pour les composants, s’assurer que les composants sont configurés adéquatement avant le voyage et réaliser prendre d’autres mesures au retour du voyage. Par exemple, les systèmes qui se trouveront dans des zones à risque élevé peuvent être configurés avec des disques durs préalablement nettoyés, un nombre limité d’applications ou encore des paramètres de configuration plus stricts. Les mesures appliquées aux appareils mobiles au retour du voyage comprennent un examen de l’appareil afin de détecter des signes physiques de tentatives de modification, le nettoyage &lt;abbr title="Nettoyage&amp;#10;Processus par lequel les données sont retirées d’un support de manière définitive. Le support d’enregistrement peut être réutilisé conformément aux politiques de sécurité des TI, mais il est impossible de récupérer les données qui s’y trouvaient ou d’y accéder."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; de la mémoire ou la recréation de l’image de la mémoire de l’appareil.</t>
+    <t>Lorsque l’on sait qu’un système ou qu’un composant système se trouvera dans une zone à risque élevé, des exigences de sécurité supplémentaires peuvent être nécessaires afin de contrer les menaces accrues. Les organisations peuvent mettre en œuvre des mesures de protection sur les systèmes ou les composants système qui sont utilisés par des personnes qui partent en voyage et qui en reviennent. Les mesures comprennent déterminer les lieux préoccupants, définir les configurations requises pour les composants, s’assurer que les composants sont configurés adéquatement avant le voyage et réaliser prendre d’autres mesures au retour du voyage. Par exemple, les systèmes qui se trouveront dans des zones à risque élevé peuvent être configurés avec des disques durs préalablement nettoyés, un nombre limité d’applications ou encore des paramètres de configuration plus stricts. Les mesures appliquées aux appareils mobiles au retour du voyage comprennent un examen de l’appareil afin de détecter des signes physiques de tentatives de modification, le nettoyage &lt;abbr title="Nettoyage&amp;#10;Processus par lequel les données sont retirées d’un support de manière définitive. Le support d’enregistrement peut être réutilisé conformément aux politiques de sécurité des TI, mais il est impossible de récupérer les données qui s’y trouvaient ou d’y accéder."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; de la mémoire ou la recréation de l’image de la mémoire de l’appareil.</t>
   </si>
   <si>
     <t>When it is known that a system or a specific system component will be in a high-risk area, additional security requirements may be needed to counter the increased threat. Organizations can implement protective measures on systems or system components used by individuals departing on and returning from travel. Actions include determining locations of concern, defining the required configurations for the components, ensuring that the components are configured as intended before travel is initiated, and taking additional actions after travel is completed. For example, systems going into high-risk areas can be configured with sanitized hard drives, limited applications, and more stringent configuration settings. Actions applied to mobile devices upon return from travel include examining the device for signs of physical tampering and purging and reimaging the device storage.</t>
@@ -2276,13 +2276,13 @@
     <t>Mettre en œuvre des mécanismes robustes d’authentification multifacteur (AMF) pour l’accès aux comptes privilégiés et non privilégiés.</t>
   </si>
   <si>
-    <t>Implement strong multi-factor authentication &lt;abbr title="Multi-factor authentication&amp;#10;A tactic that can add an additional layer of security to your devices and account. Multi-factor authentication requires additional verification (like a PIN or fingerprint) to access your devices or accounts. Two-factor authentication is a type of multi-factor authentication."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; (MFA) for access to privileged and non-privileged accounts.</t>
+    <t>Implement strong multi-factor authentication &lt;abbr title="Multi-factor authentication&amp;#10;A tactic that can add an additional layer of security to your devices and account. Multi-factor authentication requires additional verification (like a PIN or fingerprint) to access your devices or accounts. Two-factor authentication is a type of multi-factor authentication."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; (MFA) for access to privileged and non-privileged accounts.</t>
   </si>
   <si>
     <t>03.05.03.disc</t>
   </si>
   <si>
-    <t>Cette exigence s’applique aux comptes d’utilisateur. L’authentification multifacteur nécessite l’utilisation de deux facteurs différents ou plus pour l’authentification. Les facteurs d’authentification sont définis comme suit : une information connue (par exemple, un numéro d’identification personnel [NIP]), une possession (par exemple, un authentifiant physique comme une clé cryptographique &lt;abbr title="Clé cryptographique&amp;#10;Valeur numérique employée dans des processus cryptographiques, notamment le chiffrement et le déchiffrement, la génération des signatures ou encore la vérification des signatures."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; privée) ou un attribut personnel (par exemple, une authentification biométrique). Les solutions d’authentification multifacteur qui présentent des authentifiants physiques comprennent les authentifiants matériels qui fournissent des sorties à durée limitée ou de type défi-réponse ainsi que des cartes à puce. En plus d’authentifier les utilisatrices et utilisateurs au niveau du système, les organisations peuvent également avoir recours à des mécanismes d’authentification au niveau de l’application pour accroître la sécurité de l’information.</t>
+    <t>Cette exigence s’applique aux comptes d’utilisateur. L’authentification multifacteur nécessite l’utilisation de deux facteurs différents ou plus pour l’authentification. Les facteurs d’authentification sont définis comme suit : une information connue (par exemple, un numéro d’identification personnel [NIP]), une possession (par exemple, un authentifiant physique comme une clé cryptographique &lt;abbr title="Clé cryptographique&amp;#10;Valeur numérique employée dans des processus cryptographiques, notamment le chiffrement et le déchiffrement, la génération des signatures ou encore la vérification des signatures."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; privée) ou un attribut personnel (par exemple, une authentification biométrique). Les solutions d’authentification multifacteur qui présentent des authentifiants physiques comprennent les authentifiants matériels qui fournissent des sorties à durée limitée ou de type défi-réponse ainsi que des cartes à puce. En plus d’authentifier les utilisatrices et utilisateurs au niveau du système, les organisations peuvent également avoir recours à des mécanismes d’authentification au niveau de l’application pour accroître la sécurité de l’information.</t>
   </si>
   <si>
     <t>This requirement applies to user accounts. Multi-factor authentication requires the use of two or more different factors to achieve authentication. The authentication factors are defined as follows: something you know (e.g., a personal identification number [PIN]), something you have (e.g., a physical authenticator, such as a cryptographic private key), or something you are (e.g., a biometric). Multi-factor authentication solutions that feature physical authenticators include hardware authenticators that provide time-based or challenge-response outputs and smart cards. In addition to authenticating users at the system level, organizations may also employ authentication mechanisms at the application level to provide increased information security.</t>
@@ -2437,7 +2437,7 @@
     <t>03.05.07.disc</t>
   </si>
   <si>
-    <t>L’authentification fondée sur un mot de passe s’applique aux mots de passe utilisés pour l’authentification à un seul facteur ou multifacteur. Les longs mots de passe ou les phrases de passe sont préférables, par rapport à des mots de passe courts. L’application de règles de composition offre certains avantages pour la sécurité, mais réduit l’utilisabilité. Les organisations peuvent choisir d’établir et d’appliquer certaines règles pour la génération de mots de passe (notamment concernant le nombre minimal de caractères) dans certaines circonstances. Par exemple, un mot de passe oublié peut mener à une récupération de compte. Des mots de passe protégés par chiffrement comprennent le hachage cryptographique unidirectionnel salé des mots de passe. La liste des mots de passe couramment utilisés, compromis ou attendus comprend les mots de passe provenant des corpus de violations précédentes, les mots du dictionnaire et les caractères répétitifs ou séquentiels. Cette liste comprend des mots s’appliquant au contexte, comme le nom du service, le nom de l’utilisateur et des dérivations de ces éléments. L’obligation de remplacer un mot de passe temporaire par un mot de passe permanent immédiatement après la connexion au système permet de s’assurer que les mécanismes d’authentification sont suffisamment robustes et mis en œuvre à la première occasion, ce qui permet de réduire les possibilités de compromission &lt;abbr title="Compromission&amp;#10;Divulgation intentionnelle ou non intentionnelle d’information mettant en péril la confidentialité, l&amp;#x27;intégrité ou la disponibilité de ladite information."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; d’authentifiants. Il peut être possible d’utiliser de longs mots de passe ou des phrases de passe dans le but d’augmenter la complexité des mots de passe.</t>
+    <t>L’authentification fondée sur un mot de passe s’applique aux mots de passe utilisés pour l’authentification à un seul facteur ou multifacteur. Les longs mots de passe ou les phrases de passe sont préférables, par rapport à des mots de passe courts. L’application de règles de composition offre certains avantages pour la sécurité, mais réduit l’utilisabilité. Les organisations peuvent choisir d’établir et d’appliquer certaines règles pour la génération de mots de passe (notamment concernant le nombre minimal de caractères) dans certaines circonstances. Par exemple, un mot de passe oublié peut mener à une récupération de compte. Des mots de passe protégés par chiffrement comprennent le hachage cryptographique unidirectionnel salé des mots de passe. La liste des mots de passe couramment utilisés, compromis ou attendus comprend les mots de passe provenant des corpus de violations précédentes, les mots du dictionnaire et les caractères répétitifs ou séquentiels. Cette liste comprend des mots s’appliquant au contexte, comme le nom du service, le nom de l’utilisateur et des dérivations de ces éléments. L’obligation de remplacer un mot de passe temporaire par un mot de passe permanent immédiatement après la connexion au système permet de s’assurer que les mécanismes d’authentification sont suffisamment robustes et mis en œuvre à la première occasion, ce qui permet de réduire les possibilités de compromission &lt;abbr title="Compromission&amp;#10;Divulgation intentionnelle ou non intentionnelle d’information mettant en péril la confidentialité, l&amp;#x27;intégrité ou la disponibilité de ladite information."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; d’authentifiants. Il peut être possible d’utiliser de longs mots de passe ou des phrases de passe dans le but d’augmenter la complexité des mots de passe.</t>
   </si>
   <si>
     <t>Password-based authentication applies to passwords used in single-factor or multi-factor authentication. Long passwords or passphrases are preferable to shorter passwords. Enforced composition rules provide marginal security benefits while decreasing usability. However, organizations may choose to establish and enforce certain rules for password generation (e.g., minimum character length) under certain circumstances. For example, account recovery can occur when a password is forgotten. Cryptographically protected passwords include salted one-way cryptographic hashes of passwords. The list of commonly used, compromised, or expected passwords includes passwords obtained from previous breach corpuses, dictionary words, and repetitive or sequential characters. The list includes context-specific words, such as the name of the service, username, and derivatives thereof. Changing temporary passwords to permanent passwords immediately after system logon ensures that the necessary strength of the authentication mechanism is implemented at the earliest opportunity and reduces the susceptibility to authenticator compromises. Long passwords and passphrases can be used to increase the complexity of passwords.</t>
@@ -2558,7 +2558,7 @@
     <t>Incident response</t>
   </si>
   <si>
-    <t>The Incident response controls support the establishment of an operational incident handling capability for organizational systems that includes adequate preparation, monitoring, detection &lt;abbr title="Detection&amp;#10;The monitoring and analyzing of system events in order to identify unauthorized attempts to access system resources."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt;, analysis, containment, recovery, and response. Incidents are monitored, documented, and reported to appropriate organizational officials and authorities.</t>
+    <t>The Incident response controls support the establishment of an operational incident handling capability for organizational systems that includes adequate preparation, monitoring, detection &lt;abbr title="Detection&amp;#10;The monitoring and analyzing of system events in order to identify unauthorized attempts to access system resources."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt;, analysis, containment, recovery, and response. Incidents are monitored, documented, and reported to appropriate organizational officials and authorities.</t>
   </si>
   <si>
     <t>03.06.01</t>
@@ -2998,7 +2998,7 @@
     <t>Le personnel de maintenance fait référence aux personnes qui réalisent les activités de maintenance matérielle ou logicielle sur le système, et l’exigence **Autorisations d'accès physique 03.10.01** traite de l’accès physique des personnes devant réaliser des activités de maintenance qui les placent dans le périmètre de protection physique du système. La compétence technique de supervision des personnes est liée à la maintenance réalisée sur le système, tandis que la possession des autorisations d’accès appropriées est liée à la maintenance sur ou près du système. Les personnes qui n’ont pas été identifiées précédemment comme faisant partie du personnel de maintenance autorisé (par exemple, les fabricants, les consultantes et consultants, les intégratrices et intégrateurs de systèmes et les fournisseurs) pourraient avoir besoin d’un accès privilégié au système, par exemple dans les cas où la maintenance doit être réalisée avec peu ou sans préavis. Les organisations peuvent choisir d’émettre des justificatifs d’identité temporaires à ces personnes, en fonction de leurs évaluations des risques. Ces justificatifs peuvent être octroyés pour un accès unique ou pour une période très limitée.</t>
   </si>
   <si>
-    <t>Maintenance personnel refers to individuals who perform hardware or software maintenance on the system, while **Physical access authorizations 03.10.01** addresses physical access for individuals whose maintenance duties place them within the physical protection perimeter &lt;abbr title="Perimeter&amp;#10;The boundary between two network security zones through which traffic is routed."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; of the system. The technical competence of supervising individuals relates to the maintenance performed on the system, while having required access authorizations refers to maintenance on and near the system. Individuals who have not been previously identified as authorized maintenance personnel (e.g., manufacturers, consultants, systems integrators, and vendors) may require privileged access to the system, such as when they are required to conduct maintenance with little or no notice. Organizations may choose to issue temporary credentials to these individuals based on their risk assessments. Temporary credentials may be for one-time use or for very limited time periods.</t>
+    <t>Maintenance personnel refers to individuals who perform hardware or software maintenance on the system, while **Physical access authorizations 03.10.01** addresses physical access for individuals whose maintenance duties place them within the physical protection perimeter &lt;abbr title="Perimeter&amp;#10;The boundary between two network security zones through which traffic is routed."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; of the system. The technical competence of supervising individuals relates to the maintenance performed on the system, while having required access authorizations refers to maintenance on and near the system. Individuals who have not been previously identified as authorized maintenance personnel (e.g., manufacturers, consultants, systems integrators, and vendors) may require privileged access to the system, such as when they are required to conduct maintenance with little or no notice. Organizations may choose to issue temporary credentials to these individuals based on their risk assessments. Temporary credentials may be for one-time use or for very limited time periods.</t>
   </si>
   <si>
     <t>3.8</t>
@@ -3040,7 +3040,7 @@
     <t>Les supports du système comprennent les supports numériques et non numériques. Les supports numériques comprennent les disquettes, les disques à mémoire flash, les bandes magnétiques, les disques durs ou à entraînement magnétique externes ou amovibles, les disques compacts et les disques numériques polyvalents (DVD pour Digital Versatile Disc). Les supports non numériques incluent le papier et les microfilms. Le contrôle physique des supports stockés comprend la conduite d’inventaires, l’établissement de procédures afin de permettre aux personnes d’emprunter et de retourner des supports dans la bibliothèque et préserver la responsabilisation des supports stockés. Le stockage sécurisé comprend les tiroirs, les armoires et les bureaux verrouillés ainsi que les bibliothèques de supports contrôlées. Les zones contrôlées fournissent des contrôles physiques et procéduraux afin de répondre aux exigences établies pour la protection de l’information et des systèmes. Les techniques de nettoyage (par exemple, l’effacement, la destruction et la purge cryptographiques) préviennent la divulgation d’information désignée à des personnes non autorisées. Le processus de nettoyage retire l’information désignée des supports de façon à ce que l’information ne puisse pas être récupérée ou reconstruite.</t>
   </si>
   <si>
-    <t>System media includes digital and non-digital media. Digital media includes diskettes, flash drives, magnetic tapes, external or removable solid state or magnetic drives, compact discs, and digital versatile discs. Non-digital media includes paper and microfilm. Physically controlling stored media includes conducting inventories, establishing procedures to allow individuals to check out and return media to libraries, and maintaining accountability for stored media. Secure storage includes a locked drawer, desk, or cabinet or a controlled media library. Controlled areas provide physical and procedural controls to meet the requirements established for protecting information and systems. Sanitization techniques (e.g., cryptographically erasing, destroying, clearing &lt;abbr title="Clearing&amp;#10;Applying logical techniques to sanitize data in all user-addressable storage locations to protect against simple ways of recovering data. This is done by overwriting data with a new value, or if overwriting is not supported, by using a menu option to reset the device to factory settings."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt;, and purging) prevent the disclosure of specified information to unauthorized individuals. The sanitization process removes specified information from media such that the information cannot be retrieved or reconstructed.</t>
+    <t>System media includes digital and non-digital media. Digital media includes diskettes, flash drives, magnetic tapes, external or removable solid state or magnetic drives, compact discs, and digital versatile discs. Non-digital media includes paper and microfilm. Physically controlling stored media includes conducting inventories, establishing procedures to allow individuals to check out and return media to libraries, and maintaining accountability for stored media. Secure storage includes a locked drawer, desk, or cabinet or a controlled media library. Controlled areas provide physical and procedural controls to meet the requirements established for protecting information and systems. Sanitization techniques (e.g., cryptographically erasing, destroying, clearing &lt;abbr title="Clearing&amp;#10;Applying logical techniques to sanitize data in all user-addressable storage locations to protect against simple ways of recovering data. This is done by overwriting data with a new value, or if overwriting is not supported, by using a menu option to reset the device to factory settings."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt;, and purging) prevent the disclosure of specified information to unauthorized individuals. The sanitization process removes specified information from media such that the information cannot be retrieved or reconstructed.</t>
   </si>
   <si>
     <t>03.08.02</t>
@@ -3085,7 +3085,7 @@
     <t>Nettoyer les supports du système qui contiennent de l’information désignée avant leur élimination ou leur transfert hors du contrôle de l’organisation ou aux fins de réutilisation.</t>
   </si>
   <si>
-    <t>Sanitize &lt;abbr title="Sanitize&amp;#10;Sanitization is a process through which data is irreversibly removed from media. The storage media is left in a re-usable condition in accordance with IT security policy, but the data that was previously on it cannot be recovered or accessed."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; system media containing specified information prior to disposal, release out of organizational control, or release for reuse.</t>
+    <t>Sanitize &lt;abbr title="Sanitize&amp;#10;Sanitization is a process through which data is irreversibly removed from media. The storage media is left in a re-usable condition in accordance with IT security policy, but the data that was previously on it cannot be recovered or accessed."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; system media containing specified information prior to disposal, release out of organizational control, or release for reuse.</t>
   </si>
   <si>
     <t>03.08.03.disc</t>
@@ -3163,10 +3163,10 @@
     <t>03.08.05.disc</t>
   </si>
   <si>
-    <t>Les supports du système comprennent les supports numériques et non numériques. Les supports numériques incluent les disquettes, les disques à mémoire flash, les bandes magnétiques, les disques durs ou à entraînement magnétique externes ou amovibles, les disques compacts et les DVD. Les supports non numériques incluent le papier et les microfilms. Les zones contrôlées sont des espaces dans lesquels les organisations appliquent des mesures physiques ou procédurales afin de respecter les exigences établies pour la protection de l’information désignée et des systèmes. La protection des supports durant le transport peut comprendre la cryptographie &lt;abbr title="Cryptographie&amp;#10;Étude des techniques permettant de chiffrer l’information pour la rendre inintelligible ou de rendre lisible une information chiffrée."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; et/ou des contenants verrouillés. Les activités associées au transport des supports comprennent la remise des supports aux fins de transport, la vérification que les supports suivent les processus de transport adéquats et le transport en tant que tel. Le personnel autorisé responsable du transport et de la messagerie peut inclure des personnes de l’extérieur de l’organisation. Préserver la responsabilisation des supports durant le transport comprend la restriction des activités de transport au personnel autorisé et le suivi ou l’obtention des enregistrements officiels des activités de transport, à mesure que les supports se déplacent dans le système de transport, afin de prévenir et de détecter les pertes, les destructions ou les modifications. Cette exigence est associée aux exigences **Confidentialité lors de la transmission et du stockage 03.13.08** et **Protection cryptographique 03.13.11**.</t>
-  </si>
-  <si>
-    <t>System media includes digital and non-digital media. Digital media includes flash drives, diskettes, magnetic tapes, external or removable solid state or magnetic drives, compact discs, and digital versatile discs. Non-digital media includes microfilm and paper. Controlled areas are spaces for which organizations provide physical or procedural measures to meet the requirements established for protecting specified information and systems. Media protection during transport can include cryptography &lt;abbr title="Cryptography&amp;#10;The study of techniques used to make plain information unreadable, as well as to convert it back to a readable form."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; and/or locked containers. Activities associated with media transport include releasing media for transport, ensuring that media enter the appropriate transport processes, and the actual transport. Authorized transport and courier personnel may include individuals external to the organization. Maintaining accountability of media during transport includes restricting transport activities to authorized personnel and tracking or obtaining records of transport activities as the media move through the transportation system to prevent and detect loss, destruction, or tampering. This requirement is related to **Transmission and storage confidentiality 03.13.08** and **Cryptographic protection 03.13.11**.</t>
+    <t>Les supports du système comprennent les supports numériques et non numériques. Les supports numériques incluent les disquettes, les disques à mémoire flash, les bandes magnétiques, les disques durs ou à entraînement magnétique externes ou amovibles, les disques compacts et les DVD. Les supports non numériques incluent le papier et les microfilms. Les zones contrôlées sont des espaces dans lesquels les organisations appliquent des mesures physiques ou procédurales afin de respecter les exigences établies pour la protection de l’information désignée et des systèmes. La protection des supports durant le transport peut comprendre la cryptographie &lt;abbr title="Cryptographie&amp;#10;Étude des techniques permettant de chiffrer l’information pour la rendre inintelligible ou de rendre lisible une information chiffrée."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; et/ou des contenants verrouillés. Les activités associées au transport des supports comprennent la remise des supports aux fins de transport, la vérification que les supports suivent les processus de transport adéquats et le transport en tant que tel. Le personnel autorisé responsable du transport et de la messagerie peut inclure des personnes de l’extérieur de l’organisation. Préserver la responsabilisation des supports durant le transport comprend la restriction des activités de transport au personnel autorisé et le suivi ou l’obtention des enregistrements officiels des activités de transport, à mesure que les supports se déplacent dans le système de transport, afin de prévenir et de détecter les pertes, les destructions ou les modifications. Cette exigence est associée aux exigences **Confidentialité lors de la transmission et du stockage 03.13.08** et **Protection cryptographique 03.13.11**.</t>
+  </si>
+  <si>
+    <t>System media includes digital and non-digital media. Digital media includes flash drives, diskettes, magnetic tapes, external or removable solid state or magnetic drives, compact discs, and digital versatile discs. Non-digital media includes microfilm and paper. Controlled areas are spaces for which organizations provide physical or procedural measures to meet the requirements established for protecting specified information and systems. Media protection during transport can include cryptography &lt;abbr title="Cryptography&amp;#10;The study of techniques used to make plain information unreadable, as well as to convert it back to a readable form."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; and/or locked containers. Activities associated with media transport include releasing media for transport, ensuring that media enter the appropriate transport processes, and the actual transport. Authorized transport and courier personnel may include individuals external to the organization. Maintaining accountability of media during transport includes restricting transport activities to authorized personnel and tracking or obtaining records of transport activities as the media move through the transportation system to prevent and detect loss, destruction, or tampering. This requirement is related to **Transmission and storage confidentiality 03.13.08** and **Cryptographic protection 03.13.11**.</t>
   </si>
   <si>
     <t>03.08.07</t>
@@ -3937,11 +3937,11 @@
   </si>
   <si>
     <t>L’échange d’information s’applique aux échanges d’information entre deux ou plusieurs systèmes de l’organisation ou à l’extérieur de l’organisation. Les organisations doivent considérer les risques associés aux menaces nouvelles ou grandissantes qui peuvent être introduites lorsque les systèmes échangent de l’information avec d’autres systèmes qui peuvent avoir des exigences ou des stratégies de sécurité différentes. Les types d’ententes doivent être sélectionnés en fonction de facteurs comme la relation entre les organisations qui échangent de l’information (par exemple, d’un organisme gouvernemental à un autre, d’un organisme gouvernemental à une entreprise, d’une entreprise à une autre, d’un organisme gouvernemental ou d’une entreprise à un fournisseur de services, d’un organisme gouvernemental ou d’une entreprise à personne) et le niveau d’accès au système organisationnel par les utilisatrices et utilisateurs de l’autre système. Les types d’ententes peuvent inclure des ententes sur la sécurité de l’échange d’information, des ententes sur la sécurité des interconnexions, des ententes ou protocoles d’entente, des ententes sur l’échange d’information, des accords sur les niveaux de service ou d’autres types d’ententes.
-Les organisations peuvent intégrer l’information des ententes dans des contrats officiels, en particulier pour les échanges d’information entre des ministères et organismes fédéraux et des organisations non fédérales (par exemple, des prestataires de services, des entrepreneures et entrepreneurs, des développeuses et développeurs de systèmes et des intégratrices et intégrateurs de systèmes). Les renseignements qui se trouvent dans les ententes d’échange incluent les caractéristiques d’interface &lt;abbr title="Interface&amp;#10;Frontière où transitent les communications entre deux systèmes. Il peut s’agir d’un connecteur matériel utilisé pour la connexion à d’autres dispositifs ou d’une convention permettant d’établir des communications entre deux systèmes logiciels."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt;, les exigences de sécurité et de protection de la vie privée, les contrôles et les responsabilités pour chaque système.</t>
+Les organisations peuvent intégrer l’information des ententes dans des contrats officiels, en particulier pour les échanges d’information entre des ministères et organismes fédéraux et des organisations non fédérales (par exemple, des prestataires de services, des entrepreneures et entrepreneurs, des développeuses et développeurs de systèmes et des intégratrices et intégrateurs de systèmes). Les renseignements qui se trouvent dans les ententes d’échange incluent les caractéristiques d’interface &lt;abbr title="Interface&amp;#10;Frontière où transitent les communications entre deux systèmes. Il peut s’agir d’un connecteur matériel utilisé pour la connexion à d’autres dispositifs ou d’une convention permettant d’établir des communications entre deux systèmes logiciels."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt;, les exigences de sécurité et de protection de la vie privée, les contrôles et les responsabilités pour chaque système.</t>
   </si>
   <si>
     <t>Information exchange applies to information exchanges between two or more systems, both internal and external to the organization. Organizations consider the risks related to new or increased threats that may be introduced when systems exchange information with other systems that may have different security requirements or policies. The types of agreements selected are based on factors such as the relationship between the organizations exchanging information (e.g., government to government, government to business, business to business, government or business to service provider, government or business to individual) and the level of access to the organizational system by users of the other system. The types of agreements can include information exchange security agreements, interconnection security agreements, memoranda of understanding or agreement, information sharing arrangements, service-level agreements, or other types of agreements.
-Organizations may incorporate agreement information into formal contracts, especially for information exchanges established between federal departments and agencies and non-federal organizations (e.g., service providers, contractors, system developers, and system integrators). The types of information contained in exchange agreements include the interface &lt;abbr title="Interface&amp;#10;A boundary across which two systems communicate. An interface might be a hardware connector used to link to other devices, or it might be a convention used to allow communication between two software systems."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; characteristics, security and privacy requirements, controls, and responsibilities for each system.</t>
+Organizations may incorporate agreement information into formal contracts, especially for information exchanges established between federal departments and agencies and non-federal organizations (e.g., service providers, contractors, system developers, and system integrators). The types of information contained in exchange agreements include the interface &lt;abbr title="Interface&amp;#10;A boundary across which two systems communicate. An interface might be a hardware connector used to link to other devices, or it might be a convention used to allow communication between two software systems."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; characteristics, security and privacy requirements, controls, and responsibilities for each system.</t>
   </si>
   <si>
     <t>3.13</t>
@@ -3998,7 +3998,7 @@
     <t>03.13.01.disc</t>
   </si>
   <si>
-    <t>Les interfaces gérées incluent les passerelles, les routeurs, les pare-feu, les analyseurs réseau de code malveillant, les systèmes de virtualisation et les tunnels chiffrés mis en œuvre au sein d’une architecture de sécurité. Les sous-réseaux qui sont séparés physiquement ou logiquement des réseaux internes sont appelés communément des zones démilitarisées (ZD) ou DMZ &lt;abbr title="DMZ&amp;#10;Voir Zone démilitarisée."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; (pour Demilitarized Zones). La restriction ou l’interdiction d’interfaces au sein des systèmes organisationnels comprend la restriction du trafic Web externe vers les serveurs Web désignés dans des interfaces gérées et l’interdiction de la mystification d’adresses (internes et externes) pour les protocoles franchissant le périmètre.</t>
+    <t>Les interfaces gérées incluent les passerelles, les routeurs, les pare-feu, les analyseurs réseau de code malveillant, les systèmes de virtualisation et les tunnels chiffrés mis en œuvre au sein d’une architecture de sécurité. Les sous-réseaux qui sont séparés physiquement ou logiquement des réseaux internes sont appelés communément des zones démilitarisées (ZD) ou DMZ &lt;abbr title="DMZ&amp;#10;Voir Zone démilitarisée."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; (pour Demilitarized Zones). La restriction ou l’interdiction d’interfaces au sein des systèmes organisationnels comprend la restriction du trafic Web externe vers les serveurs Web désignés dans des interfaces gérées et l’interdiction de la mystification d’adresses (internes et externes) pour les protocoles franchissant le périmètre.</t>
   </si>
   <si>
     <t>Managed interfaces include gateways, routers, firewalls, network-based malicious code analysis, virtualization systems, and encrypted tunnels implemented within a security architecture. Subnetworks that are either physically or logically separated from internal networks are referred to as demilitarized zones or DMZs. Restricting or prohibiting interfaces within organizational systems includes restricting external web traffic to designated web servers within managed interfaces, prohibiting both internal and external address spoofing for protocols crossing the boundary.</t>
@@ -4127,7 +4127,7 @@
     <t>Établir et gérer les clés cryptographiques dans le système conformément aux exigences de gestion de clés suivantes : [Affectation : exigences définies par l’organisation liées à la génération, à la distribution, au stockage, à l’accès et à la destruction des clés].</t>
   </si>
   <si>
-    <t>Establish and manage cryptographic keys in the system in accordance with the following key management &lt;abbr title="Key management&amp;#10;The procedures and mechanisms for generating, disseminating, replacing, storing, archiving, and destroying cryptographic keys."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; requirements: [Assignment: organization-defined requirements for key generation, distribution, storage, access, and destruction].</t>
+    <t>Establish and manage cryptographic keys in the system in accordance with the following key management &lt;abbr title="Key management&amp;#10;The procedures and mechanisms for generating, disseminating, replacing, storing, archiving, and destroying cryptographic keys."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; requirements: [Assignment: organization-defined requirements for key generation, distribution, storage, access, and destruction].</t>
   </si>
   <si>
     <t>03.13.10.disc</t>
@@ -4232,7 +4232,7 @@
     <t>03.13.13.disc</t>
   </si>
   <si>
-    <t>Le code mobile comprend des programmes informatiques ou des parties de programme obtenus de systèmes distants, transmis sur un réseau et exécutés sur un système local sans installation explicite ou exécution par la ou le destinataire. Les décisions concernant l’utilisation de code mobile reposent sur le degré de possibilité qu’une utilisation malveillante du code cause des dommages au système. Les technologies de code mobile incluent les applets Java, JavaScript, HTML5, VBScript et WebGL. Les restrictions d’utilisation et les lignes directrices sur la mise en œuvre s’appliquent à la sélection et à l’utilisation de code mobile installé sur les serveurs ainsi que le code mobile téléchargé et exécuté sur les postes de travail et les appareils individuels, y compris les ordinateurs blocs-notes, les téléphones intelligents et les dispositifs intelligents. Les politiques et procédures liées au code mobile concernent les mesures prises afin d’empêcher le développement, l’acquisition et l’utilisation de code mobile non acceptable au sein du système, y compris exiger la signature numérique &lt;abbr title="Signature numérique&amp;#10;Mécanisme cryptographique employé pour vérifier l&amp;#x27;authenticité et l&amp;#x27;intégrité d&amp;#x27;un article (p. ex. un document, un logiciel)."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; du code mobile par une source de confiance.</t>
+    <t>Le code mobile comprend des programmes informatiques ou des parties de programme obtenus de systèmes distants, transmis sur un réseau et exécutés sur un système local sans installation explicite ou exécution par la ou le destinataire. Les décisions concernant l’utilisation de code mobile reposent sur le degré de possibilité qu’une utilisation malveillante du code cause des dommages au système. Les technologies de code mobile incluent les applets Java, JavaScript, HTML5, VBScript et WebGL. Les restrictions d’utilisation et les lignes directrices sur la mise en œuvre s’appliquent à la sélection et à l’utilisation de code mobile installé sur les serveurs ainsi que le code mobile téléchargé et exécuté sur les postes de travail et les appareils individuels, y compris les ordinateurs blocs-notes, les téléphones intelligents et les dispositifs intelligents. Les politiques et procédures liées au code mobile concernent les mesures prises afin d’empêcher le développement, l’acquisition et l’utilisation de code mobile non acceptable au sein du système, y compris exiger la signature numérique &lt;abbr title="Signature numérique&amp;#10;Mécanisme cryptographique employé pour vérifier l&amp;#x27;authenticité et l&amp;#x27;intégrité d&amp;#x27;un article (p. ex. un document, un logiciel)."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; du code mobile par une source de confiance.</t>
   </si>
   <si>
     <t>Mobile code includes software programs or parts of programs that are obtained from remote systems, transmitted across a network, and executed on a local system without explicit installation or execution by the recipient. Decisions regarding the use of mobile code are based on the potential for the code to cause damage to the system if used maliciously. Mobile code technologies include Java applets, JavaScript, HTML5, VBScript, and WebGL. Usage restrictions and implementation guidelines apply to the selection and use of mobile code installed on servers and mobile code downloaded and executed on individual workstations and devices, including notebook computers, smart phones, and smart devices. Mobile code policies and procedures address the actions taken to prevent the development, acquisition, and use of unacceptable mobile code within the system, including requiring mobile code to be digitally signed by a trusted source.</t>
@@ -4310,7 +4310,7 @@
     <t>03.14.01.disc</t>
   </si>
   <si>
-    <t>Les organisations doivent établir les systèmes qui sont touchés par les défauts logiciels et micrologiciels, y compris les vulnérabilités qui découlent de ces défauts, et signaler cette information au personnel responsable de la sécurité de l’information et de la protection de la vie privée. Les mises à jour liées à la sécurité incluent les correctifs, les ensembles de modifications provisoires, les correctifs d’urgence et les signatures de logiciel antivirus &lt;abbr title="Logiciel antivirus&amp;#10;Logiciel qui protège contre les virus, les chevaux de Troie, les vers et les logiciels espions. Le logiciel anti-virus procède à l&amp;#x27;analyse des fichiers afin d&amp;#x27;identifier des programmes qui sont ou pourraient être malveillants. L&amp;#x27;analyse permet d&amp;#x27;identifier : les virus connus, les virus auparavant inconnus et les fichiers suspects."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt;. Les organisations doivent corriger les défauts découverts au cours des évaluations de sécurité, de la surveillance continue, des activités d’intervention en cas d’incident et du traitement des erreurs du système. Les organisations peuvent tirer parti des ressources offertes (par exemple, les bases de données CWE ou CVE) pour corriger les défauts des systèmes. Les périodes définies par l’organisation pour la mise à jour de sécurité des logiciels et des micrologiciels peuvent varier en fonction de divers facteurs, notamment la criticité de la mise à jour (c’est-à-dire la gravité de la vulnérabilité associée à la faille découverte). Certains types de correctifs peuvent nécessiter plus de mises à l’essai que d’autres.</t>
+    <t>Les organisations doivent établir les systèmes qui sont touchés par les défauts logiciels et micrologiciels, y compris les vulnérabilités qui découlent de ces défauts, et signaler cette information au personnel responsable de la sécurité de l’information et de la protection de la vie privée. Les mises à jour liées à la sécurité incluent les correctifs, les ensembles de modifications provisoires, les correctifs d’urgence et les signatures de logiciel antivirus &lt;abbr title="Logiciel antivirus&amp;#10;Logiciel qui protège contre les virus, les chevaux de Troie, les vers et les logiciels espions. Le logiciel anti-virus procède à l&amp;#x27;analyse des fichiers afin d&amp;#x27;identifier des programmes qui sont ou pourraient être malveillants. L&amp;#x27;analyse permet d&amp;#x27;identifier : les virus connus, les virus auparavant inconnus et les fichiers suspects."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt;. Les organisations doivent corriger les défauts découverts au cours des évaluations de sécurité, de la surveillance continue, des activités d’intervention en cas d’incident et du traitement des erreurs du système. Les organisations peuvent tirer parti des ressources offertes (par exemple, les bases de données CWE ou CVE) pour corriger les défauts des systèmes. Les périodes définies par l’organisation pour la mise à jour de sécurité des logiciels et des micrologiciels peuvent varier en fonction de divers facteurs, notamment la criticité de la mise à jour (c’est-à-dire la gravité de la vulnérabilité associée à la faille découverte). Certains types de correctifs peuvent nécessiter plus de mises à l’essai que d’autres.</t>
   </si>
   <si>
     <t>Organizations identify systems that are affected by announced software and firmware flaws, including potential vulnerabilities that result from those flaws, and report this information to designated personnel with information security and privacy responsibilities. Security-relevant updates include patches, service packs, hot fixes, and anti-virus signatures. Organizations address the flaws discovered during security assessments, continuous monitoring, incident response activities, and system error handling. Organizations can take advantage of available resources (e.g., &lt;abbr title="Common Weakness Enumeration"&gt;CWE&lt;/abbr&gt; or &lt;abbr title="Common Vulnerabilities and Exposures"&gt;CVE&lt;/abbr&gt; databases) when remediating system flaws. Organization-defined time periods for updating security-relevant software and firmware may vary based on a variety of factors, including the criticality of the update (i.e., severity of the vulnerability related to the discovered flaw). Some types of flaw remediation may require more testing than other types.</t>
@@ -4373,13 +4373,13 @@
     <t>03.14.02.disc</t>
   </si>
   <si>
-    <t>Les insertions de code malveillant surviennent lors de l’exploitation de vulnérabilités du système. Le code malveillant peut être inséré dans le système de différentes façons, y compris par courriel, par Internet et par des dispositifs de stockage portatifs. Le code malveillant comprend les virus &lt;abbr title="Virus&amp;#10;Programme informatique qui se propage en se copiant par lui-même. Les virus informatiques se propagent d’un ordinateur à l’autre, souvent à l’insu de l’utilisateur, et causent des dommages de toutes sortes. Ils peuvent faire afficher des messages irritants, voler des données ou même permettre à d’autres utilisateurs de prendre le contrôle de l’ordinateur infecté."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt;, les vers, les chevaux de Troie et les logiciels espions. Le code malveillant peut être encodé sous différents formats, contenu dans des fichiers compressés ou cachés, ou encore dissimulé dans des fichiers en utilisant des techniques comme la stéganographie. Le code malveillant peut être présent dans des logiciels commerciaux sur étagère et dans des logiciels conçus sur mesure et peut comprendre des bombes logiques, des portes dérobées et d’autres types d’attaques qui peuvent affecter la mission et les activités de l’organisation. Des analyses périodiques du système et des balayages en temps réel des fichiers provenant de sources externes lorsqu’ils sont téléchargés, ouverts ou exécutés peuvent faciliter la détection de code malveillant. Les mécanismes de protection contre les programmes malveillants peuvent également surveiller les systèmes afin de détecter les comportements anormaux ou inattendus et prendre les mesures appropriées.
-Ces mécanismes comprennent des technologies axées ou non sur les signatures. Les mécanismes de détection qui ne sont pas axés sur les signatures intègrent des techniques d’intelligence artificielle &lt;abbr title="Intelligence artificielle&amp;#10;Sous-domaine de l&amp;#x27;informatique ayant trait au développement de programmes informatiques aptes à résoudre des problèmes, à apprendre, à comprendre des langages, à interpréter des scènes visuelles, bref, à se comporter de façon à reproduire les facultés cognitives de l&amp;#x27;intelligence humaine."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; (IA) qui utilisent des heuristiques afin de détecter, d’analyser et de décrire les caractéristiques ou les comportements des programmes malveillants. Ils fournissent également des contrôles contre de tels programmes malveillants pour lesquels il n’existe pas encore de signature ou de telles signatures s’avèrent inefficaces. Les cas où les signatures sont inexistantes ou inefficaces incluent les programmes malveillants polymorphiques (c’est-à-dire le code pour lequel les signatures sont modifiées lors de la réplication). Les mécanismes qui ne sont pas axés sur les signatures incluent les technologies basées sur la réputation. Une gestion omniprésente des configurations, des logiciels anti-exploitation et des contrôles d’intégrité logicielle peuvent également être efficaces pour empêcher l’exécution de code non autorisé.
+    <t>Les insertions de code malveillant surviennent lors de l’exploitation de vulnérabilités du système. Le code malveillant peut être inséré dans le système de différentes façons, y compris par courriel, par Internet et par des dispositifs de stockage portatifs. Le code malveillant comprend les virus &lt;abbr title="Virus&amp;#10;Programme informatique qui se propage en se copiant par lui-même. Les virus informatiques se propagent d’un ordinateur à l’autre, souvent à l’insu de l’utilisateur, et causent des dommages de toutes sortes. Ils peuvent faire afficher des messages irritants, voler des données ou même permettre à d’autres utilisateurs de prendre le contrôle de l’ordinateur infecté."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt;, les vers, les chevaux de Troie et les logiciels espions. Le code malveillant peut être encodé sous différents formats, contenu dans des fichiers compressés ou cachés, ou encore dissimulé dans des fichiers en utilisant des techniques comme la stéganographie. Le code malveillant peut être présent dans des logiciels commerciaux sur étagère et dans des logiciels conçus sur mesure et peut comprendre des bombes logiques, des portes dérobées et d’autres types d’attaques qui peuvent affecter la mission et les activités de l’organisation. Des analyses périodiques du système et des balayages en temps réel des fichiers provenant de sources externes lorsqu’ils sont téléchargés, ouverts ou exécutés peuvent faciliter la détection de code malveillant. Les mécanismes de protection contre les programmes malveillants peuvent également surveiller les systèmes afin de détecter les comportements anormaux ou inattendus et prendre les mesures appropriées.
+Ces mécanismes comprennent des technologies axées ou non sur les signatures. Les mécanismes de détection qui ne sont pas axés sur les signatures intègrent des techniques d’intelligence artificielle &lt;abbr title="Intelligence artificielle&amp;#10;Sous-domaine de l&amp;#x27;informatique ayant trait au développement de programmes informatiques aptes à résoudre des problèmes, à apprendre, à comprendre des langages, à interpréter des scènes visuelles, bref, à se comporter de façon à reproduire les facultés cognitives de l&amp;#x27;intelligence humaine."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; (IA) qui utilisent des heuristiques afin de détecter, d’analyser et de décrire les caractéristiques ou les comportements des programmes malveillants. Ils fournissent également des contrôles contre de tels programmes malveillants pour lesquels il n’existe pas encore de signature ou de telles signatures s’avèrent inefficaces. Les cas où les signatures sont inexistantes ou inefficaces incluent les programmes malveillants polymorphiques (c’est-à-dire le code pour lequel les signatures sont modifiées lors de la réplication). Les mécanismes qui ne sont pas axés sur les signatures incluent les technologies basées sur la réputation. Une gestion omniprésente des configurations, des logiciels anti-exploitation et des contrôles d’intégrité logicielle peuvent également être efficaces pour empêcher l’exécution de code non autorisé.
 S’il n’est pas possible de détecter le code malveillant à l’aide de méthodes ou de technologies de détection, les organisations peuvent miser sur des pratiques de codage sécurisées, le contrôle et la gestion des configurations, des processus d’approvisionnement de confiance et des pratiques de suivi pour veiller à ce que les logiciels n’exécutent que les fonctions prévues. Les organisations peuvent déterminer que d’autres mesures s’imposent en réponse à une détection de code malveillant. Par exemple, les organisations peuvent définir des mesures à prendre en réponse à une détection de code malveillant au cours d’analyses, de téléchargements malveillants ou d’activités malveillantes associés à une tentative d’ouverture ou d’exécution de fichier.</t>
   </si>
   <si>
-    <t>Malicious code insertions occur through the exploitation of system vulnerabilities. Malicious code can be inserted into the system in a variety of ways, including email, the Internet, and portable storage devices. Malicious code includes viruses, worms, Trojan &lt;abbr title="Trojan&amp;#10;A malicious program that is disguised as or embedded within legitimate software."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; horses, and spyware. Malicious code can be encoded in various formats, contained in compressed or hidden files, or hidden in files using techniques such as steganography. Malicious code may be present in commercial off-the-shelf software and custom-built software and could include logic bombs, backdoors, and other types of attacks that could affect organizational mission and business functions. Periodic scans of the system and real-time scans of files from external sources as files are downloaded, opened, or executed can detect malicious code. Malicious code protection mechanisms can also monitor systems for anomalous or unexpected behaviours and take appropriate actions.
-Malicious code protection mechanisms include signature- and non-signature-based technologies. Non-signature-based detection mechanisms include artificial intelligence &lt;abbr title="Artificial intelligence&amp;#10;A subfield of computer science that develops intelligent computer programs to behave in a way that would be considered intelligent if observed in a human (e.g. solve problems, learn from experience, understand language, interpret visual scenes)."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; (AI) techniques that use heuristics to detect, analyze, and describe the characteristics or behaviour of malicious code. They also provide controls against such code for which signatures do not yet exist or for which existing signatures may not be effective. Malicious code for which active signatures do not yet exist or may be ineffective includes polymorphic malicious code (i.e., code that changes signatures when it replicates). Non-signature-based mechanisms include reputation-based technologies. Pervasive configuration management, anti-exploitation software, and software integrity controls may also be effective in preventing unauthorized code execution.
+    <t>Malicious code insertions occur through the exploitation of system vulnerabilities. Malicious code can be inserted into the system in a variety of ways, including email, the Internet, and portable storage devices. Malicious code includes viruses, worms, Trojan &lt;abbr title="Trojan&amp;#10;A malicious program that is disguised as or embedded within legitimate software."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; horses, and spyware. Malicious code can be encoded in various formats, contained in compressed or hidden files, or hidden in files using techniques such as steganography. Malicious code may be present in commercial off-the-shelf software and custom-built software and could include logic bombs, backdoors, and other types of attacks that could affect organizational mission and business functions. Periodic scans of the system and real-time scans of files from external sources as files are downloaded, opened, or executed can detect malicious code. Malicious code protection mechanisms can also monitor systems for anomalous or unexpected behaviours and take appropriate actions.
+Malicious code protection mechanisms include signature- and non-signature-based technologies. Non-signature-based detection mechanisms include artificial intelligence &lt;abbr title="Artificial intelligence&amp;#10;A subfield of computer science that develops intelligent computer programs to behave in a way that would be considered intelligent if observed in a human (e.g. solve problems, learn from experience, understand language, interpret visual scenes)."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; (AI) techniques that use heuristics to detect, analyze, and describe the characteristics or behaviour of malicious code. They also provide controls against such code for which signatures do not yet exist or for which existing signatures may not be effective. Malicious code for which active signatures do not yet exist or may be ineffective includes polymorphic malicious code (i.e., code that changes signatures when it replicates). Non-signature-based mechanisms include reputation-based technologies. Pervasive configuration management, anti-exploitation software, and software integrity controls may also be effective in preventing unauthorized code execution.
 If malicious code cannot be detected by detection methods or technologies, organizations can rely on secure coding practices, configuration management and control, trusted procurement processes, and monitoring practices to help ensure that the software only performs intended functions. Organizations may determine that different actions are warranted in response to the detection of malicious code. For example, organizations can define actions to be taken in response to the detection of malicious code during scans, malicious downloads, or malicious activity when attempting to open or execute files.</t>
   </si>
   <si>
@@ -4552,7 +4552,7 @@
   </si>
   <si>
     <t>Un poste de travail administratif dédié est typiquement constitué d’un terminal d’utilisateur et d’une très petite sélection de logiciels conçus pour interfacer avec le système cible. Aux fins du présent contrôle, un poste de travail est un système à partir duquel les tâches d’administration sont réalisées, par opposition au système cible. Le poste de travail administratif dédié doit être renforcé pour le rôle afin de réduire la probabilité qu’un point d’extrémité de superutilisateur ou d’administrateur soit compromis par un auteur de menace (ce qui entraînerait logiquement la compromission du système cible). Les outils bureautiques typiques ne sont pas nécessaires sur le poste de travail administratif dédié. Toutes les applications et tous les services non essentiels doivent être supprimés. Les postes de travail administratifs dédiés n’ont pas de jonction de domaine, ne peuvent pas télécharger de correctif à partir d’Internet et ne peuvent pas mettre à jour la documentation dans les applications en réseau.
-Le retrait de l’accès Internet public des postes de travail administratifs réduit considérablement les risques de compromission. Les passerelles RPV &lt;abbr title="RPV&amp;#10;Voir Réseau privé virtuel."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; exposées à Internet ne sont pas privilégiées pour les activités d’administration à distance. Les opérateurs privés offrent une meilleure protection, mais nécessitent tout de même un chiffrement de RPV au sein de réseau. Le poste de travail administratif dédié ne doit pas devenir un moyen de déplacement latéral entre les domaines de sécurité.</t>
+Le retrait de l’accès Internet public des postes de travail administratifs réduit considérablement les risques de compromission. Les passerelles RPV &lt;abbr title="RPV&amp;#10;Voir Réseau privé virtuel."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; exposées à Internet ne sont pas privilégiées pour les activités d’administration à distance. Les opérateurs privés offrent une meilleure protection, mais nécessitent tout de même un chiffrement de RPV au sein de réseau. Le poste de travail administratif dédié ne doit pas devenir un moyen de déplacement latéral entre les domaines de sécurité.</t>
   </si>
   <si>
     <t>A dedicated administration workstation (DAW) is typically comprised of a user terminal with a very small selection of software designed for interfacing with the target system. For the purpose of this control, workstation means the system from which you are performing the administration, as opposed to the target system of administration. The &lt;abbr title="dedicated administration workstation"&gt;DAW&lt;/abbr&gt; must be hardened for the role, in order to minimize the likelihood that a superuser’s or administrator’s endpoint may be compromised by any threat actor (which would logically lead to the compromise of the target system). Typical office productivity tools are not required on the &lt;abbr title="dedicated administration workstation"&gt;DAW&lt;/abbr&gt;. All non-essential applications and services are removed. &lt;abbr title="dedicated administration workstation"&gt;DAW&lt;/abbr&gt;s are not domain-joined, cannot download patches from the internet, and cannot update documentation in networked applications.
@@ -4989,7 +4989,7 @@
     <t>03.17.02.disc</t>
   </si>
   <si>
-    <t>Les processus d’acquisition fournissent un véhicule important pour la protection de la chaîne d’approvisionnement. Il existe de nombreux outils et de nombreuses techniques, y compris le masquage de l’utilisation finale d’un système ou d’un composant système, l’achat à l’aveugle, l’exigence d’un emballage protégé contre les modifications ou l’utilisation d’une distribution de confiance ou contrôlée. Les résultats d’une évaluation des risques liés à la chaîne d’approvisionnement peuvent informer le choix des stratégies, des outils et des méthodes qui conventionnent le mieux à la situation. Les outils et les techniques peuvent fournir une protection contre la production non autorisée, le vol, la modification, la contrefaçon, l’insertion de code malveillant ou de porte dérobée &lt;abbr title="Porte dérobée&amp;#10;Moyen non recensé qui permet, discrètement ou anonymement, d&amp;#x27;accéder à distance à un ordinateur après avoir contourné les mécanismes d&amp;#x27;authentification et s&amp;#x27;être donné accès au texte en clair."&gt;&lt;sup class="fa-solid fa-circle-question"&gt;&lt;/sup&gt;&lt;/abbr&gt; et les mauvaises pratiques de développement tout au long du cycle de vie du système.
+    <t>Les processus d’acquisition fournissent un véhicule important pour la protection de la chaîne d’approvisionnement. Il existe de nombreux outils et de nombreuses techniques, y compris le masquage de l’utilisation finale d’un système ou d’un composant système, l’achat à l’aveugle, l’exigence d’un emballage protégé contre les modifications ou l’utilisation d’une distribution de confiance ou contrôlée. Les résultats d’une évaluation des risques liés à la chaîne d’approvisionnement peuvent informer le choix des stratégies, des outils et des méthodes qui conventionnent le mieux à la situation. Les outils et les techniques peuvent fournir une protection contre la production non autorisée, le vol, la modification, la contrefaçon, l’insertion de code malveillant ou de porte dérobée &lt;abbr title="Porte dérobée&amp;#10;Moyen non recensé qui permet, discrètement ou anonymement, d&amp;#x27;accéder à distance à un ordinateur après avoir contourné les mécanismes d&amp;#x27;authentification et s&amp;#x27;être donné accès au texte en clair."&gt;&lt;sup&gt;(?)&lt;/sup&gt;&lt;/abbr&gt; et les mauvaises pratiques de développement tout au long du cycle de vie du système.
 Les organisations peuvent également penser à offrir des mesures incitatives pour les fournisseurs afin de mettre en œuvre des contrôles et de favoriser la transparence des processus et des pratiques de sécurité. Elles peuvent également fournir un libellé de contrat qui traite de l’interdiction d’utiliser des composants contaminés ou contrefaits et restreindre les achats des fournisseurs qui ne sont pas dignes de confiance. Les organisations doivent considérer fournir des programmes de formation et de sensibilisation pour le personnel concernant les risques liés à la chaîne d’approvisionnement, les stratégies d’atténuation disponibles et les circonstances appropriées pour utiliser les programmes. Les méthodes pour examiner et protéger les plans de développement, la documentation et les preuves doivent être appropriées selon les exigences de sécurité de l’organisation. Les contrats peuvent également indiquer les exigences concernant la protection des documents.</t>
   </si>
   <si>
@@ -5086,16 +5086,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5401,16 +5395,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="112.109375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5418,7 +5408,7 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -5426,7 +5416,7 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5434,7 +5424,7 @@
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -5442,7 +5432,7 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5450,23 +5440,23 @@
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="216" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -5474,7 +5464,7 @@
       <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5482,7 +5472,7 @@
       <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5490,23 +5480,23 @@
       <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>25</v>
       </c>
     </row>
@@ -5514,7 +5504,7 @@
       <c r="A14" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5527,16 +5517,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="171.21875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>28</v>
       </c>
     </row>
@@ -5544,7 +5530,7 @@
       <c r="A2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5552,7 +5538,7 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5560,7 +5546,7 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5568,15 +5554,15 @@
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="144" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5584,15 +5570,15 @@
       <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>23</v>
       </c>
     </row>
@@ -5605,15 +5591,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J507"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="4" width="51.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="121.5546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="71.77734375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="47.21875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="116.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="95.6640625" style="2" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -5625,217 +5602,217 @@
       <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>61</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" t="s">
         <v>62</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>66</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" t="s">
         <v>71</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" t="s">
         <v>77</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>80</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>81</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" t="s">
         <v>82</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" t="s">
         <v>83</v>
       </c>
     </row>
@@ -5846,10 +5823,10 @@
       <c r="C11" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" t="s">
         <v>86</v>
       </c>
     </row>
@@ -5863,14 +5840,14 @@
       <c r="C12" t="s">
         <v>88</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" t="s">
         <v>89</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -5880,10 +5857,10 @@
       <c r="C13" t="s">
         <v>91</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" t="s">
         <v>92</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" t="s">
         <v>93</v>
       </c>
     </row>
@@ -5894,10 +5871,10 @@
       <c r="C14" t="s">
         <v>94</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" t="s">
         <v>95</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" t="s">
         <v>96</v>
       </c>
       <c r="J14" t="s">
@@ -5914,10 +5891,10 @@
       <c r="C15" t="s">
         <v>97</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" t="s">
         <v>98</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5931,10 +5908,10 @@
       <c r="C16" t="s">
         <v>100</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" t="s">
         <v>101</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" t="s">
         <v>102</v>
       </c>
     </row>
@@ -5948,10 +5925,10 @@
       <c r="C17" t="s">
         <v>103</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" t="s">
         <v>104</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5962,10 +5939,10 @@
       <c r="C18" t="s">
         <v>106</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" t="s">
         <v>107</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" t="s">
         <v>108</v>
       </c>
       <c r="J18" t="s">
@@ -5982,10 +5959,10 @@
       <c r="C19" t="s">
         <v>109</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" t="s">
         <v>110</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" t="s">
         <v>111</v>
       </c>
     </row>
@@ -5999,10 +5976,10 @@
       <c r="C20" t="s">
         <v>112</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" t="s">
         <v>113</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" t="s">
         <v>114</v>
       </c>
     </row>
@@ -6016,10 +5993,10 @@
       <c r="C21" t="s">
         <v>115</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" t="s">
         <v>116</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" t="s">
         <v>117</v>
       </c>
     </row>
@@ -6030,10 +6007,10 @@
       <c r="C22" t="s">
         <v>118</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" t="s">
         <v>119</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" t="s">
         <v>120</v>
       </c>
       <c r="J22" t="s">
@@ -6050,10 +6027,10 @@
       <c r="C23" t="s">
         <v>121</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" t="s">
         <v>122</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" t="s">
         <v>123</v>
       </c>
     </row>
@@ -6067,10 +6044,10 @@
       <c r="C24" t="s">
         <v>124</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" t="s">
         <v>125</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" t="s">
         <v>126</v>
       </c>
     </row>
@@ -6084,10 +6061,10 @@
       <c r="C25" t="s">
         <v>127</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" t="s">
         <v>128</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" t="s">
         <v>129</v>
       </c>
     </row>
@@ -6101,10 +6078,10 @@
       <c r="C26" t="s">
         <v>130</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" t="s">
         <v>131</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" t="s">
         <v>132</v>
       </c>
     </row>
@@ -6118,10 +6095,10 @@
       <c r="C27" t="s">
         <v>133</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" t="s">
         <v>134</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" t="s">
         <v>135</v>
       </c>
     </row>
@@ -6132,10 +6109,10 @@
       <c r="C28" t="s">
         <v>136</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" t="s">
         <v>137</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" t="s">
         <v>138</v>
       </c>
       <c r="J28" t="s">
@@ -6152,10 +6129,10 @@
       <c r="C29" t="s">
         <v>139</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" t="s">
         <v>140</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" t="s">
         <v>141</v>
       </c>
     </row>
@@ -6169,10 +6146,10 @@
       <c r="C30" t="s">
         <v>142</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" t="s">
         <v>143</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" t="s">
         <v>144</v>
       </c>
     </row>
@@ -6186,14 +6163,14 @@
       <c r="C31" t="s">
         <v>145</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" t="s">
         <v>146</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H31" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -6203,30 +6180,30 @@
       <c r="C32" t="s">
         <v>148</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" t="s">
         <v>149</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>4</v>
       </c>
       <c r="C33" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="D33" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" t="s">
         <v>153</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H33" s="2" t="s">
+      <c r="G33" t="s">
+        <v>152</v>
+      </c>
+      <c r="H33" t="s">
         <v>154</v>
       </c>
     </row>
@@ -6237,14 +6214,14 @@
       <c r="C34" t="s">
         <v>155</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" t="s">
         <v>156</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>87</v>
       </c>
@@ -6254,30 +6231,30 @@
       <c r="C35" t="s">
         <v>158</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" t="s">
         <v>159</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>4</v>
       </c>
       <c r="C36" t="s">
         <v>161</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E36" s="2" t="s">
+      <c r="D36" t="s">
+        <v>152</v>
+      </c>
+      <c r="E36" t="s">
         <v>162</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H36" s="2" t="s">
+      <c r="G36" t="s">
+        <v>152</v>
+      </c>
+      <c r="H36" t="s">
         <v>163</v>
       </c>
     </row>
@@ -6288,10 +6265,10 @@
       <c r="C37" t="s">
         <v>164</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" t="s">
         <v>165</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" t="s">
         <v>166</v>
       </c>
     </row>
@@ -6305,30 +6282,30 @@
       <c r="C38" t="s">
         <v>167</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" t="s">
         <v>168</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H38" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="360" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>4</v>
       </c>
       <c r="C39" t="s">
         <v>170</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E39" s="2" t="s">
+      <c r="D39" t="s">
+        <v>152</v>
+      </c>
+      <c r="E39" t="s">
         <v>171</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H39" s="2" t="s">
+      <c r="G39" t="s">
+        <v>152</v>
+      </c>
+      <c r="H39" t="s">
         <v>172</v>
       </c>
     </row>
@@ -6339,10 +6316,10 @@
       <c r="C40" t="s">
         <v>173</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" t="s">
         <v>174</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" t="s">
         <v>175</v>
       </c>
     </row>
@@ -6356,10 +6333,10 @@
       <c r="C41" t="s">
         <v>176</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" t="s">
         <v>177</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="H41" t="s">
         <v>178</v>
       </c>
     </row>
@@ -6373,30 +6350,30 @@
       <c r="C42" t="s">
         <v>179</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" t="s">
         <v>180</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="H42" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>4</v>
       </c>
       <c r="C43" t="s">
         <v>182</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E43" s="2" t="s">
+      <c r="D43" t="s">
+        <v>152</v>
+      </c>
+      <c r="E43" t="s">
         <v>183</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H43" s="2" t="s">
+      <c r="G43" t="s">
+        <v>152</v>
+      </c>
+      <c r="H43" t="s">
         <v>184</v>
       </c>
     </row>
@@ -6407,14 +6384,14 @@
       <c r="C44" t="s">
         <v>185</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" t="s">
         <v>186</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>87</v>
       </c>
@@ -6424,14 +6401,14 @@
       <c r="C45" t="s">
         <v>188</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" t="s">
         <v>189</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="H45" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>87</v>
       </c>
@@ -6441,14 +6418,14 @@
       <c r="C46" t="s">
         <v>191</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" t="s">
         <v>192</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="H46" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>87</v>
       </c>
@@ -6458,10 +6435,10 @@
       <c r="C47" t="s">
         <v>194</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" t="s">
         <v>195</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="H47" t="s">
         <v>196</v>
       </c>
     </row>
@@ -6475,30 +6452,30 @@
       <c r="C48" t="s">
         <v>197</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" t="s">
         <v>198</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="H48" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>4</v>
       </c>
       <c r="C49" t="s">
         <v>200</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E49" s="2" t="s">
+      <c r="D49" t="s">
+        <v>152</v>
+      </c>
+      <c r="E49" t="s">
         <v>201</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H49" s="2" t="s">
+      <c r="G49" t="s">
+        <v>152</v>
+      </c>
+      <c r="H49" t="s">
         <v>202</v>
       </c>
     </row>
@@ -6509,10 +6486,10 @@
       <c r="C50" t="s">
         <v>203</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" t="s">
         <v>204</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" t="s">
         <v>205</v>
       </c>
     </row>
@@ -6526,14 +6503,14 @@
       <c r="C51" t="s">
         <v>206</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" t="s">
         <v>207</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="H51" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>87</v>
       </c>
@@ -6543,14 +6520,14 @@
       <c r="C52" t="s">
         <v>209</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" t="s">
         <v>210</v>
       </c>
-      <c r="H52" s="2" t="s">
+      <c r="H52" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>87</v>
       </c>
@@ -6560,30 +6537,30 @@
       <c r="C53" t="s">
         <v>212</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" t="s">
         <v>213</v>
       </c>
-      <c r="H53" s="2" t="s">
+      <c r="H53" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>4</v>
       </c>
       <c r="C54" t="s">
         <v>215</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E54" s="2" t="s">
+      <c r="D54" t="s">
+        <v>152</v>
+      </c>
+      <c r="E54" t="s">
         <v>216</v>
       </c>
-      <c r="G54" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H54" s="2" t="s">
+      <c r="G54" t="s">
+        <v>152</v>
+      </c>
+      <c r="H54" t="s">
         <v>217</v>
       </c>
     </row>
@@ -6594,10 +6571,10 @@
       <c r="C55" t="s">
         <v>218</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" t="s">
         <v>219</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" t="s">
         <v>220</v>
       </c>
     </row>
@@ -6611,10 +6588,10 @@
       <c r="C56" t="s">
         <v>221</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" t="s">
         <v>222</v>
       </c>
-      <c r="H56" s="2" t="s">
+      <c r="H56" t="s">
         <v>223</v>
       </c>
     </row>
@@ -6628,30 +6605,30 @@
       <c r="C57" t="s">
         <v>224</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" t="s">
         <v>225</v>
       </c>
-      <c r="H57" s="2" t="s">
+      <c r="H57" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>4</v>
       </c>
       <c r="C58" t="s">
         <v>227</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="D58" t="s">
+        <v>152</v>
+      </c>
+      <c r="E58" t="s">
         <v>228</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H58" s="2" t="s">
+      <c r="G58" t="s">
+        <v>152</v>
+      </c>
+      <c r="H58" t="s">
         <v>229</v>
       </c>
     </row>
@@ -6662,14 +6639,14 @@
       <c r="C59" t="s">
         <v>230</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" t="s">
         <v>231</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>87</v>
       </c>
@@ -6679,14 +6656,14 @@
       <c r="C60" t="s">
         <v>233</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E60" t="s">
         <v>234</v>
       </c>
-      <c r="H60" s="2" t="s">
+      <c r="H60" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -6696,30 +6673,30 @@
       <c r="C61" t="s">
         <v>236</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" t="s">
         <v>237</v>
       </c>
-      <c r="H61" s="2" t="s">
+      <c r="H61" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>4</v>
       </c>
       <c r="C62" t="s">
         <v>239</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E62" s="2" t="s">
+      <c r="D62" t="s">
+        <v>152</v>
+      </c>
+      <c r="E62" t="s">
         <v>240</v>
       </c>
-      <c r="G62" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H62" s="2" t="s">
+      <c r="G62" t="s">
+        <v>152</v>
+      </c>
+      <c r="H62" t="s">
         <v>241</v>
       </c>
     </row>
@@ -6730,14 +6707,14 @@
       <c r="C63" t="s">
         <v>242</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" t="s">
         <v>243</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>87</v>
       </c>
@@ -6747,30 +6724,30 @@
       <c r="C64" t="s">
         <v>245</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="E64" t="s">
         <v>246</v>
       </c>
-      <c r="H64" s="2" t="s">
+      <c r="H64" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>4</v>
       </c>
       <c r="C65" t="s">
         <v>248</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E65" s="2" t="s">
+      <c r="D65" t="s">
+        <v>152</v>
+      </c>
+      <c r="E65" t="s">
         <v>249</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H65" s="2" t="s">
+      <c r="G65" t="s">
+        <v>152</v>
+      </c>
+      <c r="H65" t="s">
         <v>250</v>
       </c>
     </row>
@@ -6781,14 +6758,14 @@
       <c r="C66" t="s">
         <v>251</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D66" t="s">
         <v>252</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G66" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>87</v>
       </c>
@@ -6798,14 +6775,14 @@
       <c r="C67" t="s">
         <v>254</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="E67" t="s">
         <v>255</v>
       </c>
-      <c r="H67" s="2" t="s">
+      <c r="H67" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>87</v>
       </c>
@@ -6815,10 +6792,10 @@
       <c r="C68" t="s">
         <v>257</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="E68" t="s">
         <v>258</v>
       </c>
-      <c r="H68" s="2" t="s">
+      <c r="H68" t="s">
         <v>259</v>
       </c>
     </row>
@@ -6832,30 +6809,30 @@
       <c r="C69" t="s">
         <v>260</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="E69" t="s">
         <v>261</v>
       </c>
-      <c r="H69" s="2" t="s">
+      <c r="H69" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>4</v>
       </c>
       <c r="C70" t="s">
         <v>263</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E70" s="2" t="s">
+      <c r="D70" t="s">
+        <v>152</v>
+      </c>
+      <c r="E70" t="s">
         <v>264</v>
       </c>
-      <c r="G70" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H70" s="2" t="s">
+      <c r="G70" t="s">
+        <v>152</v>
+      </c>
+      <c r="H70" t="s">
         <v>265</v>
       </c>
     </row>
@@ -6866,14 +6843,14 @@
       <c r="C71" t="s">
         <v>266</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D71" t="s">
         <v>267</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="G71" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>87</v>
       </c>
@@ -6883,30 +6860,30 @@
       <c r="C72" t="s">
         <v>269</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="E72" t="s">
         <v>270</v>
       </c>
-      <c r="H72" s="2" t="s">
+      <c r="H72" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>4</v>
       </c>
       <c r="C73" t="s">
         <v>272</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E73" s="2" t="s">
+      <c r="D73" t="s">
+        <v>152</v>
+      </c>
+      <c r="E73" t="s">
         <v>273</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H73" s="2" t="s">
+      <c r="G73" t="s">
+        <v>152</v>
+      </c>
+      <c r="H73" t="s">
         <v>274</v>
       </c>
     </row>
@@ -6917,14 +6894,14 @@
       <c r="C74" t="s">
         <v>275</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D74" t="s">
         <v>276</v>
       </c>
-      <c r="G74" s="2" t="s">
+      <c r="G74" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>87</v>
       </c>
@@ -6934,10 +6911,10 @@
       <c r="C75" t="s">
         <v>278</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="E75" t="s">
         <v>279</v>
       </c>
-      <c r="H75" s="2" t="s">
+      <c r="H75" t="s">
         <v>280</v>
       </c>
     </row>
@@ -6951,10 +6928,10 @@
       <c r="C76" t="s">
         <v>281</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="E76" t="s">
         <v>282</v>
       </c>
-      <c r="H76" s="2" t="s">
+      <c r="H76" t="s">
         <v>283</v>
       </c>
     </row>
@@ -6968,10 +6945,10 @@
       <c r="C77" t="s">
         <v>284</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="E77" t="s">
         <v>285</v>
       </c>
-      <c r="H77" s="2" t="s">
+      <c r="H77" t="s">
         <v>286</v>
       </c>
     </row>
@@ -6985,30 +6962,30 @@
       <c r="C78" t="s">
         <v>287</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="E78" t="s">
         <v>288</v>
       </c>
-      <c r="H78" s="2" t="s">
+      <c r="H78" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>4</v>
       </c>
       <c r="C79" t="s">
         <v>290</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E79" s="2" t="s">
+      <c r="D79" t="s">
+        <v>152</v>
+      </c>
+      <c r="E79" t="s">
         <v>291</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H79" s="2" t="s">
+      <c r="G79" t="s">
+        <v>152</v>
+      </c>
+      <c r="H79" t="s">
         <v>292</v>
       </c>
     </row>
@@ -7019,14 +6996,14 @@
       <c r="C80" t="s">
         <v>293</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D80" t="s">
         <v>294</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G80" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>87</v>
       </c>
@@ -7036,10 +7013,10 @@
       <c r="C81" t="s">
         <v>296</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="E81" t="s">
         <v>297</v>
       </c>
-      <c r="H81" s="2" t="s">
+      <c r="H81" t="s">
         <v>298</v>
       </c>
     </row>
@@ -7053,10 +7030,10 @@
       <c r="C82" t="s">
         <v>299</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="E82" t="s">
         <v>300</v>
       </c>
-      <c r="H82" s="2" t="s">
+      <c r="H82" t="s">
         <v>301</v>
       </c>
     </row>
@@ -7070,10 +7047,10 @@
       <c r="C83" t="s">
         <v>302</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="E83" t="s">
         <v>303</v>
       </c>
-      <c r="H83" s="2" t="s">
+      <c r="H83" t="s">
         <v>304</v>
       </c>
     </row>
@@ -7087,30 +7064,30 @@
       <c r="C84" t="s">
         <v>305</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="E84" t="s">
         <v>306</v>
       </c>
-      <c r="H84" s="2" t="s">
+      <c r="H84" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>4</v>
       </c>
       <c r="C85" t="s">
         <v>308</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E85" s="2" t="s">
+      <c r="D85" t="s">
+        <v>152</v>
+      </c>
+      <c r="E85" t="s">
         <v>309</v>
       </c>
-      <c r="G85" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H85" s="2" t="s">
+      <c r="G85" t="s">
+        <v>152</v>
+      </c>
+      <c r="H85" t="s">
         <v>310</v>
       </c>
     </row>
@@ -7121,10 +7098,10 @@
       <c r="C86" t="s">
         <v>311</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D86" t="s">
         <v>312</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G86" t="s">
         <v>313</v>
       </c>
     </row>
@@ -7138,10 +7115,10 @@
       <c r="C87" t="s">
         <v>314</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="E87" t="s">
         <v>315</v>
       </c>
-      <c r="H87" s="2" t="s">
+      <c r="H87" t="s">
         <v>316</v>
       </c>
     </row>
@@ -7155,14 +7132,14 @@
       <c r="C88" t="s">
         <v>317</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="E88" t="s">
         <v>318</v>
       </c>
-      <c r="H88" s="2" t="s">
+      <c r="H88" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>87</v>
       </c>
@@ -7172,30 +7149,30 @@
       <c r="C89" t="s">
         <v>320</v>
       </c>
-      <c r="E89" s="2" t="s">
+      <c r="E89" t="s">
         <v>321</v>
       </c>
-      <c r="H89" s="2" t="s">
+      <c r="H89" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>4</v>
       </c>
       <c r="C90" t="s">
         <v>323</v>
       </c>
-      <c r="D90" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E90" s="2" t="s">
+      <c r="D90" t="s">
+        <v>152</v>
+      </c>
+      <c r="E90" t="s">
         <v>324</v>
       </c>
-      <c r="G90" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H90" s="2" t="s">
+      <c r="G90" t="s">
+        <v>152</v>
+      </c>
+      <c r="H90" t="s">
         <v>325</v>
       </c>
     </row>
@@ -7206,10 +7183,10 @@
       <c r="C91" t="s">
         <v>326</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D91" t="s">
         <v>327</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G91" t="s">
         <v>328</v>
       </c>
     </row>
@@ -7223,14 +7200,14 @@
       <c r="C92" t="s">
         <v>329</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="E92" t="s">
         <v>330</v>
       </c>
-      <c r="H92" s="2" t="s">
+      <c r="H92" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>87</v>
       </c>
@@ -7240,31 +7217,31 @@
       <c r="C93" t="s">
         <v>332</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="E93" t="s">
         <v>333</v>
       </c>
-      <c r="H93" s="2" t="s">
+      <c r="H93" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>4</v>
       </c>
       <c r="C94" t="s">
         <v>335</v>
       </c>
-      <c r="E94" s="2" t="s">
+      <c r="E94" t="s">
         <v>336</v>
       </c>
-      <c r="H94" s="2" t="s">
+      <c r="H94" t="s">
         <v>337</v>
       </c>
       <c r="J94" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>87</v>
       </c>
@@ -7274,14 +7251,14 @@
       <c r="C95" t="s">
         <v>338</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="E95" t="s">
         <v>339</v>
       </c>
-      <c r="H95" s="2" t="s">
+      <c r="H95" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>87</v>
       </c>
@@ -7291,10 +7268,10 @@
       <c r="C96" t="s">
         <v>341</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="E96" t="s">
         <v>342</v>
       </c>
-      <c r="H96" s="2" t="s">
+      <c r="H96" t="s">
         <v>343</v>
       </c>
     </row>
@@ -7308,30 +7285,30 @@
       <c r="C97" t="s">
         <v>344</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="E97" t="s">
         <v>345</v>
       </c>
-      <c r="H97" s="2" t="s">
+      <c r="H97" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B98">
         <v>4</v>
       </c>
       <c r="C98" t="s">
         <v>347</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E98" s="2" t="s">
+      <c r="D98" t="s">
+        <v>152</v>
+      </c>
+      <c r="E98" t="s">
         <v>348</v>
       </c>
-      <c r="G98" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H98" s="2" t="s">
+      <c r="G98" t="s">
+        <v>152</v>
+      </c>
+      <c r="H98" t="s">
         <v>349</v>
       </c>
     </row>
@@ -7342,10 +7319,10 @@
       <c r="C99" t="s">
         <v>350</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="D99" t="s">
         <v>351</v>
       </c>
-      <c r="G99" s="2" t="s">
+      <c r="G99" t="s">
         <v>352</v>
       </c>
     </row>
@@ -7359,14 +7336,14 @@
       <c r="C100" t="s">
         <v>353</v>
       </c>
-      <c r="E100" s="2" t="s">
+      <c r="E100" t="s">
         <v>354</v>
       </c>
-      <c r="H100" s="2" t="s">
+      <c r="H100" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>87</v>
       </c>
@@ -7376,30 +7353,30 @@
       <c r="C101" t="s">
         <v>356</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="E101" t="s">
         <v>357</v>
       </c>
-      <c r="H101" s="2" t="s">
+      <c r="H101" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B102">
         <v>4</v>
       </c>
       <c r="C102" t="s">
         <v>359</v>
       </c>
-      <c r="D102" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E102" s="2" t="s">
+      <c r="D102" t="s">
+        <v>152</v>
+      </c>
+      <c r="E102" t="s">
         <v>360</v>
       </c>
-      <c r="G102" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H102" s="2" t="s">
+      <c r="G102" t="s">
+        <v>152</v>
+      </c>
+      <c r="H102" t="s">
         <v>361</v>
       </c>
     </row>
@@ -7410,16 +7387,16 @@
       <c r="C103" t="s">
         <v>362</v>
       </c>
-      <c r="D103" s="2" t="s">
+      <c r="D103" t="s">
         <v>363</v>
       </c>
-      <c r="E103" s="2" t="s">
+      <c r="E103" t="s">
         <v>364</v>
       </c>
-      <c r="G103" s="2" t="s">
+      <c r="G103" t="s">
         <v>365</v>
       </c>
-      <c r="H103" s="2" t="s">
+      <c r="H103" t="s">
         <v>366</v>
       </c>
     </row>
@@ -7430,10 +7407,10 @@
       <c r="C104" t="s">
         <v>367</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D104" t="s">
         <v>368</v>
       </c>
-      <c r="G104" s="2" t="s">
+      <c r="G104" t="s">
         <v>369</v>
       </c>
     </row>
@@ -7444,17 +7421,17 @@
       <c r="C105" t="s">
         <v>370</v>
       </c>
-      <c r="E105" s="2" t="s">
+      <c r="E105" t="s">
         <v>371</v>
       </c>
-      <c r="H105" s="2" t="s">
+      <c r="H105" t="s">
         <v>372</v>
       </c>
       <c r="J105" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>87</v>
       </c>
@@ -7464,10 +7441,10 @@
       <c r="C106" t="s">
         <v>373</v>
       </c>
-      <c r="E106" s="2" t="s">
+      <c r="E106" t="s">
         <v>374</v>
       </c>
-      <c r="H106" s="2" t="s">
+      <c r="H106" t="s">
         <v>375</v>
       </c>
     </row>
@@ -7481,10 +7458,10 @@
       <c r="C107" t="s">
         <v>376</v>
       </c>
-      <c r="E107" s="2" t="s">
+      <c r="E107" t="s">
         <v>377</v>
       </c>
-      <c r="H107" s="2" t="s">
+      <c r="H107" t="s">
         <v>378</v>
       </c>
     </row>
@@ -7498,14 +7475,14 @@
       <c r="C108" t="s">
         <v>379</v>
       </c>
-      <c r="E108" s="2" t="s">
+      <c r="E108" t="s">
         <v>380</v>
       </c>
-      <c r="H108" s="2" t="s">
+      <c r="H108" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>87</v>
       </c>
@@ -7515,30 +7492,30 @@
       <c r="C109" t="s">
         <v>382</v>
       </c>
-      <c r="E109" s="2" t="s">
+      <c r="E109" t="s">
         <v>383</v>
       </c>
-      <c r="H109" s="2" t="s">
+      <c r="H109" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B110">
         <v>4</v>
       </c>
       <c r="C110" t="s">
         <v>385</v>
       </c>
-      <c r="D110" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E110" s="2" t="s">
+      <c r="D110" t="s">
+        <v>152</v>
+      </c>
+      <c r="E110" t="s">
         <v>386</v>
       </c>
-      <c r="G110" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H110" s="2" t="s">
+      <c r="G110" t="s">
+        <v>152</v>
+      </c>
+      <c r="H110" t="s">
         <v>387</v>
       </c>
     </row>
@@ -7549,10 +7526,10 @@
       <c r="C111" t="s">
         <v>388</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="D111" t="s">
         <v>389</v>
       </c>
-      <c r="G111" s="2" t="s">
+      <c r="G111" t="s">
         <v>390</v>
       </c>
     </row>
@@ -7563,17 +7540,17 @@
       <c r="C112" t="s">
         <v>391</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="E112" t="s">
         <v>392</v>
       </c>
-      <c r="H112" s="2" t="s">
+      <c r="H112" t="s">
         <v>393</v>
       </c>
       <c r="J112" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>87</v>
       </c>
@@ -7583,10 +7560,10 @@
       <c r="C113" t="s">
         <v>394</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="E113" t="s">
         <v>395</v>
       </c>
-      <c r="H113" s="2" t="s">
+      <c r="H113" t="s">
         <v>396</v>
       </c>
     </row>
@@ -7600,14 +7577,14 @@
       <c r="C114" t="s">
         <v>397</v>
       </c>
-      <c r="E114" s="2" t="s">
+      <c r="E114" t="s">
         <v>398</v>
       </c>
-      <c r="H114" s="2" t="s">
+      <c r="H114" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>87</v>
       </c>
@@ -7617,50 +7594,50 @@
       <c r="C115" t="s">
         <v>399</v>
       </c>
-      <c r="E115" s="2" t="s">
+      <c r="E115" t="s">
         <v>400</v>
       </c>
-      <c r="H115" s="2" t="s">
+      <c r="H115" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B116">
         <v>4</v>
       </c>
       <c r="C116" t="s">
         <v>402</v>
       </c>
-      <c r="D116" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E116" s="2" t="s">
+      <c r="D116" t="s">
+        <v>152</v>
+      </c>
+      <c r="E116" t="s">
         <v>403</v>
       </c>
-      <c r="G116" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H116" s="2" t="s">
+      <c r="G116" t="s">
+        <v>152</v>
+      </c>
+      <c r="H116" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B117">
         <v>2</v>
       </c>
       <c r="C117" t="s">
         <v>405</v>
       </c>
-      <c r="D117" s="2" t="s">
+      <c r="D117" t="s">
         <v>406</v>
       </c>
-      <c r="E117" s="2" t="s">
+      <c r="E117" t="s">
         <v>407</v>
       </c>
-      <c r="G117" s="2" t="s">
+      <c r="G117" t="s">
         <v>408</v>
       </c>
-      <c r="H117" s="2" t="s">
+      <c r="H117" t="s">
         <v>409</v>
       </c>
     </row>
@@ -7671,14 +7648,14 @@
       <c r="C118" t="s">
         <v>410</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D118" t="s">
         <v>411</v>
       </c>
-      <c r="G118" s="2" t="s">
+      <c r="G118" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>87</v>
       </c>
@@ -7688,10 +7665,10 @@
       <c r="C119" t="s">
         <v>413</v>
       </c>
-      <c r="E119" s="2" t="s">
+      <c r="E119" t="s">
         <v>414</v>
       </c>
-      <c r="H119" s="2" t="s">
+      <c r="H119" t="s">
         <v>415</v>
       </c>
     </row>
@@ -7705,30 +7682,30 @@
       <c r="C120" t="s">
         <v>416</v>
       </c>
-      <c r="E120" s="2" t="s">
+      <c r="E120" t="s">
         <v>417</v>
       </c>
-      <c r="H120" s="2" t="s">
+      <c r="H120" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B121">
         <v>4</v>
       </c>
       <c r="C121" t="s">
         <v>419</v>
       </c>
-      <c r="D121" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E121" s="2" t="s">
+      <c r="D121" t="s">
+        <v>152</v>
+      </c>
+      <c r="E121" t="s">
         <v>420</v>
       </c>
-      <c r="G121" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H121" s="2" t="s">
+      <c r="G121" t="s">
+        <v>152</v>
+      </c>
+      <c r="H121" t="s">
         <v>421</v>
       </c>
     </row>
@@ -7739,10 +7716,10 @@
       <c r="C122" t="s">
         <v>422</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="D122" t="s">
         <v>423</v>
       </c>
-      <c r="G122" s="2" t="s">
+      <c r="G122" t="s">
         <v>424</v>
       </c>
     </row>
@@ -7753,10 +7730,10 @@
       <c r="C123" t="s">
         <v>425</v>
       </c>
-      <c r="E123" s="2" t="s">
+      <c r="E123" t="s">
         <v>426</v>
       </c>
-      <c r="H123" s="2" t="s">
+      <c r="H123" t="s">
         <v>427</v>
       </c>
       <c r="J123" t="s">
@@ -7773,10 +7750,10 @@
       <c r="C124" t="s">
         <v>428</v>
       </c>
-      <c r="E124" s="2" t="s">
+      <c r="E124" t="s">
         <v>429</v>
       </c>
-      <c r="H124" s="2" t="s">
+      <c r="H124" t="s">
         <v>430</v>
       </c>
     </row>
@@ -7790,10 +7767,10 @@
       <c r="C125" t="s">
         <v>431</v>
       </c>
-      <c r="E125" s="2" t="s">
+      <c r="E125" t="s">
         <v>432</v>
       </c>
-      <c r="H125" s="2" t="s">
+      <c r="H125" t="s">
         <v>433</v>
       </c>
     </row>
@@ -7807,10 +7784,10 @@
       <c r="C126" t="s">
         <v>434</v>
       </c>
-      <c r="E126" s="2" t="s">
+      <c r="E126" t="s">
         <v>435</v>
       </c>
-      <c r="H126" s="2" t="s">
+      <c r="H126" t="s">
         <v>436</v>
       </c>
     </row>
@@ -7824,10 +7801,10 @@
       <c r="C127" t="s">
         <v>437</v>
       </c>
-      <c r="E127" s="2" t="s">
+      <c r="E127" t="s">
         <v>438</v>
       </c>
-      <c r="H127" s="2" t="s">
+      <c r="H127" t="s">
         <v>439</v>
       </c>
     </row>
@@ -7841,10 +7818,10 @@
       <c r="C128" t="s">
         <v>440</v>
       </c>
-      <c r="E128" s="2" t="s">
+      <c r="E128" t="s">
         <v>441</v>
       </c>
-      <c r="H128" s="2" t="s">
+      <c r="H128" t="s">
         <v>442</v>
       </c>
     </row>
@@ -7858,10 +7835,10 @@
       <c r="C129" t="s">
         <v>443</v>
       </c>
-      <c r="E129" s="2" t="s">
+      <c r="E129" t="s">
         <v>444</v>
       </c>
-      <c r="H129" s="2" t="s">
+      <c r="H129" t="s">
         <v>445</v>
       </c>
     </row>
@@ -7875,30 +7852,30 @@
       <c r="C130" t="s">
         <v>446</v>
       </c>
-      <c r="E130" s="2" t="s">
+      <c r="E130" t="s">
         <v>447</v>
       </c>
-      <c r="H130" s="2" t="s">
+      <c r="H130" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B131">
         <v>4</v>
       </c>
       <c r="C131" t="s">
         <v>449</v>
       </c>
-      <c r="D131" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E131" s="2" t="s">
+      <c r="D131" t="s">
+        <v>152</v>
+      </c>
+      <c r="E131" t="s">
         <v>450</v>
       </c>
-      <c r="G131" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H131" s="2" t="s">
+      <c r="G131" t="s">
+        <v>152</v>
+      </c>
+      <c r="H131" t="s">
         <v>451</v>
       </c>
     </row>
@@ -7909,14 +7886,14 @@
       <c r="C132" t="s">
         <v>452</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="D132" t="s">
         <v>453</v>
       </c>
-      <c r="G132" s="2" t="s">
+      <c r="G132" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>87</v>
       </c>
@@ -7926,10 +7903,10 @@
       <c r="C133" t="s">
         <v>455</v>
       </c>
-      <c r="E133" s="2" t="s">
+      <c r="E133" t="s">
         <v>456</v>
       </c>
-      <c r="H133" s="2" t="s">
+      <c r="H133" t="s">
         <v>457</v>
       </c>
     </row>
@@ -7943,48 +7920,48 @@
       <c r="C134" t="s">
         <v>458</v>
       </c>
-      <c r="E134" s="2" t="s">
+      <c r="E134" t="s">
         <v>459</v>
       </c>
-      <c r="H134" s="2" t="s">
+      <c r="H134" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B135">
         <v>4</v>
       </c>
       <c r="C135" t="s">
         <v>461</v>
       </c>
-      <c r="D135" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E135" s="2" t="s">
+      <c r="D135" t="s">
+        <v>152</v>
+      </c>
+      <c r="E135" t="s">
         <v>462</v>
       </c>
-      <c r="G135" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H135" s="2" t="s">
+      <c r="G135" t="s">
+        <v>152</v>
+      </c>
+      <c r="H135" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B136">
         <v>3</v>
       </c>
       <c r="C136" t="s">
         <v>464</v>
       </c>
-      <c r="D136" s="2" t="s">
+      <c r="D136" t="s">
         <v>465</v>
       </c>
-      <c r="G136" s="2" t="s">
+      <c r="G136" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>87</v>
       </c>
@@ -7994,10 +7971,10 @@
       <c r="C137" t="s">
         <v>467</v>
       </c>
-      <c r="E137" s="2" t="s">
+      <c r="E137" t="s">
         <v>468</v>
       </c>
-      <c r="H137" s="2" t="s">
+      <c r="H137" t="s">
         <v>469</v>
       </c>
     </row>
@@ -8011,48 +7988,48 @@
       <c r="C138" t="s">
         <v>470</v>
       </c>
-      <c r="E138" s="2" t="s">
+      <c r="E138" t="s">
         <v>471</v>
       </c>
-      <c r="H138" s="2" t="s">
+      <c r="H138" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B139">
         <v>4</v>
       </c>
       <c r="C139" t="s">
         <v>473</v>
       </c>
-      <c r="D139" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E139" s="2" t="s">
+      <c r="D139" t="s">
+        <v>152</v>
+      </c>
+      <c r="E139" t="s">
         <v>474</v>
       </c>
-      <c r="G139" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H139" s="2" t="s">
+      <c r="G139" t="s">
+        <v>152</v>
+      </c>
+      <c r="H139" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B140">
         <v>3</v>
       </c>
       <c r="C140" t="s">
         <v>476</v>
       </c>
-      <c r="D140" s="2" t="s">
+      <c r="D140" t="s">
         <v>477</v>
       </c>
-      <c r="G140" s="2" t="s">
+      <c r="G140" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>87</v>
       </c>
@@ -8062,10 +8039,10 @@
       <c r="C141" t="s">
         <v>479</v>
       </c>
-      <c r="E141" s="2" t="s">
+      <c r="E141" t="s">
         <v>480</v>
       </c>
-      <c r="H141" s="2" t="s">
+      <c r="H141" t="s">
         <v>481</v>
       </c>
     </row>
@@ -8079,14 +8056,14 @@
       <c r="C142" t="s">
         <v>482</v>
       </c>
-      <c r="E142" s="2" t="s">
+      <c r="E142" t="s">
         <v>483</v>
       </c>
-      <c r="H142" s="2" t="s">
+      <c r="H142" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>87</v>
       </c>
@@ -8096,48 +8073,48 @@
       <c r="C143" t="s">
         <v>485</v>
       </c>
-      <c r="E143" s="2" t="s">
+      <c r="E143" t="s">
         <v>486</v>
       </c>
-      <c r="H143" s="2" t="s">
+      <c r="H143" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B144">
         <v>4</v>
       </c>
       <c r="C144" t="s">
         <v>488</v>
       </c>
-      <c r="D144" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E144" s="2" t="s">
+      <c r="D144" t="s">
+        <v>152</v>
+      </c>
+      <c r="E144" t="s">
         <v>489</v>
       </c>
-      <c r="G144" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H144" s="2" t="s">
+      <c r="G144" t="s">
+        <v>152</v>
+      </c>
+      <c r="H144" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B145">
         <v>3</v>
       </c>
       <c r="C145" t="s">
         <v>491</v>
       </c>
-      <c r="D145" s="2" t="s">
+      <c r="D145" t="s">
         <v>492</v>
       </c>
-      <c r="G145" s="2" t="s">
+      <c r="G145" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>87</v>
       </c>
@@ -8147,10 +8124,10 @@
       <c r="C146" t="s">
         <v>494</v>
       </c>
-      <c r="E146" s="2" t="s">
+      <c r="E146" t="s">
         <v>495</v>
       </c>
-      <c r="H146" s="2" t="s">
+      <c r="H146" t="s">
         <v>496</v>
       </c>
     </row>
@@ -8164,30 +8141,30 @@
       <c r="C147" t="s">
         <v>497</v>
       </c>
-      <c r="E147" s="2" t="s">
+      <c r="E147" t="s">
         <v>498</v>
       </c>
-      <c r="H147" s="2" t="s">
+      <c r="H147" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B148">
         <v>4</v>
       </c>
       <c r="C148" t="s">
         <v>500</v>
       </c>
-      <c r="D148" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E148" s="2" t="s">
+      <c r="D148" t="s">
+        <v>152</v>
+      </c>
+      <c r="E148" t="s">
         <v>501</v>
       </c>
-      <c r="G148" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H148" s="2" t="s">
+      <c r="G148" t="s">
+        <v>152</v>
+      </c>
+      <c r="H148" t="s">
         <v>502</v>
       </c>
     </row>
@@ -8198,10 +8175,10 @@
       <c r="C149" t="s">
         <v>503</v>
       </c>
-      <c r="D149" s="2" t="s">
+      <c r="D149" t="s">
         <v>504</v>
       </c>
-      <c r="G149" s="2" t="s">
+      <c r="G149" t="s">
         <v>505</v>
       </c>
     </row>
@@ -8215,14 +8192,14 @@
       <c r="C150" t="s">
         <v>506</v>
       </c>
-      <c r="E150" s="2" t="s">
+      <c r="E150" t="s">
         <v>507</v>
       </c>
-      <c r="H150" s="2" t="s">
+      <c r="H150" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>87</v>
       </c>
@@ -8232,30 +8209,30 @@
       <c r="C151" t="s">
         <v>509</v>
       </c>
-      <c r="E151" s="2" t="s">
+      <c r="E151" t="s">
         <v>510</v>
       </c>
-      <c r="H151" s="2" t="s">
+      <c r="H151" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B152">
         <v>4</v>
       </c>
       <c r="C152" t="s">
         <v>512</v>
       </c>
-      <c r="D152" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E152" s="2" t="s">
+      <c r="D152" t="s">
+        <v>152</v>
+      </c>
+      <c r="E152" t="s">
         <v>513</v>
       </c>
-      <c r="G152" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H152" s="2" t="s">
+      <c r="G152" t="s">
+        <v>152</v>
+      </c>
+      <c r="H152" t="s">
         <v>514</v>
       </c>
     </row>
@@ -8266,14 +8243,14 @@
       <c r="C153" t="s">
         <v>515</v>
       </c>
-      <c r="D153" s="2" t="s">
+      <c r="D153" t="s">
         <v>516</v>
       </c>
-      <c r="G153" s="2" t="s">
+      <c r="G153" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>87</v>
       </c>
@@ -8283,14 +8260,14 @@
       <c r="C154" t="s">
         <v>518</v>
       </c>
-      <c r="E154" s="2" t="s">
+      <c r="E154" t="s">
         <v>519</v>
       </c>
-      <c r="H154" s="2" t="s">
+      <c r="H154" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>87</v>
       </c>
@@ -8300,50 +8277,50 @@
       <c r="C155" t="s">
         <v>521</v>
       </c>
-      <c r="E155" s="2" t="s">
+      <c r="E155" t="s">
         <v>522</v>
       </c>
-      <c r="H155" s="2" t="s">
+      <c r="H155" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B156">
         <v>4</v>
       </c>
       <c r="C156" t="s">
         <v>524</v>
       </c>
-      <c r="D156" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E156" s="2" t="s">
+      <c r="D156" t="s">
+        <v>152</v>
+      </c>
+      <c r="E156" t="s">
         <v>525</v>
       </c>
-      <c r="G156" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H156" s="2" t="s">
+      <c r="G156" t="s">
+        <v>152</v>
+      </c>
+      <c r="H156" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B157">
         <v>2</v>
       </c>
       <c r="C157" t="s">
         <v>527</v>
       </c>
-      <c r="D157" s="2" t="s">
+      <c r="D157" t="s">
         <v>528</v>
       </c>
-      <c r="E157" s="2" t="s">
+      <c r="E157" t="s">
         <v>529</v>
       </c>
-      <c r="G157" s="2" t="s">
+      <c r="G157" t="s">
         <v>530</v>
       </c>
-      <c r="H157" s="2" t="s">
+      <c r="H157" t="s">
         <v>531</v>
       </c>
     </row>
@@ -8354,10 +8331,10 @@
       <c r="C158" t="s">
         <v>532</v>
       </c>
-      <c r="D158" s="2" t="s">
+      <c r="D158" t="s">
         <v>533</v>
       </c>
-      <c r="G158" s="2" t="s">
+      <c r="G158" t="s">
         <v>534</v>
       </c>
     </row>
@@ -8371,14 +8348,14 @@
       <c r="C159" t="s">
         <v>535</v>
       </c>
-      <c r="E159" s="2" t="s">
+      <c r="E159" t="s">
         <v>536</v>
       </c>
-      <c r="H159" s="2" t="s">
+      <c r="H159" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>87</v>
       </c>
@@ -8388,30 +8365,30 @@
       <c r="C160" t="s">
         <v>538</v>
       </c>
-      <c r="E160" s="2" t="s">
+      <c r="E160" t="s">
         <v>539</v>
       </c>
-      <c r="H160" s="2" t="s">
+      <c r="H160" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B161">
         <v>4</v>
       </c>
       <c r="C161" t="s">
         <v>541</v>
       </c>
-      <c r="D161" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E161" s="2" t="s">
+      <c r="D161" t="s">
+        <v>152</v>
+      </c>
+      <c r="E161" t="s">
         <v>542</v>
       </c>
-      <c r="G161" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H161" s="2" t="s">
+      <c r="G161" t="s">
+        <v>152</v>
+      </c>
+      <c r="H161" t="s">
         <v>543</v>
       </c>
     </row>
@@ -8422,14 +8399,14 @@
       <c r="C162" t="s">
         <v>544</v>
       </c>
-      <c r="D162" s="2" t="s">
+      <c r="D162" t="s">
         <v>545</v>
       </c>
-      <c r="G162" s="2" t="s">
+      <c r="G162" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>87</v>
       </c>
@@ -8439,10 +8416,10 @@
       <c r="C163" t="s">
         <v>547</v>
       </c>
-      <c r="E163" s="2" t="s">
+      <c r="E163" t="s">
         <v>548</v>
       </c>
-      <c r="H163" s="2" t="s">
+      <c r="H163" t="s">
         <v>549</v>
       </c>
     </row>
@@ -8456,30 +8433,30 @@
       <c r="C164" t="s">
         <v>550</v>
       </c>
-      <c r="E164" s="2" t="s">
+      <c r="E164" t="s">
         <v>551</v>
       </c>
-      <c r="H164" s="2" t="s">
+      <c r="H164" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B165">
         <v>4</v>
       </c>
       <c r="C165" t="s">
         <v>553</v>
       </c>
-      <c r="D165" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E165" s="2" t="s">
+      <c r="D165" t="s">
+        <v>152</v>
+      </c>
+      <c r="E165" t="s">
         <v>554</v>
       </c>
-      <c r="G165" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H165" s="2" t="s">
+      <c r="G165" t="s">
+        <v>152</v>
+      </c>
+      <c r="H165" t="s">
         <v>555</v>
       </c>
     </row>
@@ -8490,10 +8467,10 @@
       <c r="C166" t="s">
         <v>556</v>
       </c>
-      <c r="D166" s="2" t="s">
+      <c r="D166" t="s">
         <v>557</v>
       </c>
-      <c r="G166" s="2" t="s">
+      <c r="G166" t="s">
         <v>558</v>
       </c>
     </row>
@@ -8507,14 +8484,14 @@
       <c r="C167" t="s">
         <v>559</v>
       </c>
-      <c r="E167" s="2" t="s">
+      <c r="E167" t="s">
         <v>560</v>
       </c>
-      <c r="H167" s="2" t="s">
+      <c r="H167" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>87</v>
       </c>
@@ -8524,10 +8501,10 @@
       <c r="C168" t="s">
         <v>562</v>
       </c>
-      <c r="E168" s="2" t="s">
+      <c r="E168" t="s">
         <v>563</v>
       </c>
-      <c r="H168" s="2" t="s">
+      <c r="H168" t="s">
         <v>564</v>
       </c>
     </row>
@@ -8541,10 +8518,10 @@
       <c r="C169" t="s">
         <v>565</v>
       </c>
-      <c r="E169" s="2" t="s">
+      <c r="E169" t="s">
         <v>566</v>
       </c>
-      <c r="H169" s="2" t="s">
+      <c r="H169" t="s">
         <v>567</v>
       </c>
     </row>
@@ -8558,30 +8535,30 @@
       <c r="C170" t="s">
         <v>568</v>
       </c>
-      <c r="E170" s="2" t="s">
+      <c r="E170" t="s">
         <v>569</v>
       </c>
-      <c r="H170" s="2" t="s">
+      <c r="H170" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B171">
         <v>4</v>
       </c>
       <c r="C171" t="s">
         <v>571</v>
       </c>
-      <c r="D171" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E171" s="2" t="s">
+      <c r="D171" t="s">
+        <v>152</v>
+      </c>
+      <c r="E171" t="s">
         <v>572</v>
       </c>
-      <c r="G171" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H171" s="2" t="s">
+      <c r="G171" t="s">
+        <v>152</v>
+      </c>
+      <c r="H171" t="s">
         <v>573</v>
       </c>
     </row>
@@ -8592,10 +8569,10 @@
       <c r="C172" t="s">
         <v>574</v>
       </c>
-      <c r="D172" s="2" t="s">
+      <c r="D172" t="s">
         <v>575</v>
       </c>
-      <c r="G172" s="2" t="s">
+      <c r="G172" t="s">
         <v>576</v>
       </c>
     </row>
@@ -8609,10 +8586,10 @@
       <c r="C173" t="s">
         <v>577</v>
       </c>
-      <c r="E173" s="2" t="s">
+      <c r="E173" t="s">
         <v>578</v>
       </c>
-      <c r="H173" s="2" t="s">
+      <c r="H173" t="s">
         <v>579</v>
       </c>
     </row>
@@ -8626,30 +8603,30 @@
       <c r="C174" t="s">
         <v>580</v>
       </c>
-      <c r="E174" s="2" t="s">
+      <c r="E174" t="s">
         <v>581</v>
       </c>
-      <c r="H174" s="2" t="s">
+      <c r="H174" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B175">
         <v>4</v>
       </c>
       <c r="C175" t="s">
         <v>583</v>
       </c>
-      <c r="D175" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E175" s="2" t="s">
+      <c r="D175" t="s">
+        <v>152</v>
+      </c>
+      <c r="E175" t="s">
         <v>584</v>
       </c>
-      <c r="G175" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H175" s="2" t="s">
+      <c r="G175" t="s">
+        <v>152</v>
+      </c>
+      <c r="H175" t="s">
         <v>585</v>
       </c>
     </row>
@@ -8660,10 +8637,10 @@
       <c r="C176" t="s">
         <v>586</v>
       </c>
-      <c r="D176" s="2" t="s">
+      <c r="D176" t="s">
         <v>587</v>
       </c>
-      <c r="G176" s="2" t="s">
+      <c r="G176" t="s">
         <v>588</v>
       </c>
     </row>
@@ -8677,30 +8654,30 @@
       <c r="C177" t="s">
         <v>589</v>
       </c>
-      <c r="E177" s="2" t="s">
+      <c r="E177" t="s">
         <v>590</v>
       </c>
-      <c r="H177" s="2" t="s">
+      <c r="H177" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B178">
         <v>4</v>
       </c>
       <c r="C178" t="s">
         <v>592</v>
       </c>
-      <c r="D178" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E178" s="2" t="s">
+      <c r="D178" t="s">
+        <v>152</v>
+      </c>
+      <c r="E178" t="s">
         <v>593</v>
       </c>
-      <c r="G178" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H178" s="2" t="s">
+      <c r="G178" t="s">
+        <v>152</v>
+      </c>
+      <c r="H178" t="s">
         <v>594</v>
       </c>
     </row>
@@ -8711,10 +8688,10 @@
       <c r="C179" t="s">
         <v>595</v>
       </c>
-      <c r="D179" s="2" t="s">
+      <c r="D179" t="s">
         <v>596</v>
       </c>
-      <c r="G179" s="2" t="s">
+      <c r="G179" t="s">
         <v>597</v>
       </c>
     </row>
@@ -8728,14 +8705,14 @@
       <c r="C180" t="s">
         <v>598</v>
       </c>
-      <c r="E180" s="2" t="s">
+      <c r="E180" t="s">
         <v>599</v>
       </c>
-      <c r="H180" s="2" t="s">
+      <c r="H180" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>87</v>
       </c>
@@ -8745,14 +8722,14 @@
       <c r="C181" t="s">
         <v>601</v>
       </c>
-      <c r="E181" s="2" t="s">
+      <c r="E181" t="s">
         <v>602</v>
       </c>
-      <c r="H181" s="2" t="s">
+      <c r="H181" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>87</v>
       </c>
@@ -8762,10 +8739,10 @@
       <c r="C182" t="s">
         <v>604</v>
       </c>
-      <c r="E182" s="2" t="s">
+      <c r="E182" t="s">
         <v>605</v>
       </c>
-      <c r="H182" s="2" t="s">
+      <c r="H182" t="s">
         <v>606</v>
       </c>
     </row>
@@ -8779,30 +8756,30 @@
       <c r="C183" t="s">
         <v>607</v>
       </c>
-      <c r="E183" s="2" t="s">
+      <c r="E183" t="s">
         <v>608</v>
       </c>
-      <c r="H183" s="2" t="s">
+      <c r="H183" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B184">
         <v>4</v>
       </c>
       <c r="C184" t="s">
         <v>610</v>
       </c>
-      <c r="D184" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E184" s="2" t="s">
+      <c r="D184" t="s">
+        <v>152</v>
+      </c>
+      <c r="E184" t="s">
         <v>611</v>
       </c>
-      <c r="G184" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H184" s="2" t="s">
+      <c r="G184" t="s">
+        <v>152</v>
+      </c>
+      <c r="H184" t="s">
         <v>612</v>
       </c>
     </row>
@@ -8813,10 +8790,10 @@
       <c r="C185" t="s">
         <v>613</v>
       </c>
-      <c r="D185" s="2" t="s">
+      <c r="D185" t="s">
         <v>614</v>
       </c>
-      <c r="G185" s="2" t="s">
+      <c r="G185" t="s">
         <v>615</v>
       </c>
     </row>
@@ -8830,10 +8807,10 @@
       <c r="C186" t="s">
         <v>616</v>
       </c>
-      <c r="E186" s="2" t="s">
+      <c r="E186" t="s">
         <v>617</v>
       </c>
-      <c r="H186" s="2" t="s">
+      <c r="H186" t="s">
         <v>618</v>
       </c>
     </row>
@@ -8847,10 +8824,10 @@
       <c r="C187" t="s">
         <v>619</v>
       </c>
-      <c r="E187" s="2" t="s">
+      <c r="E187" t="s">
         <v>620</v>
       </c>
-      <c r="H187" s="2" t="s">
+      <c r="H187" t="s">
         <v>621</v>
       </c>
     </row>
@@ -8864,30 +8841,30 @@
       <c r="C188" t="s">
         <v>622</v>
       </c>
-      <c r="E188" s="2" t="s">
+      <c r="E188" t="s">
         <v>623</v>
       </c>
-      <c r="H188" s="2" t="s">
+      <c r="H188" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B189">
         <v>4</v>
       </c>
       <c r="C189" t="s">
         <v>625</v>
       </c>
-      <c r="D189" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E189" s="2" t="s">
+      <c r="D189" t="s">
+        <v>152</v>
+      </c>
+      <c r="E189" t="s">
         <v>626</v>
       </c>
-      <c r="G189" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H189" s="2" t="s">
+      <c r="G189" t="s">
+        <v>152</v>
+      </c>
+      <c r="H189" t="s">
         <v>627</v>
       </c>
     </row>
@@ -8898,10 +8875,10 @@
       <c r="C190" t="s">
         <v>628</v>
       </c>
-      <c r="D190" s="2" t="s">
+      <c r="D190" t="s">
         <v>629</v>
       </c>
-      <c r="G190" s="2" t="s">
+      <c r="G190" t="s">
         <v>630</v>
       </c>
     </row>
@@ -8915,10 +8892,10 @@
       <c r="C191" t="s">
         <v>631</v>
       </c>
-      <c r="E191" s="2" t="s">
+      <c r="E191" t="s">
         <v>632</v>
       </c>
-      <c r="H191" s="2" t="s">
+      <c r="H191" t="s">
         <v>633</v>
       </c>
     </row>
@@ -8932,10 +8909,10 @@
       <c r="C192" t="s">
         <v>634</v>
       </c>
-      <c r="E192" s="2" t="s">
+      <c r="E192" t="s">
         <v>635</v>
       </c>
-      <c r="H192" s="2" t="s">
+      <c r="H192" t="s">
         <v>636</v>
       </c>
     </row>
@@ -8949,30 +8926,30 @@
       <c r="C193" t="s">
         <v>637</v>
       </c>
-      <c r="E193" s="2" t="s">
+      <c r="E193" t="s">
         <v>638</v>
       </c>
-      <c r="H193" s="2" t="s">
+      <c r="H193" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B194">
         <v>4</v>
       </c>
       <c r="C194" t="s">
         <v>640</v>
       </c>
-      <c r="D194" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E194" s="2" t="s">
+      <c r="D194" t="s">
+        <v>152</v>
+      </c>
+      <c r="E194" t="s">
         <v>641</v>
       </c>
-      <c r="G194" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H194" s="2" t="s">
+      <c r="G194" t="s">
+        <v>152</v>
+      </c>
+      <c r="H194" t="s">
         <v>642</v>
       </c>
     </row>
@@ -8983,10 +8960,10 @@
       <c r="C195" t="s">
         <v>643</v>
       </c>
-      <c r="D195" s="2" t="s">
+      <c r="D195" t="s">
         <v>644</v>
       </c>
-      <c r="G195" s="2" t="s">
+      <c r="G195" t="s">
         <v>645</v>
       </c>
     </row>
@@ -9000,10 +8977,10 @@
       <c r="C196" t="s">
         <v>646</v>
       </c>
-      <c r="E196" s="2" t="s">
+      <c r="E196" t="s">
         <v>647</v>
       </c>
-      <c r="H196" s="2" t="s">
+      <c r="H196" t="s">
         <v>648</v>
       </c>
     </row>
@@ -9017,48 +8994,48 @@
       <c r="C197" t="s">
         <v>649</v>
       </c>
-      <c r="E197" s="2" t="s">
+      <c r="E197" t="s">
         <v>650</v>
       </c>
-      <c r="H197" s="2" t="s">
+      <c r="H197" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B198">
         <v>4</v>
       </c>
       <c r="C198" t="s">
         <v>652</v>
       </c>
-      <c r="D198" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E198" s="2" t="s">
+      <c r="D198" t="s">
+        <v>152</v>
+      </c>
+      <c r="E198" t="s">
         <v>653</v>
       </c>
-      <c r="G198" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H198" s="2" t="s">
+      <c r="G198" t="s">
+        <v>152</v>
+      </c>
+      <c r="H198" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B199">
         <v>3</v>
       </c>
       <c r="C199" t="s">
         <v>655</v>
       </c>
-      <c r="D199" s="2" t="s">
+      <c r="D199" t="s">
         <v>656</v>
       </c>
-      <c r="G199" s="2" t="s">
+      <c r="G199" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>87</v>
       </c>
@@ -9068,14 +9045,14 @@
       <c r="C200" t="s">
         <v>658</v>
       </c>
-      <c r="E200" s="2" t="s">
+      <c r="E200" t="s">
         <v>659</v>
       </c>
-      <c r="H200" s="2" t="s">
+      <c r="H200" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>87</v>
       </c>
@@ -9085,68 +9062,68 @@
       <c r="C201" t="s">
         <v>661</v>
       </c>
-      <c r="E201" s="2" t="s">
+      <c r="E201" t="s">
         <v>662</v>
       </c>
-      <c r="H201" s="2" t="s">
+      <c r="H201" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B202">
         <v>4</v>
       </c>
       <c r="C202" t="s">
         <v>664</v>
       </c>
-      <c r="D202" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E202" s="2" t="s">
+      <c r="D202" t="s">
+        <v>152</v>
+      </c>
+      <c r="E202" t="s">
         <v>665</v>
       </c>
-      <c r="G202" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H202" s="2" t="s">
+      <c r="G202" t="s">
+        <v>152</v>
+      </c>
+      <c r="H202" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B203">
         <v>2</v>
       </c>
       <c r="C203" t="s">
         <v>667</v>
       </c>
-      <c r="D203" s="2" t="s">
+      <c r="D203" t="s">
         <v>668</v>
       </c>
-      <c r="E203" s="2" t="s">
+      <c r="E203" t="s">
         <v>669</v>
       </c>
-      <c r="G203" s="2" t="s">
+      <c r="G203" t="s">
         <v>670</v>
       </c>
-      <c r="H203" s="2" t="s">
+      <c r="H203" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B204">
         <v>3</v>
       </c>
       <c r="C204" t="s">
         <v>672</v>
       </c>
-      <c r="D204" s="2" t="s">
+      <c r="D204" t="s">
         <v>673</v>
       </c>
-      <c r="G204" s="2" t="s">
+      <c r="G204" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>87</v>
       </c>
@@ -9156,14 +9133,14 @@
       <c r="C205" t="s">
         <v>675</v>
       </c>
-      <c r="E205" s="2" t="s">
+      <c r="E205" t="s">
         <v>676</v>
       </c>
-      <c r="H205" s="2" t="s">
+      <c r="H205" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>87</v>
       </c>
@@ -9173,30 +9150,30 @@
       <c r="C206" t="s">
         <v>678</v>
       </c>
-      <c r="E206" s="2" t="s">
+      <c r="E206" t="s">
         <v>679</v>
       </c>
-      <c r="H206" s="2" t="s">
+      <c r="H206" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B207">
         <v>4</v>
       </c>
       <c r="C207" t="s">
         <v>681</v>
       </c>
-      <c r="D207" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E207" s="2" t="s">
+      <c r="D207" t="s">
+        <v>152</v>
+      </c>
+      <c r="E207" t="s">
         <v>682</v>
       </c>
-      <c r="G207" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H207" s="2" t="s">
+      <c r="G207" t="s">
+        <v>152</v>
+      </c>
+      <c r="H207" t="s">
         <v>683</v>
       </c>
     </row>
@@ -9207,14 +9184,14 @@
       <c r="C208" t="s">
         <v>684</v>
       </c>
-      <c r="D208" s="2" t="s">
+      <c r="D208" t="s">
         <v>685</v>
       </c>
-      <c r="G208" s="2" t="s">
+      <c r="G208" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>87</v>
       </c>
@@ -9224,30 +9201,30 @@
       <c r="C209" t="s">
         <v>687</v>
       </c>
-      <c r="E209" s="2" t="s">
+      <c r="E209" t="s">
         <v>688</v>
       </c>
-      <c r="H209" s="2" t="s">
+      <c r="H209" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B210">
         <v>4</v>
       </c>
       <c r="C210" t="s">
         <v>690</v>
       </c>
-      <c r="D210" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E210" s="2" t="s">
+      <c r="D210" t="s">
+        <v>152</v>
+      </c>
+      <c r="E210" t="s">
         <v>691</v>
       </c>
-      <c r="G210" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H210" s="2" t="s">
+      <c r="G210" t="s">
+        <v>152</v>
+      </c>
+      <c r="H210" t="s">
         <v>692</v>
       </c>
     </row>
@@ -9258,14 +9235,14 @@
       <c r="C211" t="s">
         <v>693</v>
       </c>
-      <c r="D211" s="2" t="s">
+      <c r="D211" t="s">
         <v>694</v>
       </c>
-      <c r="G211" s="2" t="s">
+      <c r="G211" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>87</v>
       </c>
@@ -9275,30 +9252,30 @@
       <c r="C212" t="s">
         <v>696</v>
       </c>
-      <c r="E212" s="2" t="s">
+      <c r="E212" t="s">
         <v>697</v>
       </c>
-      <c r="H212" s="2" t="s">
+      <c r="H212" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B213">
         <v>4</v>
       </c>
       <c r="C213" t="s">
         <v>699</v>
       </c>
-      <c r="D213" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E213" s="2" t="s">
+      <c r="D213" t="s">
+        <v>152</v>
+      </c>
+      <c r="E213" t="s">
         <v>700</v>
       </c>
-      <c r="G213" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H213" s="2" t="s">
+      <c r="G213" t="s">
+        <v>152</v>
+      </c>
+      <c r="H213" t="s">
         <v>701</v>
       </c>
     </row>
@@ -9309,10 +9286,10 @@
       <c r="C214" t="s">
         <v>702</v>
       </c>
-      <c r="D214" s="2" t="s">
+      <c r="D214" t="s">
         <v>703</v>
       </c>
-      <c r="G214" s="2" t="s">
+      <c r="G214" t="s">
         <v>704</v>
       </c>
     </row>
@@ -9326,30 +9303,30 @@
       <c r="C215" t="s">
         <v>705</v>
       </c>
-      <c r="E215" s="2" t="s">
+      <c r="E215" t="s">
         <v>706</v>
       </c>
-      <c r="H215" s="2" t="s">
+      <c r="H215" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B216">
         <v>4</v>
       </c>
       <c r="C216" t="s">
         <v>708</v>
       </c>
-      <c r="D216" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E216" s="2" t="s">
+      <c r="D216" t="s">
+        <v>152</v>
+      </c>
+      <c r="E216" t="s">
         <v>709</v>
       </c>
-      <c r="G216" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H216" s="2" t="s">
+      <c r="G216" t="s">
+        <v>152</v>
+      </c>
+      <c r="H216" t="s">
         <v>710</v>
       </c>
     </row>
@@ -9360,14 +9337,14 @@
       <c r="C217" t="s">
         <v>711</v>
       </c>
-      <c r="D217" s="2" t="s">
+      <c r="D217" t="s">
         <v>712</v>
       </c>
-      <c r="G217" s="2" t="s">
+      <c r="G217" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>87</v>
       </c>
@@ -9377,10 +9354,10 @@
       <c r="C218" t="s">
         <v>714</v>
       </c>
-      <c r="E218" s="2" t="s">
+      <c r="E218" t="s">
         <v>715</v>
       </c>
-      <c r="H218" s="2" t="s">
+      <c r="H218" t="s">
         <v>716</v>
       </c>
     </row>
@@ -9394,10 +9371,10 @@
       <c r="C219" t="s">
         <v>717</v>
       </c>
-      <c r="E219" s="2" t="s">
+      <c r="E219" t="s">
         <v>718</v>
       </c>
-      <c r="H219" s="2" t="s">
+      <c r="H219" t="s">
         <v>719</v>
       </c>
     </row>
@@ -9411,14 +9388,14 @@
       <c r="C220" t="s">
         <v>720</v>
       </c>
-      <c r="E220" s="2" t="s">
+      <c r="E220" t="s">
         <v>721</v>
       </c>
-      <c r="H220" s="2" t="s">
+      <c r="H220" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>87</v>
       </c>
@@ -9428,30 +9405,30 @@
       <c r="C221" t="s">
         <v>723</v>
       </c>
-      <c r="E221" s="2" t="s">
+      <c r="E221" t="s">
         <v>724</v>
       </c>
-      <c r="H221" s="2" t="s">
+      <c r="H221" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B222">
         <v>4</v>
       </c>
       <c r="C222" t="s">
         <v>726</v>
       </c>
-      <c r="D222" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E222" s="2" t="s">
+      <c r="D222" t="s">
+        <v>152</v>
+      </c>
+      <c r="E222" t="s">
         <v>727</v>
       </c>
-      <c r="G222" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H222" s="2" t="s">
+      <c r="G222" t="s">
+        <v>152</v>
+      </c>
+      <c r="H222" t="s">
         <v>728</v>
       </c>
     </row>
@@ -9462,14 +9439,14 @@
       <c r="C223" t="s">
         <v>729</v>
       </c>
-      <c r="D223" s="2" t="s">
+      <c r="D223" t="s">
         <v>730</v>
       </c>
-      <c r="G223" s="2" t="s">
+      <c r="G223" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>87</v>
       </c>
@@ -9479,14 +9456,14 @@
       <c r="C224" t="s">
         <v>732</v>
       </c>
-      <c r="E224" s="2" t="s">
+      <c r="E224" t="s">
         <v>733</v>
       </c>
-      <c r="H224" s="2" t="s">
+      <c r="H224" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>87</v>
       </c>
@@ -9496,10 +9473,10 @@
       <c r="C225" t="s">
         <v>735</v>
       </c>
-      <c r="E225" s="2" t="s">
+      <c r="E225" t="s">
         <v>736</v>
       </c>
-      <c r="H225" s="2" t="s">
+      <c r="H225" t="s">
         <v>737</v>
       </c>
     </row>
@@ -9513,10 +9490,10 @@
       <c r="C226" t="s">
         <v>738</v>
       </c>
-      <c r="E226" s="2" t="s">
+      <c r="E226" t="s">
         <v>739</v>
       </c>
-      <c r="H226" s="2" t="s">
+      <c r="H226" t="s">
         <v>740</v>
       </c>
     </row>
@@ -9530,10 +9507,10 @@
       <c r="C227" t="s">
         <v>741</v>
       </c>
-      <c r="E227" s="2" t="s">
+      <c r="E227" t="s">
         <v>742</v>
       </c>
-      <c r="H227" s="2" t="s">
+      <c r="H227" t="s">
         <v>743</v>
       </c>
     </row>
@@ -9547,14 +9524,14 @@
       <c r="C228" t="s">
         <v>744</v>
       </c>
-      <c r="E228" s="2" t="s">
+      <c r="E228" t="s">
         <v>745</v>
       </c>
-      <c r="H228" s="2" t="s">
+      <c r="H228" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>87</v>
       </c>
@@ -9564,30 +9541,30 @@
       <c r="C229" t="s">
         <v>747</v>
       </c>
-      <c r="E229" s="2" t="s">
+      <c r="E229" t="s">
         <v>748</v>
       </c>
-      <c r="H229" s="2" t="s">
+      <c r="H229" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B230">
         <v>4</v>
       </c>
       <c r="C230" t="s">
         <v>750</v>
       </c>
-      <c r="D230" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E230" s="2" t="s">
+      <c r="D230" t="s">
+        <v>152</v>
+      </c>
+      <c r="E230" t="s">
         <v>751</v>
       </c>
-      <c r="G230" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H230" s="2" t="s">
+      <c r="G230" t="s">
+        <v>152</v>
+      </c>
+      <c r="H230" t="s">
         <v>752</v>
       </c>
     </row>
@@ -9598,10 +9575,10 @@
       <c r="C231" t="s">
         <v>753</v>
       </c>
-      <c r="D231" s="2" t="s">
+      <c r="D231" t="s">
         <v>754</v>
       </c>
-      <c r="G231" s="2" t="s">
+      <c r="G231" t="s">
         <v>755</v>
       </c>
     </row>
@@ -9615,30 +9592,30 @@
       <c r="C232" t="s">
         <v>756</v>
       </c>
-      <c r="E232" s="2" t="s">
+      <c r="E232" t="s">
         <v>757</v>
       </c>
-      <c r="H232" s="2" t="s">
+      <c r="H232" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B233">
         <v>4</v>
       </c>
       <c r="C233" t="s">
         <v>759</v>
       </c>
-      <c r="D233" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E233" s="2" t="s">
+      <c r="D233" t="s">
+        <v>152</v>
+      </c>
+      <c r="E233" t="s">
         <v>760</v>
       </c>
-      <c r="G233" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H233" s="2" t="s">
+      <c r="G233" t="s">
+        <v>152</v>
+      </c>
+      <c r="H233" t="s">
         <v>761</v>
       </c>
     </row>
@@ -9649,14 +9626,14 @@
       <c r="C234" t="s">
         <v>762</v>
       </c>
-      <c r="D234" s="2" t="s">
+      <c r="D234" t="s">
         <v>763</v>
       </c>
-      <c r="G234" s="2" t="s">
+      <c r="G234" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>87</v>
       </c>
@@ -9666,10 +9643,10 @@
       <c r="C235" t="s">
         <v>765</v>
       </c>
-      <c r="E235" s="2" t="s">
+      <c r="E235" t="s">
         <v>766</v>
       </c>
-      <c r="H235" s="2" t="s">
+      <c r="H235" t="s">
         <v>767</v>
       </c>
     </row>
@@ -9683,14 +9660,14 @@
       <c r="C236" t="s">
         <v>768</v>
       </c>
-      <c r="E236" s="2" t="s">
+      <c r="E236" t="s">
         <v>769</v>
       </c>
-      <c r="H236" s="2" t="s">
+      <c r="H236" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>87</v>
       </c>
@@ -9700,10 +9677,10 @@
       <c r="C237" t="s">
         <v>771</v>
       </c>
-      <c r="E237" s="2" t="s">
+      <c r="E237" t="s">
         <v>772</v>
       </c>
-      <c r="H237" s="2" t="s">
+      <c r="H237" t="s">
         <v>773</v>
       </c>
     </row>
@@ -9717,14 +9694,14 @@
       <c r="C238" t="s">
         <v>774</v>
       </c>
-      <c r="E238" s="2" t="s">
+      <c r="E238" t="s">
         <v>775</v>
       </c>
-      <c r="H238" s="2" t="s">
+      <c r="H238" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>87</v>
       </c>
@@ -9734,10 +9711,10 @@
       <c r="C239" t="s">
         <v>777</v>
       </c>
-      <c r="E239" s="2" t="s">
+      <c r="E239" t="s">
         <v>778</v>
       </c>
-      <c r="H239" s="2" t="s">
+      <c r="H239" t="s">
         <v>779</v>
       </c>
     </row>
@@ -9751,50 +9728,50 @@
       <c r="C240" t="s">
         <v>780</v>
       </c>
-      <c r="E240" s="2" t="s">
+      <c r="E240" t="s">
         <v>781</v>
       </c>
-      <c r="H240" s="2" t="s">
+      <c r="H240" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="241" spans="1:10" ht="288" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B241">
         <v>4</v>
       </c>
       <c r="C241" t="s">
         <v>783</v>
       </c>
-      <c r="D241" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E241" s="2" t="s">
+      <c r="D241" t="s">
+        <v>152</v>
+      </c>
+      <c r="E241" t="s">
         <v>784</v>
       </c>
-      <c r="G241" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H241" s="2" t="s">
+      <c r="G241" t="s">
+        <v>152</v>
+      </c>
+      <c r="H241" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B242">
         <v>2</v>
       </c>
       <c r="C242" t="s">
         <v>786</v>
       </c>
-      <c r="D242" s="2" t="s">
+      <c r="D242" t="s">
         <v>787</v>
       </c>
-      <c r="E242" s="2" t="s">
+      <c r="E242" t="s">
         <v>788</v>
       </c>
-      <c r="G242" s="2" t="s">
+      <c r="G242" t="s">
         <v>789</v>
       </c>
-      <c r="H242" s="2" t="s">
+      <c r="H242" t="s">
         <v>790</v>
       </c>
     </row>
@@ -9805,14 +9782,14 @@
       <c r="C243" t="s">
         <v>791</v>
       </c>
-      <c r="D243" s="2" t="s">
+      <c r="D243" t="s">
         <v>792</v>
       </c>
-      <c r="G243" s="2" t="s">
+      <c r="G243" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="244" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>87</v>
       </c>
@@ -9822,44 +9799,44 @@
       <c r="C244" t="s">
         <v>794</v>
       </c>
-      <c r="E244" s="2" t="s">
+      <c r="E244" t="s">
         <v>795</v>
       </c>
-      <c r="H244" s="2" t="s">
+      <c r="H244" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="245" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B245">
         <v>4</v>
       </c>
       <c r="C245" t="s">
         <v>797</v>
       </c>
-      <c r="D245" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E245" s="2" t="s">
+      <c r="D245" t="s">
+        <v>152</v>
+      </c>
+      <c r="E245" t="s">
         <v>798</v>
       </c>
-      <c r="G245" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H245" s="2" t="s">
+      <c r="G245" t="s">
+        <v>152</v>
+      </c>
+      <c r="H245" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="246" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B246">
         <v>3</v>
       </c>
       <c r="C246" t="s">
         <v>800</v>
       </c>
-      <c r="D246" s="2" t="s">
+      <c r="D246" t="s">
         <v>801</v>
       </c>
-      <c r="G246" s="2" t="s">
+      <c r="G246" t="s">
         <v>802</v>
       </c>
     </row>
@@ -9873,14 +9850,14 @@
       <c r="C247" t="s">
         <v>803</v>
       </c>
-      <c r="E247" s="2" t="s">
+      <c r="E247" t="s">
         <v>804</v>
       </c>
-      <c r="H247" s="2" t="s">
+      <c r="H247" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="248" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>87</v>
       </c>
@@ -9890,10 +9867,10 @@
       <c r="C248" t="s">
         <v>806</v>
       </c>
-      <c r="E248" s="2" t="s">
+      <c r="E248" t="s">
         <v>807</v>
       </c>
-      <c r="H248" s="2" t="s">
+      <c r="H248" t="s">
         <v>808</v>
       </c>
     </row>
@@ -9907,14 +9884,14 @@
       <c r="C249" t="s">
         <v>809</v>
       </c>
-      <c r="E249" s="2" t="s">
+      <c r="E249" t="s">
         <v>810</v>
       </c>
-      <c r="H249" s="2" t="s">
+      <c r="H249" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="250" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>87</v>
       </c>
@@ -9924,30 +9901,30 @@
       <c r="C250" t="s">
         <v>812</v>
       </c>
-      <c r="E250" s="2" t="s">
+      <c r="E250" t="s">
         <v>813</v>
       </c>
-      <c r="H250" s="2" t="s">
+      <c r="H250" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="251" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B251">
         <v>4</v>
       </c>
       <c r="C251" t="s">
         <v>815</v>
       </c>
-      <c r="D251" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E251" s="2" t="s">
+      <c r="D251" t="s">
+        <v>152</v>
+      </c>
+      <c r="E251" t="s">
         <v>816</v>
       </c>
-      <c r="G251" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H251" s="2" t="s">
+      <c r="G251" t="s">
+        <v>152</v>
+      </c>
+      <c r="H251" t="s">
         <v>817</v>
       </c>
     </row>
@@ -9958,10 +9935,10 @@
       <c r="C252" t="s">
         <v>818</v>
       </c>
-      <c r="D252" s="2" t="s">
+      <c r="D252" t="s">
         <v>819</v>
       </c>
-      <c r="G252" s="2" t="s">
+      <c r="G252" t="s">
         <v>820</v>
       </c>
     </row>
@@ -9975,30 +9952,30 @@
       <c r="C253" t="s">
         <v>821</v>
       </c>
-      <c r="E253" s="2" t="s">
+      <c r="E253" t="s">
         <v>822</v>
       </c>
-      <c r="H253" s="2" t="s">
+      <c r="H253" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="254" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B254">
         <v>4</v>
       </c>
       <c r="C254" t="s">
         <v>824</v>
       </c>
-      <c r="D254" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E254" s="2" t="s">
+      <c r="D254" t="s">
+        <v>152</v>
+      </c>
+      <c r="E254" t="s">
         <v>825</v>
       </c>
-      <c r="G254" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H254" s="2" t="s">
+      <c r="G254" t="s">
+        <v>152</v>
+      </c>
+      <c r="H254" t="s">
         <v>826</v>
       </c>
     </row>
@@ -10009,31 +9986,31 @@
       <c r="C255" t="s">
         <v>827</v>
       </c>
-      <c r="D255" s="2" t="s">
+      <c r="D255" t="s">
         <v>828</v>
       </c>
-      <c r="G255" s="2" t="s">
+      <c r="G255" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B256">
         <v>4</v>
       </c>
       <c r="C256" t="s">
         <v>830</v>
       </c>
-      <c r="E256" s="2" t="s">
+      <c r="E256" t="s">
         <v>831</v>
       </c>
-      <c r="H256" s="2" t="s">
+      <c r="H256" t="s">
         <v>832</v>
       </c>
       <c r="J256" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="257" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>87</v>
       </c>
@@ -10043,10 +10020,10 @@
       <c r="C257" t="s">
         <v>833</v>
       </c>
-      <c r="E257" s="2" t="s">
+      <c r="E257" t="s">
         <v>834</v>
       </c>
-      <c r="H257" s="2" t="s">
+      <c r="H257" t="s">
         <v>835</v>
       </c>
     </row>
@@ -10060,10 +10037,10 @@
       <c r="C258" t="s">
         <v>836</v>
       </c>
-      <c r="E258" s="2" t="s">
+      <c r="E258" t="s">
         <v>837</v>
       </c>
-      <c r="H258" s="2" t="s">
+      <c r="H258" t="s">
         <v>838</v>
       </c>
     </row>
@@ -10077,14 +10054,14 @@
       <c r="C259" t="s">
         <v>839</v>
       </c>
-      <c r="E259" s="2" t="s">
+      <c r="E259" t="s">
         <v>840</v>
       </c>
-      <c r="H259" s="2" t="s">
+      <c r="H259" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="260" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>87</v>
       </c>
@@ -10094,30 +10071,30 @@
       <c r="C260" t="s">
         <v>842</v>
       </c>
-      <c r="E260" s="2" t="s">
+      <c r="E260" t="s">
         <v>843</v>
       </c>
-      <c r="H260" s="2" t="s">
+      <c r="H260" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B261">
         <v>4</v>
       </c>
       <c r="C261" t="s">
         <v>845</v>
       </c>
-      <c r="D261" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E261" s="2" t="s">
+      <c r="D261" t="s">
+        <v>152</v>
+      </c>
+      <c r="E261" t="s">
         <v>846</v>
       </c>
-      <c r="G261" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H261" s="2" t="s">
+      <c r="G261" t="s">
+        <v>152</v>
+      </c>
+      <c r="H261" t="s">
         <v>847</v>
       </c>
     </row>
@@ -10128,10 +10105,10 @@
       <c r="C262" t="s">
         <v>848</v>
       </c>
-      <c r="D262" s="2" t="s">
+      <c r="D262" t="s">
         <v>849</v>
       </c>
-      <c r="G262" s="2" t="s">
+      <c r="G262" t="s">
         <v>850</v>
       </c>
     </row>
@@ -10142,10 +10119,10 @@
       <c r="C263" t="s">
         <v>851</v>
       </c>
-      <c r="E263" s="2" t="s">
+      <c r="E263" t="s">
         <v>852</v>
       </c>
-      <c r="H263" s="2" t="s">
+      <c r="H263" t="s">
         <v>853</v>
       </c>
       <c r="J263" t="s">
@@ -10162,10 +10139,10 @@
       <c r="C264" t="s">
         <v>854</v>
       </c>
-      <c r="E264" s="2" t="s">
+      <c r="E264" t="s">
         <v>855</v>
       </c>
-      <c r="H264" s="2" t="s">
+      <c r="H264" t="s">
         <v>856</v>
       </c>
     </row>
@@ -10179,10 +10156,10 @@
       <c r="C265" t="s">
         <v>857</v>
       </c>
-      <c r="E265" s="2" t="s">
+      <c r="E265" t="s">
         <v>858</v>
       </c>
-      <c r="H265" s="2" t="s">
+      <c r="H265" t="s">
         <v>859</v>
       </c>
     </row>
@@ -10196,10 +10173,10 @@
       <c r="C266" t="s">
         <v>860</v>
       </c>
-      <c r="E266" s="2" t="s">
+      <c r="E266" t="s">
         <v>861</v>
       </c>
-      <c r="H266" s="2" t="s">
+      <c r="H266" t="s">
         <v>862</v>
       </c>
     </row>
@@ -10213,10 +10190,10 @@
       <c r="C267" t="s">
         <v>863</v>
       </c>
-      <c r="E267" s="2" t="s">
+      <c r="E267" t="s">
         <v>864</v>
       </c>
-      <c r="H267" s="2" t="s">
+      <c r="H267" t="s">
         <v>865</v>
       </c>
     </row>
@@ -10230,10 +10207,10 @@
       <c r="C268" t="s">
         <v>866</v>
       </c>
-      <c r="E268" s="2" t="s">
+      <c r="E268" t="s">
         <v>867</v>
       </c>
-      <c r="H268" s="2" t="s">
+      <c r="H268" t="s">
         <v>868</v>
       </c>
     </row>
@@ -10247,14 +10224,14 @@
       <c r="C269" t="s">
         <v>869</v>
       </c>
-      <c r="E269" s="2" t="s">
+      <c r="E269" t="s">
         <v>870</v>
       </c>
-      <c r="H269" s="2" t="s">
+      <c r="H269" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>87</v>
       </c>
@@ -10264,14 +10241,14 @@
       <c r="C270" t="s">
         <v>872</v>
       </c>
-      <c r="E270" s="2" t="s">
+      <c r="E270" t="s">
         <v>873</v>
       </c>
-      <c r="H270" s="2" t="s">
+      <c r="H270" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="271" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>87</v>
       </c>
@@ -10281,10 +10258,10 @@
       <c r="C271" t="s">
         <v>875</v>
       </c>
-      <c r="E271" s="2" t="s">
+      <c r="E271" t="s">
         <v>876</v>
       </c>
-      <c r="H271" s="2" t="s">
+      <c r="H271" t="s">
         <v>877</v>
       </c>
     </row>
@@ -10298,50 +10275,50 @@
       <c r="C272" t="s">
         <v>878</v>
       </c>
-      <c r="E272" s="2" t="s">
+      <c r="E272" t="s">
         <v>879</v>
       </c>
-      <c r="H272" s="2" t="s">
+      <c r="H272" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="273" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B273">
         <v>4</v>
       </c>
       <c r="C273" t="s">
         <v>881</v>
       </c>
-      <c r="D273" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E273" s="2" t="s">
+      <c r="D273" t="s">
+        <v>152</v>
+      </c>
+      <c r="E273" t="s">
         <v>882</v>
       </c>
-      <c r="G273" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H273" s="2" t="s">
+      <c r="G273" t="s">
+        <v>152</v>
+      </c>
+      <c r="H273" t="s">
         <v>883</v>
       </c>
     </row>
-    <row r="274" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B274">
         <v>2</v>
       </c>
       <c r="C274" t="s">
         <v>884</v>
       </c>
-      <c r="D274" s="2" t="s">
+      <c r="D274" t="s">
         <v>885</v>
       </c>
-      <c r="E274" s="2" t="s">
+      <c r="E274" t="s">
         <v>886</v>
       </c>
-      <c r="G274" s="2" t="s">
+      <c r="G274" t="s">
         <v>885</v>
       </c>
-      <c r="H274" s="2" t="s">
+      <c r="H274" t="s">
         <v>887</v>
       </c>
     </row>
@@ -10352,10 +10329,10 @@
       <c r="C275" t="s">
         <v>888</v>
       </c>
-      <c r="D275" s="2" t="s">
+      <c r="D275" t="s">
         <v>889</v>
       </c>
-      <c r="G275" s="2" t="s">
+      <c r="G275" t="s">
         <v>890</v>
       </c>
     </row>
@@ -10369,14 +10346,14 @@
       <c r="C276" t="s">
         <v>891</v>
       </c>
-      <c r="E276" s="2" t="s">
+      <c r="E276" t="s">
         <v>892</v>
       </c>
-      <c r="H276" s="2" t="s">
+      <c r="H276" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="277" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>87</v>
       </c>
@@ -10386,14 +10363,14 @@
       <c r="C277" t="s">
         <v>894</v>
       </c>
-      <c r="E277" s="2" t="s">
+      <c r="E277" t="s">
         <v>895</v>
       </c>
-      <c r="H277" s="2" t="s">
+      <c r="H277" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="278" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>87</v>
       </c>
@@ -10403,30 +10380,30 @@
       <c r="C278" t="s">
         <v>897</v>
       </c>
-      <c r="E278" s="2" t="s">
+      <c r="E278" t="s">
         <v>898</v>
       </c>
-      <c r="H278" s="2" t="s">
+      <c r="H278" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="279" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B279">
         <v>4</v>
       </c>
       <c r="C279" t="s">
         <v>900</v>
       </c>
-      <c r="D279" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E279" s="2" t="s">
+      <c r="D279" t="s">
+        <v>152</v>
+      </c>
+      <c r="E279" t="s">
         <v>901</v>
       </c>
-      <c r="G279" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H279" s="2" t="s">
+      <c r="G279" t="s">
+        <v>152</v>
+      </c>
+      <c r="H279" t="s">
         <v>902</v>
       </c>
     </row>
@@ -10437,10 +10414,10 @@
       <c r="C280" t="s">
         <v>903</v>
       </c>
-      <c r="D280" s="2" t="s">
+      <c r="D280" t="s">
         <v>904</v>
       </c>
-      <c r="G280" s="2" t="s">
+      <c r="G280" t="s">
         <v>905</v>
       </c>
     </row>
@@ -10454,14 +10431,14 @@
       <c r="C281" t="s">
         <v>906</v>
       </c>
-      <c r="E281" s="2" t="s">
+      <c r="E281" t="s">
         <v>907</v>
       </c>
-      <c r="H281" s="2" t="s">
+      <c r="H281" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="282" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>87</v>
       </c>
@@ -10471,10 +10448,10 @@
       <c r="C282" t="s">
         <v>909</v>
       </c>
-      <c r="E282" s="2" t="s">
+      <c r="E282" t="s">
         <v>910</v>
       </c>
-      <c r="H282" s="2" t="s">
+      <c r="H282" t="s">
         <v>911</v>
       </c>
     </row>
@@ -10488,30 +10465,30 @@
       <c r="C283" t="s">
         <v>912</v>
       </c>
-      <c r="E283" s="2" t="s">
+      <c r="E283" t="s">
         <v>913</v>
       </c>
-      <c r="H283" s="2" t="s">
+      <c r="H283" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B284">
         <v>4</v>
       </c>
       <c r="C284" t="s">
         <v>915</v>
       </c>
-      <c r="D284" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E284" s="2" t="s">
+      <c r="D284" t="s">
+        <v>152</v>
+      </c>
+      <c r="E284" t="s">
         <v>916</v>
       </c>
-      <c r="G284" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H284" s="2" t="s">
+      <c r="G284" t="s">
+        <v>152</v>
+      </c>
+      <c r="H284" t="s">
         <v>917</v>
       </c>
     </row>
@@ -10522,10 +10499,10 @@
       <c r="C285" t="s">
         <v>918</v>
       </c>
-      <c r="D285" s="2" t="s">
+      <c r="D285" t="s">
         <v>919</v>
       </c>
-      <c r="G285" s="2" t="s">
+      <c r="G285" t="s">
         <v>920</v>
       </c>
     </row>
@@ -10539,10 +10516,10 @@
       <c r="C286" t="s">
         <v>921</v>
       </c>
-      <c r="E286" s="2" t="s">
+      <c r="E286" t="s">
         <v>922</v>
       </c>
-      <c r="H286" s="2" t="s">
+      <c r="H286" t="s">
         <v>923</v>
       </c>
     </row>
@@ -10556,10 +10533,10 @@
       <c r="C287" t="s">
         <v>924</v>
       </c>
-      <c r="E287" s="2" t="s">
+      <c r="E287" t="s">
         <v>925</v>
       </c>
-      <c r="H287" s="2" t="s">
+      <c r="H287" t="s">
         <v>926</v>
       </c>
     </row>
@@ -10573,14 +10550,14 @@
       <c r="C288" t="s">
         <v>927</v>
       </c>
-      <c r="E288" s="2" t="s">
+      <c r="E288" t="s">
         <v>928</v>
       </c>
-      <c r="H288" s="2" t="s">
+      <c r="H288" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="289" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>87</v>
       </c>
@@ -10590,50 +10567,50 @@
       <c r="C289" t="s">
         <v>930</v>
       </c>
-      <c r="E289" s="2" t="s">
+      <c r="E289" t="s">
         <v>931</v>
       </c>
-      <c r="H289" s="2" t="s">
+      <c r="H289" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="290" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B290">
         <v>4</v>
       </c>
       <c r="C290" t="s">
         <v>933</v>
       </c>
-      <c r="D290" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E290" s="2" t="s">
+      <c r="D290" t="s">
+        <v>152</v>
+      </c>
+      <c r="E290" t="s">
         <v>934</v>
       </c>
-      <c r="G290" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H290" s="2" t="s">
+      <c r="G290" t="s">
+        <v>152</v>
+      </c>
+      <c r="H290" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="291" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B291">
         <v>2</v>
       </c>
       <c r="C291" t="s">
         <v>936</v>
       </c>
-      <c r="D291" s="2" t="s">
+      <c r="D291" t="s">
         <v>937</v>
       </c>
-      <c r="E291" s="2" t="s">
+      <c r="E291" t="s">
         <v>938</v>
       </c>
-      <c r="G291" s="2" t="s">
+      <c r="G291" t="s">
         <v>939</v>
       </c>
-      <c r="H291" s="2" t="s">
+      <c r="H291" t="s">
         <v>940</v>
       </c>
     </row>
@@ -10644,10 +10621,10 @@
       <c r="C292" t="s">
         <v>941</v>
       </c>
-      <c r="D292" s="2" t="s">
+      <c r="D292" t="s">
         <v>942</v>
       </c>
-      <c r="G292" s="2" t="s">
+      <c r="G292" t="s">
         <v>943</v>
       </c>
     </row>
@@ -10661,30 +10638,30 @@
       <c r="C293" t="s">
         <v>944</v>
       </c>
-      <c r="E293" s="2" t="s">
+      <c r="E293" t="s">
         <v>945</v>
       </c>
-      <c r="H293" s="2" t="s">
+      <c r="H293" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="294" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B294">
         <v>4</v>
       </c>
       <c r="C294" t="s">
         <v>947</v>
       </c>
-      <c r="D294" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E294" s="2" t="s">
+      <c r="D294" t="s">
+        <v>152</v>
+      </c>
+      <c r="E294" t="s">
         <v>948</v>
       </c>
-      <c r="G294" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H294" s="2" t="s">
+      <c r="G294" t="s">
+        <v>152</v>
+      </c>
+      <c r="H294" t="s">
         <v>949</v>
       </c>
     </row>
@@ -10695,10 +10672,10 @@
       <c r="C295" t="s">
         <v>950</v>
       </c>
-      <c r="D295" s="2" t="s">
+      <c r="D295" t="s">
         <v>951</v>
       </c>
-      <c r="G295" s="2" t="s">
+      <c r="G295" t="s">
         <v>952</v>
       </c>
     </row>
@@ -10712,30 +10689,30 @@
       <c r="C296" t="s">
         <v>953</v>
       </c>
-      <c r="E296" s="2" t="s">
+      <c r="E296" t="s">
         <v>954</v>
       </c>
-      <c r="H296" s="2" t="s">
+      <c r="H296" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="297" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B297">
         <v>4</v>
       </c>
       <c r="C297" t="s">
         <v>956</v>
       </c>
-      <c r="D297" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E297" s="2" t="s">
+      <c r="D297" t="s">
+        <v>152</v>
+      </c>
+      <c r="E297" t="s">
         <v>957</v>
       </c>
-      <c r="G297" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H297" s="2" t="s">
+      <c r="G297" t="s">
+        <v>152</v>
+      </c>
+      <c r="H297" t="s">
         <v>958</v>
       </c>
     </row>
@@ -10746,14 +10723,14 @@
       <c r="C298" t="s">
         <v>959</v>
       </c>
-      <c r="D298" s="2" t="s">
+      <c r="D298" t="s">
         <v>960</v>
       </c>
-      <c r="G298" s="2" t="s">
+      <c r="G298" t="s">
         <v>961</v>
       </c>
     </row>
-    <row r="299" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>87</v>
       </c>
@@ -10763,30 +10740,30 @@
       <c r="C299" t="s">
         <v>962</v>
       </c>
-      <c r="E299" s="2" t="s">
+      <c r="E299" t="s">
         <v>963</v>
       </c>
-      <c r="H299" s="2" t="s">
+      <c r="H299" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="300" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B300">
         <v>4</v>
       </c>
       <c r="C300" t="s">
         <v>965</v>
       </c>
-      <c r="D300" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E300" s="2" t="s">
+      <c r="D300" t="s">
+        <v>152</v>
+      </c>
+      <c r="E300" t="s">
         <v>966</v>
       </c>
-      <c r="G300" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H300" s="2" t="s">
+      <c r="G300" t="s">
+        <v>152</v>
+      </c>
+      <c r="H300" t="s">
         <v>967</v>
       </c>
     </row>
@@ -10797,14 +10774,14 @@
       <c r="C301" t="s">
         <v>968</v>
       </c>
-      <c r="D301" s="2" t="s">
+      <c r="D301" t="s">
         <v>969</v>
       </c>
-      <c r="G301" s="2" t="s">
+      <c r="G301" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="302" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>87</v>
       </c>
@@ -10814,30 +10791,30 @@
       <c r="C302" t="s">
         <v>971</v>
       </c>
-      <c r="E302" s="2" t="s">
+      <c r="E302" t="s">
         <v>972</v>
       </c>
-      <c r="H302" s="2" t="s">
+      <c r="H302" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="303" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B303">
         <v>4</v>
       </c>
       <c r="C303" t="s">
         <v>974</v>
       </c>
-      <c r="D303" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E303" s="2" t="s">
+      <c r="D303" t="s">
+        <v>152</v>
+      </c>
+      <c r="E303" t="s">
         <v>975</v>
       </c>
-      <c r="G303" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H303" s="2" t="s">
+      <c r="G303" t="s">
+        <v>152</v>
+      </c>
+      <c r="H303" t="s">
         <v>976</v>
       </c>
     </row>
@@ -10848,10 +10825,10 @@
       <c r="C304" t="s">
         <v>977</v>
       </c>
-      <c r="D304" s="2" t="s">
+      <c r="D304" t="s">
         <v>978</v>
       </c>
-      <c r="G304" s="2" t="s">
+      <c r="G304" t="s">
         <v>979</v>
       </c>
     </row>
@@ -10865,10 +10842,10 @@
       <c r="C305" t="s">
         <v>980</v>
       </c>
-      <c r="E305" s="2" t="s">
+      <c r="E305" t="s">
         <v>981</v>
       </c>
-      <c r="H305" s="2" t="s">
+      <c r="H305" t="s">
         <v>982</v>
       </c>
     </row>
@@ -10882,10 +10859,10 @@
       <c r="C306" t="s">
         <v>983</v>
       </c>
-      <c r="E306" s="2" t="s">
+      <c r="E306" t="s">
         <v>984</v>
       </c>
-      <c r="H306" s="2" t="s">
+      <c r="H306" t="s">
         <v>985</v>
       </c>
     </row>
@@ -10899,30 +10876,30 @@
       <c r="C307" t="s">
         <v>986</v>
       </c>
-      <c r="E307" s="2" t="s">
+      <c r="E307" t="s">
         <v>987</v>
       </c>
-      <c r="H307" s="2" t="s">
+      <c r="H307" t="s">
         <v>988</v>
       </c>
     </row>
-    <row r="308" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B308">
         <v>4</v>
       </c>
       <c r="C308" t="s">
         <v>989</v>
       </c>
-      <c r="D308" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E308" s="2" t="s">
+      <c r="D308" t="s">
+        <v>152</v>
+      </c>
+      <c r="E308" t="s">
         <v>990</v>
       </c>
-      <c r="G308" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H308" s="2" t="s">
+      <c r="G308" t="s">
+        <v>152</v>
+      </c>
+      <c r="H308" t="s">
         <v>991</v>
       </c>
     </row>
@@ -10933,10 +10910,10 @@
       <c r="C309" t="s">
         <v>992</v>
       </c>
-      <c r="D309" s="2" t="s">
+      <c r="D309" t="s">
         <v>993</v>
       </c>
-      <c r="G309" s="2" t="s">
+      <c r="G309" t="s">
         <v>994</v>
       </c>
     </row>
@@ -10950,10 +10927,10 @@
       <c r="C310" t="s">
         <v>995</v>
       </c>
-      <c r="E310" s="2" t="s">
+      <c r="E310" t="s">
         <v>996</v>
       </c>
-      <c r="H310" s="2" t="s">
+      <c r="H310" t="s">
         <v>997</v>
       </c>
     </row>
@@ -10967,30 +10944,30 @@
       <c r="C311" t="s">
         <v>998</v>
       </c>
-      <c r="E311" s="2" t="s">
+      <c r="E311" t="s">
         <v>999</v>
       </c>
-      <c r="H311" s="2" t="s">
+      <c r="H311" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="312" spans="1:8" ht="216" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B312">
         <v>4</v>
       </c>
       <c r="C312" t="s">
         <v>1001</v>
       </c>
-      <c r="D312" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E312" s="2" t="s">
+      <c r="D312" t="s">
+        <v>152</v>
+      </c>
+      <c r="E312" t="s">
         <v>1002</v>
       </c>
-      <c r="G312" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H312" s="2" t="s">
+      <c r="G312" t="s">
+        <v>152</v>
+      </c>
+      <c r="H312" t="s">
         <v>1003</v>
       </c>
     </row>
@@ -11001,10 +10978,10 @@
       <c r="C313" t="s">
         <v>1004</v>
       </c>
-      <c r="D313" s="2" t="s">
+      <c r="D313" t="s">
         <v>1005</v>
       </c>
-      <c r="G313" s="2" t="s">
+      <c r="G313" t="s">
         <v>1006</v>
       </c>
     </row>
@@ -11018,14 +10995,14 @@
       <c r="C314" t="s">
         <v>1007</v>
       </c>
-      <c r="E314" s="2" t="s">
+      <c r="E314" t="s">
         <v>1008</v>
       </c>
-      <c r="H314" s="2" t="s">
+      <c r="H314" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="315" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>87</v>
       </c>
@@ -11035,50 +11012,50 @@
       <c r="C315" t="s">
         <v>1010</v>
       </c>
-      <c r="E315" s="2" t="s">
+      <c r="E315" t="s">
         <v>1011</v>
       </c>
-      <c r="H315" s="2" t="s">
+      <c r="H315" t="s">
         <v>1012</v>
       </c>
     </row>
-    <row r="316" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B316">
         <v>4</v>
       </c>
       <c r="C316" t="s">
         <v>1013</v>
       </c>
-      <c r="D316" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E316" s="2" t="s">
+      <c r="D316" t="s">
+        <v>152</v>
+      </c>
+      <c r="E316" t="s">
         <v>1014</v>
       </c>
-      <c r="G316" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H316" s="2" t="s">
+      <c r="G316" t="s">
+        <v>152</v>
+      </c>
+      <c r="H316" t="s">
         <v>1015</v>
       </c>
     </row>
-    <row r="317" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B317">
         <v>2</v>
       </c>
       <c r="C317" t="s">
         <v>1016</v>
       </c>
-      <c r="D317" s="2" t="s">
+      <c r="D317" t="s">
         <v>1017</v>
       </c>
-      <c r="E317" s="2" t="s">
+      <c r="E317" t="s">
         <v>1018</v>
       </c>
-      <c r="G317" s="2" t="s">
+      <c r="G317" t="s">
         <v>1019</v>
       </c>
-      <c r="H317" s="2" t="s">
+      <c r="H317" t="s">
         <v>1020</v>
       </c>
     </row>
@@ -11089,10 +11066,10 @@
       <c r="C318" t="s">
         <v>1021</v>
       </c>
-      <c r="D318" s="2" t="s">
+      <c r="D318" t="s">
         <v>1022</v>
       </c>
-      <c r="G318" s="2" t="s">
+      <c r="G318" t="s">
         <v>1023</v>
       </c>
     </row>
@@ -11106,14 +11083,14 @@
       <c r="C319" t="s">
         <v>1024</v>
       </c>
-      <c r="E319" s="2" t="s">
+      <c r="E319" t="s">
         <v>1025</v>
       </c>
-      <c r="H319" s="2" t="s">
+      <c r="H319" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="320" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>87</v>
       </c>
@@ -11123,30 +11100,30 @@
       <c r="C320" t="s">
         <v>1027</v>
       </c>
-      <c r="E320" s="2" t="s">
+      <c r="E320" t="s">
         <v>1028</v>
       </c>
-      <c r="H320" s="2" t="s">
+      <c r="H320" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="321" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B321">
         <v>4</v>
       </c>
       <c r="C321" t="s">
         <v>1030</v>
       </c>
-      <c r="D321" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E321" s="2" t="s">
+      <c r="D321" t="s">
+        <v>152</v>
+      </c>
+      <c r="E321" t="s">
         <v>1031</v>
       </c>
-      <c r="G321" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H321" s="2" t="s">
+      <c r="G321" t="s">
+        <v>152</v>
+      </c>
+      <c r="H321" t="s">
         <v>1032</v>
       </c>
     </row>
@@ -11157,10 +11134,10 @@
       <c r="C322" t="s">
         <v>1033</v>
       </c>
-      <c r="D322" s="2" t="s">
+      <c r="D322" t="s">
         <v>1034</v>
       </c>
-      <c r="G322" s="2" t="s">
+      <c r="G322" t="s">
         <v>1035</v>
       </c>
     </row>
@@ -11171,10 +11148,10 @@
       <c r="C323" t="s">
         <v>1036</v>
       </c>
-      <c r="E323" s="2" t="s">
+      <c r="E323" t="s">
         <v>1037</v>
       </c>
-      <c r="H323" s="2" t="s">
+      <c r="H323" t="s">
         <v>1038</v>
       </c>
       <c r="J323" t="s">
@@ -11191,10 +11168,10 @@
       <c r="C324" t="s">
         <v>1039</v>
       </c>
-      <c r="E324" s="2" t="s">
+      <c r="E324" t="s">
         <v>1040</v>
       </c>
-      <c r="H324" s="2" t="s">
+      <c r="H324" t="s">
         <v>1041</v>
       </c>
     </row>
@@ -11208,10 +11185,10 @@
       <c r="C325" t="s">
         <v>1042</v>
       </c>
-      <c r="E325" s="2" t="s">
+      <c r="E325" t="s">
         <v>1043</v>
       </c>
-      <c r="H325" s="2" t="s">
+      <c r="H325" t="s">
         <v>1044</v>
       </c>
     </row>
@@ -11225,10 +11202,10 @@
       <c r="C326" t="s">
         <v>1045</v>
       </c>
-      <c r="E326" s="2" t="s">
+      <c r="E326" t="s">
         <v>1046</v>
       </c>
-      <c r="H326" s="2" t="s">
+      <c r="H326" t="s">
         <v>1047</v>
       </c>
     </row>
@@ -11239,10 +11216,10 @@
       <c r="C327" t="s">
         <v>1048</v>
       </c>
-      <c r="E327" s="2" t="s">
+      <c r="E327" t="s">
         <v>1049</v>
       </c>
-      <c r="H327" s="2" t="s">
+      <c r="H327" t="s">
         <v>1050</v>
       </c>
       <c r="J327" t="s">
@@ -11259,10 +11236,10 @@
       <c r="C328" t="s">
         <v>1051</v>
       </c>
-      <c r="E328" s="2" t="s">
+      <c r="E328" t="s">
         <v>1052</v>
       </c>
-      <c r="H328" s="2" t="s">
+      <c r="H328" t="s">
         <v>1053</v>
       </c>
     </row>
@@ -11276,50 +11253,50 @@
       <c r="C329" t="s">
         <v>1054</v>
       </c>
-      <c r="E329" s="2" t="s">
+      <c r="E329" t="s">
         <v>1055</v>
       </c>
-      <c r="H329" s="2" t="s">
+      <c r="H329" t="s">
         <v>1056</v>
       </c>
     </row>
-    <row r="330" spans="1:10" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B330">
         <v>4</v>
       </c>
       <c r="C330" t="s">
         <v>1057</v>
       </c>
-      <c r="D330" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E330" s="2" t="s">
+      <c r="D330" t="s">
+        <v>152</v>
+      </c>
+      <c r="E330" t="s">
         <v>1058</v>
       </c>
-      <c r="G330" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H330" s="2" t="s">
+      <c r="G330" t="s">
+        <v>152</v>
+      </c>
+      <c r="H330" t="s">
         <v>1059</v>
       </c>
     </row>
-    <row r="331" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B331">
         <v>2</v>
       </c>
       <c r="C331" t="s">
         <v>1060</v>
       </c>
-      <c r="D331" s="2" t="s">
+      <c r="D331" t="s">
         <v>1061</v>
       </c>
-      <c r="E331" s="2" t="s">
+      <c r="E331" t="s">
         <v>1062</v>
       </c>
-      <c r="G331" s="2" t="s">
+      <c r="G331" t="s">
         <v>1063</v>
       </c>
-      <c r="H331" s="2" t="s">
+      <c r="H331" t="s">
         <v>1064</v>
       </c>
     </row>
@@ -11330,10 +11307,10 @@
       <c r="C332" t="s">
         <v>1065</v>
       </c>
-      <c r="D332" s="2" t="s">
+      <c r="D332" t="s">
         <v>1066</v>
       </c>
-      <c r="G332" s="2" t="s">
+      <c r="G332" t="s">
         <v>1067</v>
       </c>
     </row>
@@ -11347,10 +11324,10 @@
       <c r="C333" t="s">
         <v>1068</v>
       </c>
-      <c r="E333" s="2" t="s">
+      <c r="E333" t="s">
         <v>1069</v>
       </c>
-      <c r="H333" s="2" t="s">
+      <c r="H333" t="s">
         <v>1070</v>
       </c>
     </row>
@@ -11364,10 +11341,10 @@
       <c r="C334" t="s">
         <v>1071</v>
       </c>
-      <c r="E334" s="2" t="s">
+      <c r="E334" t="s">
         <v>1072</v>
       </c>
-      <c r="H334" s="2" t="s">
+      <c r="H334" t="s">
         <v>1073</v>
       </c>
     </row>
@@ -11381,10 +11358,10 @@
       <c r="C335" t="s">
         <v>1074</v>
       </c>
-      <c r="E335" s="2" t="s">
+      <c r="E335" t="s">
         <v>1075</v>
       </c>
-      <c r="H335" s="2" t="s">
+      <c r="H335" t="s">
         <v>1076</v>
       </c>
     </row>
@@ -11398,30 +11375,30 @@
       <c r="C336" t="s">
         <v>1077</v>
       </c>
-      <c r="E336" s="2" t="s">
+      <c r="E336" t="s">
         <v>1078</v>
       </c>
-      <c r="H336" s="2" t="s">
+      <c r="H336" t="s">
         <v>1079</v>
       </c>
     </row>
-    <row r="337" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B337">
         <v>4</v>
       </c>
       <c r="C337" t="s">
         <v>1080</v>
       </c>
-      <c r="D337" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E337" s="2" t="s">
+      <c r="D337" t="s">
+        <v>152</v>
+      </c>
+      <c r="E337" t="s">
         <v>1081</v>
       </c>
-      <c r="G337" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H337" s="2" t="s">
+      <c r="G337" t="s">
+        <v>152</v>
+      </c>
+      <c r="H337" t="s">
         <v>1082</v>
       </c>
     </row>
@@ -11432,10 +11409,10 @@
       <c r="C338" t="s">
         <v>1083</v>
       </c>
-      <c r="D338" s="2" t="s">
+      <c r="D338" t="s">
         <v>1084</v>
       </c>
-      <c r="G338" s="2" t="s">
+      <c r="G338" t="s">
         <v>1085</v>
       </c>
     </row>
@@ -11449,14 +11426,14 @@
       <c r="C339" t="s">
         <v>1086</v>
       </c>
-      <c r="E339" s="2" t="s">
+      <c r="E339" t="s">
         <v>1087</v>
       </c>
-      <c r="H339" s="2" t="s">
+      <c r="H339" t="s">
         <v>1088</v>
       </c>
     </row>
-    <row r="340" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>87</v>
       </c>
@@ -11466,30 +11443,30 @@
       <c r="C340" t="s">
         <v>1089</v>
       </c>
-      <c r="E340" s="2" t="s">
+      <c r="E340" t="s">
         <v>1090</v>
       </c>
-      <c r="H340" s="2" t="s">
+      <c r="H340" t="s">
         <v>1091</v>
       </c>
     </row>
-    <row r="341" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B341">
         <v>4</v>
       </c>
       <c r="C341" t="s">
         <v>1092</v>
       </c>
-      <c r="D341" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E341" s="2" t="s">
+      <c r="D341" t="s">
+        <v>152</v>
+      </c>
+      <c r="E341" t="s">
         <v>1093</v>
       </c>
-      <c r="G341" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H341" s="2" t="s">
+      <c r="G341" t="s">
+        <v>152</v>
+      </c>
+      <c r="H341" t="s">
         <v>1094</v>
       </c>
     </row>
@@ -11500,10 +11477,10 @@
       <c r="C342" t="s">
         <v>1095</v>
       </c>
-      <c r="D342" s="2" t="s">
+      <c r="D342" t="s">
         <v>1096</v>
       </c>
-      <c r="G342" s="2" t="s">
+      <c r="G342" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -11517,10 +11494,10 @@
       <c r="C343" t="s">
         <v>1098</v>
       </c>
-      <c r="E343" s="2" t="s">
+      <c r="E343" t="s">
         <v>1099</v>
       </c>
-      <c r="H343" s="2" t="s">
+      <c r="H343" t="s">
         <v>1100</v>
       </c>
     </row>
@@ -11534,30 +11511,30 @@
       <c r="C344" t="s">
         <v>1101</v>
       </c>
-      <c r="E344" s="2" t="s">
+      <c r="E344" t="s">
         <v>1102</v>
       </c>
-      <c r="H344" s="2" t="s">
+      <c r="H344" t="s">
         <v>1103</v>
       </c>
     </row>
-    <row r="345" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B345">
         <v>4</v>
       </c>
       <c r="C345" t="s">
         <v>1104</v>
       </c>
-      <c r="D345" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E345" s="2" t="s">
+      <c r="D345" t="s">
+        <v>152</v>
+      </c>
+      <c r="E345" t="s">
         <v>1105</v>
       </c>
-      <c r="G345" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H345" s="2" t="s">
+      <c r="G345" t="s">
+        <v>152</v>
+      </c>
+      <c r="H345" t="s">
         <v>1106</v>
       </c>
     </row>
@@ -11568,10 +11545,10 @@
       <c r="C346" t="s">
         <v>1107</v>
       </c>
-      <c r="D346" s="2" t="s">
+      <c r="D346" t="s">
         <v>1108</v>
       </c>
-      <c r="G346" s="2" t="s">
+      <c r="G346" t="s">
         <v>1109</v>
       </c>
     </row>
@@ -11582,10 +11559,10 @@
       <c r="C347" t="s">
         <v>1110</v>
       </c>
-      <c r="E347" s="2" t="s">
+      <c r="E347" t="s">
         <v>1111</v>
       </c>
-      <c r="H347" s="2" t="s">
+      <c r="H347" t="s">
         <v>1112</v>
       </c>
       <c r="J347" t="s">
@@ -11602,10 +11579,10 @@
       <c r="C348" t="s">
         <v>1113</v>
       </c>
-      <c r="E348" s="2" t="s">
+      <c r="E348" t="s">
         <v>1114</v>
       </c>
-      <c r="H348" s="2" t="s">
+      <c r="H348" t="s">
         <v>1115</v>
       </c>
     </row>
@@ -11619,10 +11596,10 @@
       <c r="C349" t="s">
         <v>1116</v>
       </c>
-      <c r="E349" s="2" t="s">
+      <c r="E349" t="s">
         <v>1117</v>
       </c>
-      <c r="H349" s="2" t="s">
+      <c r="H349" t="s">
         <v>1118</v>
       </c>
     </row>
@@ -11636,10 +11613,10 @@
       <c r="C350" t="s">
         <v>1119</v>
       </c>
-      <c r="E350" s="2" t="s">
+      <c r="E350" t="s">
         <v>1120</v>
       </c>
-      <c r="H350" s="2" t="s">
+      <c r="H350" t="s">
         <v>1121</v>
       </c>
     </row>
@@ -11653,10 +11630,10 @@
       <c r="C351" t="s">
         <v>1122</v>
       </c>
-      <c r="E351" s="2" t="s">
+      <c r="E351" t="s">
         <v>1123</v>
       </c>
-      <c r="H351" s="2" t="s">
+      <c r="H351" t="s">
         <v>1124</v>
       </c>
     </row>
@@ -11670,10 +11647,10 @@
       <c r="C352" t="s">
         <v>1125</v>
       </c>
-      <c r="E352" s="2" t="s">
+      <c r="E352" t="s">
         <v>1126</v>
       </c>
-      <c r="H352" s="2" t="s">
+      <c r="H352" t="s">
         <v>1127</v>
       </c>
     </row>
@@ -11687,30 +11664,30 @@
       <c r="C353" t="s">
         <v>1128</v>
       </c>
-      <c r="E353" s="2" t="s">
+      <c r="E353" t="s">
         <v>1129</v>
       </c>
-      <c r="H353" s="2" t="s">
+      <c r="H353" t="s">
         <v>1130</v>
       </c>
     </row>
-    <row r="354" spans="1:8" ht="216" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B354">
         <v>4</v>
       </c>
       <c r="C354" t="s">
         <v>1131</v>
       </c>
-      <c r="D354" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E354" s="2" t="s">
+      <c r="D354" t="s">
+        <v>152</v>
+      </c>
+      <c r="E354" t="s">
         <v>1132</v>
       </c>
-      <c r="G354" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H354" s="2" t="s">
+      <c r="G354" t="s">
+        <v>152</v>
+      </c>
+      <c r="H354" t="s">
         <v>1133</v>
       </c>
     </row>
@@ -11721,10 +11698,10 @@
       <c r="C355" t="s">
         <v>1134</v>
       </c>
-      <c r="D355" s="2" t="s">
+      <c r="D355" t="s">
         <v>1135</v>
       </c>
-      <c r="G355" s="2" t="s">
+      <c r="G355" t="s">
         <v>1136</v>
       </c>
     </row>
@@ -11738,50 +11715,50 @@
       <c r="C356" t="s">
         <v>1137</v>
       </c>
-      <c r="E356" s="2" t="s">
+      <c r="E356" t="s">
         <v>1138</v>
       </c>
-      <c r="H356" s="2" t="s">
+      <c r="H356" t="s">
         <v>1139</v>
       </c>
     </row>
-    <row r="357" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B357">
         <v>4</v>
       </c>
       <c r="C357" t="s">
         <v>1140</v>
       </c>
-      <c r="D357" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E357" s="2" t="s">
+      <c r="D357" t="s">
+        <v>152</v>
+      </c>
+      <c r="E357" t="s">
         <v>1141</v>
       </c>
-      <c r="G357" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H357" s="2" t="s">
+      <c r="G357" t="s">
+        <v>152</v>
+      </c>
+      <c r="H357" t="s">
         <v>1142</v>
       </c>
     </row>
-    <row r="358" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B358">
         <v>2</v>
       </c>
       <c r="C358" t="s">
         <v>1143</v>
       </c>
-      <c r="D358" s="2" t="s">
+      <c r="D358" t="s">
         <v>1144</v>
       </c>
-      <c r="E358" s="2" t="s">
+      <c r="E358" t="s">
         <v>1145</v>
       </c>
-      <c r="G358" s="2" t="s">
+      <c r="G358" t="s">
         <v>1146</v>
       </c>
-      <c r="H358" s="2" t="s">
+      <c r="H358" t="s">
         <v>1147</v>
       </c>
     </row>
@@ -11792,14 +11769,14 @@
       <c r="C359" t="s">
         <v>1148</v>
       </c>
-      <c r="D359" s="2" t="s">
+      <c r="D359" t="s">
         <v>1144</v>
       </c>
-      <c r="G359" s="2" t="s">
+      <c r="G359" t="s">
         <v>1146</v>
       </c>
     </row>
-    <row r="360" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>87</v>
       </c>
@@ -11809,10 +11786,10 @@
       <c r="C360" t="s">
         <v>1149</v>
       </c>
-      <c r="E360" s="2" t="s">
+      <c r="E360" t="s">
         <v>1150</v>
       </c>
-      <c r="H360" s="2" t="s">
+      <c r="H360" t="s">
         <v>1151</v>
       </c>
     </row>
@@ -11826,30 +11803,30 @@
       <c r="C361" t="s">
         <v>1152</v>
       </c>
-      <c r="E361" s="2" t="s">
+      <c r="E361" t="s">
         <v>1153</v>
       </c>
-      <c r="H361" s="2" t="s">
+      <c r="H361" t="s">
         <v>1154</v>
       </c>
     </row>
-    <row r="362" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B362">
         <v>4</v>
       </c>
       <c r="C362" t="s">
         <v>1155</v>
       </c>
-      <c r="D362" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E362" s="2" t="s">
+      <c r="D362" t="s">
+        <v>152</v>
+      </c>
+      <c r="E362" t="s">
         <v>1156</v>
       </c>
-      <c r="G362" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H362" s="2" t="s">
+      <c r="G362" t="s">
+        <v>152</v>
+      </c>
+      <c r="H362" t="s">
         <v>1157</v>
       </c>
     </row>
@@ -11860,14 +11837,14 @@
       <c r="C363" t="s">
         <v>1158</v>
       </c>
-      <c r="D363" s="2" t="s">
+      <c r="D363" t="s">
         <v>1159</v>
       </c>
-      <c r="G363" s="2" t="s">
+      <c r="G363" t="s">
         <v>1160</v>
       </c>
     </row>
-    <row r="364" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>87</v>
       </c>
@@ -11877,10 +11854,10 @@
       <c r="C364" t="s">
         <v>1161</v>
       </c>
-      <c r="E364" s="2" t="s">
+      <c r="E364" t="s">
         <v>1162</v>
       </c>
-      <c r="H364" s="2" t="s">
+      <c r="H364" t="s">
         <v>1163</v>
       </c>
     </row>
@@ -11894,14 +11871,14 @@
       <c r="C365" t="s">
         <v>1164</v>
       </c>
-      <c r="E365" s="2" t="s">
+      <c r="E365" t="s">
         <v>1165</v>
       </c>
-      <c r="H365" s="2" t="s">
+      <c r="H365" t="s">
         <v>1166</v>
       </c>
     </row>
-    <row r="366" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>87</v>
       </c>
@@ -11911,30 +11888,30 @@
       <c r="C366" t="s">
         <v>1167</v>
       </c>
-      <c r="E366" s="2" t="s">
+      <c r="E366" t="s">
         <v>1168</v>
       </c>
-      <c r="H366" s="2" t="s">
+      <c r="H366" t="s">
         <v>1169</v>
       </c>
     </row>
-    <row r="367" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B367">
         <v>4</v>
       </c>
       <c r="C367" t="s">
         <v>1170</v>
       </c>
-      <c r="D367" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E367" s="2" t="s">
+      <c r="D367" t="s">
+        <v>152</v>
+      </c>
+      <c r="E367" t="s">
         <v>1171</v>
       </c>
-      <c r="G367" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H367" s="2" t="s">
+      <c r="G367" t="s">
+        <v>152</v>
+      </c>
+      <c r="H367" t="s">
         <v>1172</v>
       </c>
     </row>
@@ -11945,10 +11922,10 @@
       <c r="C368" t="s">
         <v>1173</v>
       </c>
-      <c r="D368" s="2" t="s">
+      <c r="D368" t="s">
         <v>1174</v>
       </c>
-      <c r="G368" s="2" t="s">
+      <c r="G368" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -11962,30 +11939,30 @@
       <c r="C369" t="s">
         <v>1176</v>
       </c>
-      <c r="E369" s="2" t="s">
+      <c r="E369" t="s">
         <v>1177</v>
       </c>
-      <c r="H369" s="2" t="s">
+      <c r="H369" t="s">
         <v>1178</v>
       </c>
     </row>
-    <row r="370" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B370">
         <v>4</v>
       </c>
       <c r="C370" t="s">
         <v>1179</v>
       </c>
-      <c r="D370" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E370" s="2" t="s">
+      <c r="D370" t="s">
+        <v>152</v>
+      </c>
+      <c r="E370" t="s">
         <v>1180</v>
       </c>
-      <c r="G370" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H370" s="2" t="s">
+      <c r="G370" t="s">
+        <v>152</v>
+      </c>
+      <c r="H370" t="s">
         <v>1181</v>
       </c>
     </row>
@@ -11996,16 +11973,16 @@
       <c r="C371" t="s">
         <v>1182</v>
       </c>
-      <c r="D371" s="2" t="s">
+      <c r="D371" t="s">
         <v>1183</v>
       </c>
-      <c r="E371" s="2" t="s">
+      <c r="E371" t="s">
         <v>1184</v>
       </c>
-      <c r="G371" s="2" t="s">
+      <c r="G371" t="s">
         <v>1185</v>
       </c>
-      <c r="H371" s="2" t="s">
+      <c r="H371" t="s">
         <v>1186</v>
       </c>
     </row>
@@ -12016,14 +11993,14 @@
       <c r="C372" t="s">
         <v>1187</v>
       </c>
-      <c r="D372" s="2" t="s">
+      <c r="D372" t="s">
         <v>1188</v>
       </c>
-      <c r="G372" s="2" t="s">
+      <c r="G372" t="s">
         <v>1189</v>
       </c>
     </row>
-    <row r="373" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>87</v>
       </c>
@@ -12033,30 +12010,30 @@
       <c r="C373" t="s">
         <v>1190</v>
       </c>
-      <c r="E373" s="2" t="s">
+      <c r="E373" t="s">
         <v>1191</v>
       </c>
-      <c r="H373" s="2" t="s">
+      <c r="H373" t="s">
         <v>1192</v>
       </c>
     </row>
-    <row r="374" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B374">
         <v>4</v>
       </c>
       <c r="C374" t="s">
         <v>1193</v>
       </c>
-      <c r="D374" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E374" s="2" t="s">
+      <c r="D374" t="s">
+        <v>152</v>
+      </c>
+      <c r="E374" t="s">
         <v>1194</v>
       </c>
-      <c r="G374" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H374" s="2" t="s">
+      <c r="G374" t="s">
+        <v>152</v>
+      </c>
+      <c r="H374" t="s">
         <v>1195</v>
       </c>
     </row>
@@ -12067,10 +12044,10 @@
       <c r="C375" t="s">
         <v>1196</v>
       </c>
-      <c r="D375" s="2" t="s">
+      <c r="D375" t="s">
         <v>1197</v>
       </c>
-      <c r="G375" s="2" t="s">
+      <c r="G375" t="s">
         <v>1198</v>
       </c>
     </row>
@@ -12081,10 +12058,10 @@
       <c r="C376" t="s">
         <v>1199</v>
       </c>
-      <c r="E376" s="2" t="s">
+      <c r="E376" t="s">
         <v>1200</v>
       </c>
-      <c r="H376" s="2" t="s">
+      <c r="H376" t="s">
         <v>1201</v>
       </c>
       <c r="J376" t="s">
@@ -12101,10 +12078,10 @@
       <c r="C377" t="s">
         <v>1202</v>
       </c>
-      <c r="E377" s="2" t="s">
+      <c r="E377" t="s">
         <v>1203</v>
       </c>
-      <c r="H377" s="2" t="s">
+      <c r="H377" t="s">
         <v>1204</v>
       </c>
     </row>
@@ -12118,10 +12095,10 @@
       <c r="C378" t="s">
         <v>1205</v>
       </c>
-      <c r="E378" s="2" t="s">
+      <c r="E378" t="s">
         <v>1206</v>
       </c>
-      <c r="H378" s="2" t="s">
+      <c r="H378" t="s">
         <v>1207</v>
       </c>
     </row>
@@ -12132,10 +12109,10 @@
       <c r="C379" t="s">
         <v>1208</v>
       </c>
-      <c r="E379" s="2" t="s">
+      <c r="E379" t="s">
         <v>1209</v>
       </c>
-      <c r="H379" s="2" t="s">
+      <c r="H379" t="s">
         <v>1210</v>
       </c>
       <c r="J379" t="s">
@@ -12152,10 +12129,10 @@
       <c r="C380" t="s">
         <v>1211</v>
       </c>
-      <c r="E380" s="2" t="s">
+      <c r="E380" t="s">
         <v>1212</v>
       </c>
-      <c r="H380" s="2" t="s">
+      <c r="H380" t="s">
         <v>1213</v>
       </c>
     </row>
@@ -12169,10 +12146,10 @@
       <c r="C381" t="s">
         <v>1214</v>
       </c>
-      <c r="E381" s="2" t="s">
+      <c r="E381" t="s">
         <v>1215</v>
       </c>
-      <c r="H381" s="2" t="s">
+      <c r="H381" t="s">
         <v>1216</v>
       </c>
     </row>
@@ -12186,30 +12163,30 @@
       <c r="C382" t="s">
         <v>1217</v>
       </c>
-      <c r="E382" s="2" t="s">
+      <c r="E382" t="s">
         <v>1218</v>
       </c>
-      <c r="H382" s="2" t="s">
+      <c r="H382" t="s">
         <v>1219</v>
       </c>
     </row>
-    <row r="383" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B383">
         <v>4</v>
       </c>
       <c r="C383" t="s">
         <v>1220</v>
       </c>
-      <c r="D383" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E383" s="2" t="s">
+      <c r="D383" t="s">
+        <v>152</v>
+      </c>
+      <c r="E383" t="s">
         <v>1221</v>
       </c>
-      <c r="G383" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H383" s="2" t="s">
+      <c r="G383" t="s">
+        <v>152</v>
+      </c>
+      <c r="H383" t="s">
         <v>1222</v>
       </c>
     </row>
@@ -12220,14 +12197,14 @@
       <c r="C384" t="s">
         <v>1223</v>
       </c>
-      <c r="D384" s="2" t="s">
+      <c r="D384" t="s">
         <v>1224</v>
       </c>
-      <c r="G384" s="2" t="s">
+      <c r="G384" t="s">
         <v>1225</v>
       </c>
     </row>
-    <row r="385" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>87</v>
       </c>
@@ -12237,30 +12214,30 @@
       <c r="C385" t="s">
         <v>1226</v>
       </c>
-      <c r="E385" s="2" t="s">
+      <c r="E385" t="s">
         <v>1227</v>
       </c>
-      <c r="H385" s="2" t="s">
+      <c r="H385" t="s">
         <v>1228</v>
       </c>
     </row>
-    <row r="386" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B386">
         <v>4</v>
       </c>
       <c r="C386" t="s">
         <v>1229</v>
       </c>
-      <c r="D386" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E386" s="2" t="s">
+      <c r="D386" t="s">
+        <v>152</v>
+      </c>
+      <c r="E386" t="s">
         <v>1230</v>
       </c>
-      <c r="G386" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H386" s="2" t="s">
+      <c r="G386" t="s">
+        <v>152</v>
+      </c>
+      <c r="H386" t="s">
         <v>1231</v>
       </c>
     </row>
@@ -12271,14 +12248,14 @@
       <c r="C387" t="s">
         <v>1232</v>
       </c>
-      <c r="D387" s="2" t="s">
+      <c r="D387" t="s">
         <v>1233</v>
       </c>
-      <c r="G387" s="2" t="s">
+      <c r="G387" t="s">
         <v>1234</v>
       </c>
     </row>
-    <row r="388" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>87</v>
       </c>
@@ -12288,14 +12265,14 @@
       <c r="C388" t="s">
         <v>1235</v>
       </c>
-      <c r="E388" s="2" t="s">
+      <c r="E388" t="s">
         <v>1236</v>
       </c>
-      <c r="H388" s="2" t="s">
+      <c r="H388" t="s">
         <v>1237</v>
       </c>
     </row>
-    <row r="389" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>87</v>
       </c>
@@ -12305,10 +12282,10 @@
       <c r="C389" t="s">
         <v>1238</v>
       </c>
-      <c r="E389" s="2" t="s">
+      <c r="E389" t="s">
         <v>1239</v>
       </c>
-      <c r="H389" s="2" t="s">
+      <c r="H389" t="s">
         <v>1240</v>
       </c>
     </row>
@@ -12322,50 +12299,50 @@
       <c r="C390" t="s">
         <v>1241</v>
       </c>
-      <c r="E390" s="2" t="s">
+      <c r="E390" t="s">
         <v>1242</v>
       </c>
-      <c r="H390" s="2" t="s">
+      <c r="H390" t="s">
         <v>1243</v>
       </c>
     </row>
-    <row r="391" spans="1:8" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B391">
         <v>4</v>
       </c>
       <c r="C391" t="s">
         <v>1244</v>
       </c>
-      <c r="D391" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E391" s="2" t="s">
+      <c r="D391" t="s">
+        <v>152</v>
+      </c>
+      <c r="E391" t="s">
         <v>1245</v>
       </c>
-      <c r="G391" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H391" s="2" t="s">
+      <c r="G391" t="s">
+        <v>152</v>
+      </c>
+      <c r="H391" t="s">
         <v>1246</v>
       </c>
     </row>
-    <row r="392" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B392">
         <v>2</v>
       </c>
       <c r="C392" t="s">
         <v>1247</v>
       </c>
-      <c r="D392" s="2" t="s">
+      <c r="D392" t="s">
         <v>1248</v>
       </c>
-      <c r="E392" s="2" t="s">
+      <c r="E392" t="s">
         <v>1249</v>
       </c>
-      <c r="G392" s="2" t="s">
+      <c r="G392" t="s">
         <v>1250</v>
       </c>
-      <c r="H392" s="2" t="s">
+      <c r="H392" t="s">
         <v>1251</v>
       </c>
     </row>
@@ -12376,14 +12353,14 @@
       <c r="C393" t="s">
         <v>1252</v>
       </c>
-      <c r="D393" s="2" t="s">
+      <c r="D393" t="s">
         <v>1253</v>
       </c>
-      <c r="G393" s="2" t="s">
+      <c r="G393" t="s">
         <v>1254</v>
       </c>
     </row>
-    <row r="394" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>87</v>
       </c>
@@ -12393,14 +12370,14 @@
       <c r="C394" t="s">
         <v>1255</v>
       </c>
-      <c r="E394" s="2" t="s">
+      <c r="E394" t="s">
         <v>1256</v>
       </c>
-      <c r="H394" s="2" t="s">
+      <c r="H394" t="s">
         <v>1257</v>
       </c>
     </row>
-    <row r="395" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>87</v>
       </c>
@@ -12410,14 +12387,14 @@
       <c r="C395" t="s">
         <v>1258</v>
       </c>
-      <c r="E395" s="2" t="s">
+      <c r="E395" t="s">
         <v>1259</v>
       </c>
-      <c r="H395" s="2" t="s">
+      <c r="H395" t="s">
         <v>1260</v>
       </c>
     </row>
-    <row r="396" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>87</v>
       </c>
@@ -12427,30 +12404,30 @@
       <c r="C396" t="s">
         <v>1261</v>
       </c>
-      <c r="E396" s="2" t="s">
+      <c r="E396" t="s">
         <v>1262</v>
       </c>
-      <c r="H396" s="2" t="s">
+      <c r="H396" t="s">
         <v>1263</v>
       </c>
     </row>
-    <row r="397" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B397">
         <v>4</v>
       </c>
       <c r="C397" t="s">
         <v>1264</v>
       </c>
-      <c r="D397" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E397" s="2" t="s">
+      <c r="D397" t="s">
+        <v>152</v>
+      </c>
+      <c r="E397" t="s">
         <v>1265</v>
       </c>
-      <c r="G397" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H397" s="2" t="s">
+      <c r="G397" t="s">
+        <v>152</v>
+      </c>
+      <c r="H397" t="s">
         <v>1266</v>
       </c>
     </row>
@@ -12461,10 +12438,10 @@
       <c r="C398" t="s">
         <v>1267</v>
       </c>
-      <c r="D398" s="2" t="s">
+      <c r="D398" t="s">
         <v>1268</v>
       </c>
-      <c r="G398" s="2" t="s">
+      <c r="G398" t="s">
         <v>1269</v>
       </c>
     </row>
@@ -12478,44 +12455,44 @@
       <c r="C399" t="s">
         <v>1270</v>
       </c>
-      <c r="E399" s="2" t="s">
+      <c r="E399" t="s">
         <v>1271</v>
       </c>
-      <c r="H399" s="2" t="s">
+      <c r="H399" t="s">
         <v>1272</v>
       </c>
     </row>
-    <row r="400" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B400">
         <v>4</v>
       </c>
       <c r="C400" t="s">
         <v>1273</v>
       </c>
-      <c r="D400" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E400" s="2" t="s">
+      <c r="D400" t="s">
+        <v>152</v>
+      </c>
+      <c r="E400" t="s">
         <v>1274</v>
       </c>
-      <c r="G400" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H400" s="2" t="s">
+      <c r="G400" t="s">
+        <v>152</v>
+      </c>
+      <c r="H400" t="s">
         <v>1275</v>
       </c>
     </row>
-    <row r="401" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B401">
         <v>3</v>
       </c>
       <c r="C401" t="s">
         <v>1276</v>
       </c>
-      <c r="D401" s="2" t="s">
+      <c r="D401" t="s">
         <v>1277</v>
       </c>
-      <c r="G401" s="2" t="s">
+      <c r="G401" t="s">
         <v>1278</v>
       </c>
     </row>
@@ -12529,30 +12506,30 @@
       <c r="C402" t="s">
         <v>1279</v>
       </c>
-      <c r="E402" s="2" t="s">
+      <c r="E402" t="s">
         <v>1280</v>
       </c>
-      <c r="H402" s="2" t="s">
+      <c r="H402" t="s">
         <v>1281</v>
       </c>
     </row>
-    <row r="403" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B403">
         <v>4</v>
       </c>
       <c r="C403" t="s">
         <v>1282</v>
       </c>
-      <c r="D403" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E403" s="2" t="s">
+      <c r="D403" t="s">
+        <v>152</v>
+      </c>
+      <c r="E403" t="s">
         <v>1283</v>
       </c>
-      <c r="G403" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H403" s="2" t="s">
+      <c r="G403" t="s">
+        <v>152</v>
+      </c>
+      <c r="H403" t="s">
         <v>1284</v>
       </c>
     </row>
@@ -12563,14 +12540,14 @@
       <c r="C404" t="s">
         <v>1285</v>
       </c>
-      <c r="D404" s="2" t="s">
+      <c r="D404" t="s">
         <v>1286</v>
       </c>
-      <c r="G404" s="2" t="s">
+      <c r="G404" t="s">
         <v>1287</v>
       </c>
     </row>
-    <row r="405" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>87</v>
       </c>
@@ -12580,30 +12557,30 @@
       <c r="C405" t="s">
         <v>1288</v>
       </c>
-      <c r="E405" s="2" t="s">
+      <c r="E405" t="s">
         <v>1289</v>
       </c>
-      <c r="H405" s="2" t="s">
+      <c r="H405" t="s">
         <v>1290</v>
       </c>
     </row>
-    <row r="406" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B406">
         <v>4</v>
       </c>
       <c r="C406" t="s">
         <v>1291</v>
       </c>
-      <c r="D406" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E406" s="2" t="s">
+      <c r="D406" t="s">
+        <v>152</v>
+      </c>
+      <c r="E406" t="s">
         <v>1292</v>
       </c>
-      <c r="G406" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H406" s="2" t="s">
+      <c r="G406" t="s">
+        <v>152</v>
+      </c>
+      <c r="H406" t="s">
         <v>1293</v>
       </c>
     </row>
@@ -12614,14 +12591,14 @@
       <c r="C407" t="s">
         <v>1294</v>
       </c>
-      <c r="D407" s="2" t="s">
+      <c r="D407" t="s">
         <v>1295</v>
       </c>
-      <c r="G407" s="2" t="s">
+      <c r="G407" t="s">
         <v>1296</v>
       </c>
     </row>
-    <row r="408" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>87</v>
       </c>
@@ -12631,30 +12608,30 @@
       <c r="C408" t="s">
         <v>1297</v>
       </c>
-      <c r="E408" s="2" t="s">
+      <c r="E408" t="s">
         <v>1298</v>
       </c>
-      <c r="H408" s="2" t="s">
+      <c r="H408" t="s">
         <v>1299</v>
       </c>
     </row>
-    <row r="409" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B409">
         <v>4</v>
       </c>
       <c r="C409" t="s">
         <v>1300</v>
       </c>
-      <c r="D409" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E409" s="2" t="s">
+      <c r="D409" t="s">
+        <v>152</v>
+      </c>
+      <c r="E409" t="s">
         <v>1301</v>
       </c>
-      <c r="G409" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H409" s="2" t="s">
+      <c r="G409" t="s">
+        <v>152</v>
+      </c>
+      <c r="H409" t="s">
         <v>1302</v>
       </c>
     </row>
@@ -12665,14 +12642,14 @@
       <c r="C410" t="s">
         <v>1303</v>
       </c>
-      <c r="D410" s="2" t="s">
+      <c r="D410" t="s">
         <v>1304</v>
       </c>
-      <c r="G410" s="2" t="s">
+      <c r="G410" t="s">
         <v>1305</v>
       </c>
     </row>
-    <row r="411" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>87</v>
       </c>
@@ -12682,30 +12659,30 @@
       <c r="C411" t="s">
         <v>1306</v>
       </c>
-      <c r="E411" s="2" t="s">
+      <c r="E411" t="s">
         <v>1307</v>
       </c>
-      <c r="H411" s="2" t="s">
+      <c r="H411" t="s">
         <v>1308</v>
       </c>
     </row>
-    <row r="412" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B412">
         <v>4</v>
       </c>
       <c r="C412" t="s">
         <v>1309</v>
       </c>
-      <c r="D412" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E412" s="2" t="s">
+      <c r="D412" t="s">
+        <v>152</v>
+      </c>
+      <c r="E412" t="s">
         <v>1310</v>
       </c>
-      <c r="G412" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H412" s="2" t="s">
+      <c r="G412" t="s">
+        <v>152</v>
+      </c>
+      <c r="H412" t="s">
         <v>1311</v>
       </c>
     </row>
@@ -12716,14 +12693,14 @@
       <c r="C413" t="s">
         <v>1312</v>
       </c>
-      <c r="D413" s="2" t="s">
+      <c r="D413" t="s">
         <v>1313</v>
       </c>
-      <c r="G413" s="2" t="s">
+      <c r="G413" t="s">
         <v>1314</v>
       </c>
     </row>
-    <row r="414" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>87</v>
       </c>
@@ -12733,30 +12710,30 @@
       <c r="C414" t="s">
         <v>1315</v>
       </c>
-      <c r="E414" s="2" t="s">
+      <c r="E414" t="s">
         <v>1316</v>
       </c>
-      <c r="H414" s="2" t="s">
+      <c r="H414" t="s">
         <v>1317</v>
       </c>
     </row>
-    <row r="415" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B415">
         <v>4</v>
       </c>
       <c r="C415" t="s">
         <v>1318</v>
       </c>
-      <c r="D415" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E415" s="2" t="s">
+      <c r="D415" t="s">
+        <v>152</v>
+      </c>
+      <c r="E415" t="s">
         <v>1319</v>
       </c>
-      <c r="G415" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H415" s="2" t="s">
+      <c r="G415" t="s">
+        <v>152</v>
+      </c>
+      <c r="H415" t="s">
         <v>1320</v>
       </c>
     </row>
@@ -12767,14 +12744,14 @@
       <c r="C416" t="s">
         <v>1321</v>
       </c>
-      <c r="D416" s="2" t="s">
+      <c r="D416" t="s">
         <v>1322</v>
       </c>
-      <c r="G416" s="2" t="s">
+      <c r="G416" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="417" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>87</v>
       </c>
@@ -12784,10 +12761,10 @@
       <c r="C417" t="s">
         <v>1324</v>
       </c>
-      <c r="E417" s="2" t="s">
+      <c r="E417" t="s">
         <v>1325</v>
       </c>
-      <c r="H417" s="2" t="s">
+      <c r="H417" t="s">
         <v>1326</v>
       </c>
     </row>
@@ -12801,30 +12778,30 @@
       <c r="C418" t="s">
         <v>1327</v>
       </c>
-      <c r="E418" s="2" t="s">
+      <c r="E418" t="s">
         <v>1328</v>
       </c>
-      <c r="H418" s="2" t="s">
+      <c r="H418" t="s">
         <v>1329</v>
       </c>
     </row>
-    <row r="419" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B419">
         <v>4</v>
       </c>
       <c r="C419" t="s">
         <v>1330</v>
       </c>
-      <c r="D419" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E419" s="2" t="s">
+      <c r="D419" t="s">
+        <v>152</v>
+      </c>
+      <c r="E419" t="s">
         <v>1331</v>
       </c>
-      <c r="G419" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H419" s="2" t="s">
+      <c r="G419" t="s">
+        <v>152</v>
+      </c>
+      <c r="H419" t="s">
         <v>1332</v>
       </c>
     </row>
@@ -12835,10 +12812,10 @@
       <c r="C420" t="s">
         <v>1333</v>
       </c>
-      <c r="D420" s="2" t="s">
+      <c r="D420" t="s">
         <v>1334</v>
       </c>
-      <c r="G420" s="2" t="s">
+      <c r="G420" t="s">
         <v>1335</v>
       </c>
     </row>
@@ -12852,10 +12829,10 @@
       <c r="C421" t="s">
         <v>1336</v>
       </c>
-      <c r="E421" s="2" t="s">
+      <c r="E421" t="s">
         <v>1337</v>
       </c>
-      <c r="H421" s="2" t="s">
+      <c r="H421" t="s">
         <v>1338</v>
       </c>
     </row>
@@ -12869,30 +12846,30 @@
       <c r="C422" t="s">
         <v>1339</v>
       </c>
-      <c r="E422" s="2" t="s">
+      <c r="E422" t="s">
         <v>1340</v>
       </c>
-      <c r="H422" s="2" t="s">
+      <c r="H422" t="s">
         <v>1341</v>
       </c>
     </row>
-    <row r="423" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B423">
         <v>4</v>
       </c>
       <c r="C423" t="s">
         <v>1342</v>
       </c>
-      <c r="D423" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E423" s="2" t="s">
+      <c r="D423" t="s">
+        <v>152</v>
+      </c>
+      <c r="E423" t="s">
         <v>1343</v>
       </c>
-      <c r="G423" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H423" s="2" t="s">
+      <c r="G423" t="s">
+        <v>152</v>
+      </c>
+      <c r="H423" t="s">
         <v>1344</v>
       </c>
     </row>
@@ -12903,10 +12880,10 @@
       <c r="C424" t="s">
         <v>1345</v>
       </c>
-      <c r="D424" s="2" t="s">
+      <c r="D424" t="s">
         <v>1346</v>
       </c>
-      <c r="G424" s="2" t="s">
+      <c r="G424" t="s">
         <v>1347</v>
       </c>
     </row>
@@ -12920,50 +12897,50 @@
       <c r="C425" t="s">
         <v>1348</v>
       </c>
-      <c r="E425" s="2" t="s">
+      <c r="E425" t="s">
         <v>1349</v>
       </c>
-      <c r="H425" s="2" t="s">
+      <c r="H425" t="s">
         <v>1350</v>
       </c>
     </row>
-    <row r="426" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B426">
         <v>4</v>
       </c>
       <c r="C426" t="s">
         <v>1351</v>
       </c>
-      <c r="D426" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E426" s="2" t="s">
+      <c r="D426" t="s">
+        <v>152</v>
+      </c>
+      <c r="E426" t="s">
         <v>1352</v>
       </c>
-      <c r="G426" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H426" s="2" t="s">
+      <c r="G426" t="s">
+        <v>152</v>
+      </c>
+      <c r="H426" t="s">
         <v>1353</v>
       </c>
     </row>
-    <row r="427" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B427">
         <v>2</v>
       </c>
       <c r="C427" t="s">
         <v>1354</v>
       </c>
-      <c r="D427" s="2" t="s">
+      <c r="D427" t="s">
         <v>1355</v>
       </c>
-      <c r="E427" s="2" t="s">
+      <c r="E427" t="s">
         <v>1356</v>
       </c>
-      <c r="G427" s="2" t="s">
+      <c r="G427" t="s">
         <v>1357</v>
       </c>
-      <c r="H427" s="2" t="s">
+      <c r="H427" t="s">
         <v>1358</v>
       </c>
     </row>
@@ -12974,10 +12951,10 @@
       <c r="C428" t="s">
         <v>1359</v>
       </c>
-      <c r="D428" s="2" t="s">
+      <c r="D428" t="s">
         <v>1360</v>
       </c>
-      <c r="G428" s="2" t="s">
+      <c r="G428" t="s">
         <v>1361</v>
       </c>
     </row>
@@ -12991,14 +12968,14 @@
       <c r="C429" t="s">
         <v>1362</v>
       </c>
-      <c r="E429" s="2" t="s">
+      <c r="E429" t="s">
         <v>1363</v>
       </c>
-      <c r="H429" s="2" t="s">
+      <c r="H429" t="s">
         <v>1364</v>
       </c>
     </row>
-    <row r="430" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>87</v>
       </c>
@@ -13008,30 +12985,30 @@
       <c r="C430" t="s">
         <v>1365</v>
       </c>
-      <c r="E430" s="2" t="s">
+      <c r="E430" t="s">
         <v>1366</v>
       </c>
-      <c r="H430" s="2" t="s">
+      <c r="H430" t="s">
         <v>1367</v>
       </c>
     </row>
-    <row r="431" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B431">
         <v>4</v>
       </c>
       <c r="C431" t="s">
         <v>1368</v>
       </c>
-      <c r="D431" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E431" s="2" t="s">
+      <c r="D431" t="s">
+        <v>152</v>
+      </c>
+      <c r="E431" t="s">
         <v>1369</v>
       </c>
-      <c r="G431" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H431" s="2" t="s">
+      <c r="G431" t="s">
+        <v>152</v>
+      </c>
+      <c r="H431" t="s">
         <v>1370</v>
       </c>
     </row>
@@ -13042,14 +13019,14 @@
       <c r="C432" t="s">
         <v>1371</v>
       </c>
-      <c r="D432" s="2" t="s">
+      <c r="D432" t="s">
         <v>1372</v>
       </c>
-      <c r="G432" s="2" t="s">
+      <c r="G432" t="s">
         <v>1373</v>
       </c>
     </row>
-    <row r="433" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>87</v>
       </c>
@@ -13059,14 +13036,14 @@
       <c r="C433" t="s">
         <v>1374</v>
       </c>
-      <c r="E433" s="2" t="s">
+      <c r="E433" t="s">
         <v>1375</v>
       </c>
-      <c r="H433" s="2" t="s">
+      <c r="H433" t="s">
         <v>1376</v>
       </c>
     </row>
-    <row r="434" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>87</v>
       </c>
@@ -13076,10 +13053,10 @@
       <c r="C434" t="s">
         <v>1377</v>
       </c>
-      <c r="E434" s="2" t="s">
+      <c r="E434" t="s">
         <v>1378</v>
       </c>
-      <c r="H434" s="2" t="s">
+      <c r="H434" t="s">
         <v>1379</v>
       </c>
     </row>
@@ -13090,17 +13067,17 @@
       <c r="C435" t="s">
         <v>1380</v>
       </c>
-      <c r="E435" s="2" t="s">
+      <c r="E435" t="s">
         <v>1381</v>
       </c>
-      <c r="H435" s="2" t="s">
+      <c r="H435" t="s">
         <v>1382</v>
       </c>
       <c r="J435" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="436" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>87</v>
       </c>
@@ -13110,14 +13087,14 @@
       <c r="C436" t="s">
         <v>1383</v>
       </c>
-      <c r="E436" s="2" t="s">
+      <c r="E436" t="s">
         <v>1384</v>
       </c>
-      <c r="H436" s="2" t="s">
+      <c r="H436" t="s">
         <v>1385</v>
       </c>
     </row>
-    <row r="437" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>87</v>
       </c>
@@ -13127,30 +13104,30 @@
       <c r="C437" t="s">
         <v>1386</v>
       </c>
-      <c r="E437" s="2" t="s">
+      <c r="E437" t="s">
         <v>1387</v>
       </c>
-      <c r="H437" s="2" t="s">
+      <c r="H437" t="s">
         <v>1388</v>
       </c>
     </row>
-    <row r="438" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B438">
         <v>4</v>
       </c>
       <c r="C438" t="s">
         <v>1389</v>
       </c>
-      <c r="D438" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E438" s="2" t="s">
+      <c r="D438" t="s">
+        <v>152</v>
+      </c>
+      <c r="E438" t="s">
         <v>1390</v>
       </c>
-      <c r="G438" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H438" s="2" t="s">
+      <c r="G438" t="s">
+        <v>152</v>
+      </c>
+      <c r="H438" t="s">
         <v>1391</v>
       </c>
     </row>
@@ -13161,10 +13138,10 @@
       <c r="C439" t="s">
         <v>1392</v>
       </c>
-      <c r="D439" s="2" t="s">
+      <c r="D439" t="s">
         <v>1393</v>
       </c>
-      <c r="G439" s="2" t="s">
+      <c r="G439" t="s">
         <v>1394</v>
       </c>
     </row>
@@ -13178,10 +13155,10 @@
       <c r="C440" t="s">
         <v>1395</v>
       </c>
-      <c r="E440" s="2" t="s">
+      <c r="E440" t="s">
         <v>1396</v>
       </c>
-      <c r="H440" s="2" t="s">
+      <c r="H440" t="s">
         <v>1397</v>
       </c>
     </row>
@@ -13195,30 +13172,30 @@
       <c r="C441" t="s">
         <v>1398</v>
       </c>
-      <c r="E441" s="2" t="s">
+      <c r="E441" t="s">
         <v>1399</v>
       </c>
-      <c r="H441" s="2" t="s">
+      <c r="H441" t="s">
         <v>1400</v>
       </c>
     </row>
-    <row r="442" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B442">
         <v>4</v>
       </c>
       <c r="C442" t="s">
         <v>1401</v>
       </c>
-      <c r="D442" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E442" s="2" t="s">
+      <c r="D442" t="s">
+        <v>152</v>
+      </c>
+      <c r="E442" t="s">
         <v>1402</v>
       </c>
-      <c r="G442" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H442" s="2" t="s">
+      <c r="G442" t="s">
+        <v>152</v>
+      </c>
+      <c r="H442" t="s">
         <v>1403</v>
       </c>
     </row>
@@ -13229,10 +13206,10 @@
       <c r="C443" t="s">
         <v>1404</v>
       </c>
-      <c r="D443" s="2" t="s">
+      <c r="D443" t="s">
         <v>1405</v>
       </c>
-      <c r="G443" s="2" t="s">
+      <c r="G443" t="s">
         <v>1406</v>
       </c>
     </row>
@@ -13243,10 +13220,10 @@
       <c r="C444" t="s">
         <v>1407</v>
       </c>
-      <c r="E444" s="2" t="s">
+      <c r="E444" t="s">
         <v>1408</v>
       </c>
-      <c r="H444" s="2" t="s">
+      <c r="H444" t="s">
         <v>1409</v>
       </c>
       <c r="J444" t="s">
@@ -13263,10 +13240,10 @@
       <c r="C445" t="s">
         <v>1410</v>
       </c>
-      <c r="E445" s="2" t="s">
+      <c r="E445" t="s">
         <v>1411</v>
       </c>
-      <c r="H445" s="2" t="s">
+      <c r="H445" t="s">
         <v>1412</v>
       </c>
     </row>
@@ -13280,10 +13257,10 @@
       <c r="C446" t="s">
         <v>1413</v>
       </c>
-      <c r="E446" s="2" t="s">
+      <c r="E446" t="s">
         <v>1414</v>
       </c>
-      <c r="H446" s="2" t="s">
+      <c r="H446" t="s">
         <v>1415</v>
       </c>
     </row>
@@ -13297,10 +13274,10 @@
       <c r="C447" t="s">
         <v>1416</v>
       </c>
-      <c r="E447" s="2" t="s">
+      <c r="E447" t="s">
         <v>1417</v>
       </c>
-      <c r="H447" s="2" t="s">
+      <c r="H447" t="s">
         <v>1418</v>
       </c>
     </row>
@@ -13314,30 +13291,30 @@
       <c r="C448" t="s">
         <v>1419</v>
       </c>
-      <c r="E448" s="2" t="s">
+      <c r="E448" t="s">
         <v>1420</v>
       </c>
-      <c r="H448" s="2" t="s">
+      <c r="H448" t="s">
         <v>1421</v>
       </c>
     </row>
-    <row r="449" spans="1:10" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B449">
         <v>4</v>
       </c>
       <c r="C449" t="s">
         <v>1422</v>
       </c>
-      <c r="D449" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E449" s="2" t="s">
+      <c r="D449" t="s">
+        <v>152</v>
+      </c>
+      <c r="E449" t="s">
         <v>1423</v>
       </c>
-      <c r="G449" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H449" s="2" t="s">
+      <c r="G449" t="s">
+        <v>152</v>
+      </c>
+      <c r="H449" t="s">
         <v>1424</v>
       </c>
     </row>
@@ -13348,14 +13325,14 @@
       <c r="C450" t="s">
         <v>1425</v>
       </c>
-      <c r="D450" s="2" t="s">
+      <c r="D450" t="s">
         <v>1426</v>
       </c>
-      <c r="G450" s="2" t="s">
+      <c r="G450" t="s">
         <v>1427</v>
       </c>
     </row>
-    <row r="451" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>87</v>
       </c>
@@ -13365,30 +13342,30 @@
       <c r="C451" t="s">
         <v>1428</v>
       </c>
-      <c r="E451" s="2" t="s">
+      <c r="E451" t="s">
         <v>1429</v>
       </c>
-      <c r="H451" s="2" t="s">
+      <c r="H451" t="s">
         <v>1430</v>
       </c>
     </row>
-    <row r="452" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B452">
         <v>4</v>
       </c>
       <c r="C452" t="s">
         <v>1431</v>
       </c>
-      <c r="D452" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E452" s="2" t="s">
+      <c r="D452" t="s">
+        <v>152</v>
+      </c>
+      <c r="E452" t="s">
         <v>1432</v>
       </c>
-      <c r="G452" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H452" s="2" t="s">
+      <c r="G452" t="s">
+        <v>152</v>
+      </c>
+      <c r="H452" t="s">
         <v>1433</v>
       </c>
     </row>
@@ -13399,14 +13376,14 @@
       <c r="C453" t="s">
         <v>1434</v>
       </c>
-      <c r="D453" s="2" t="s">
+      <c r="D453" t="s">
         <v>1435</v>
       </c>
-      <c r="G453" s="2" t="s">
+      <c r="G453" t="s">
         <v>1436</v>
       </c>
     </row>
-    <row r="454" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>87</v>
       </c>
@@ -13416,14 +13393,14 @@
       <c r="C454" t="s">
         <v>1437</v>
       </c>
-      <c r="E454" s="2" t="s">
+      <c r="E454" t="s">
         <v>213</v>
       </c>
-      <c r="H454" s="2" t="s">
+      <c r="H454" t="s">
         <v>1438</v>
       </c>
     </row>
-    <row r="455" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>87</v>
       </c>
@@ -13433,14 +13410,14 @@
       <c r="C455" t="s">
         <v>1439</v>
       </c>
-      <c r="E455" s="2" t="s">
+      <c r="E455" t="s">
         <v>1440</v>
       </c>
-      <c r="H455" s="2" t="s">
+      <c r="H455" t="s">
         <v>1441</v>
       </c>
     </row>
-    <row r="456" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>87</v>
       </c>
@@ -13450,50 +13427,50 @@
       <c r="C456" t="s">
         <v>1442</v>
       </c>
-      <c r="E456" s="2" t="s">
+      <c r="E456" t="s">
         <v>1443</v>
       </c>
-      <c r="H456" s="2" t="s">
+      <c r="H456" t="s">
         <v>1444</v>
       </c>
     </row>
-    <row r="457" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B457">
         <v>4</v>
       </c>
       <c r="C457" t="s">
         <v>1445</v>
       </c>
-      <c r="D457" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E457" s="2" t="s">
+      <c r="D457" t="s">
+        <v>152</v>
+      </c>
+      <c r="E457" t="s">
         <v>1446</v>
       </c>
-      <c r="G457" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H457" s="2" t="s">
+      <c r="G457" t="s">
+        <v>152</v>
+      </c>
+      <c r="H457" t="s">
         <v>1447</v>
       </c>
     </row>
-    <row r="458" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B458">
         <v>2</v>
       </c>
       <c r="C458" t="s">
         <v>1448</v>
       </c>
-      <c r="D458" s="2" t="s">
+      <c r="D458" t="s">
         <v>1449</v>
       </c>
-      <c r="E458" s="2" t="s">
+      <c r="E458" t="s">
         <v>1450</v>
       </c>
-      <c r="G458" s="2" t="s">
+      <c r="G458" t="s">
         <v>1451</v>
       </c>
-      <c r="H458" s="2" t="s">
+      <c r="H458" t="s">
         <v>1452</v>
       </c>
     </row>
@@ -13504,14 +13481,14 @@
       <c r="C459" t="s">
         <v>1453</v>
       </c>
-      <c r="D459" s="2" t="s">
+      <c r="D459" t="s">
         <v>1454</v>
       </c>
-      <c r="G459" s="2" t="s">
+      <c r="G459" t="s">
         <v>1455</v>
       </c>
     </row>
-    <row r="460" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>87</v>
       </c>
@@ -13521,10 +13498,10 @@
       <c r="C460" t="s">
         <v>1456</v>
       </c>
-      <c r="E460" s="2" t="s">
+      <c r="E460" t="s">
         <v>1457</v>
       </c>
-      <c r="H460" s="2" t="s">
+      <c r="H460" t="s">
         <v>1458</v>
       </c>
     </row>
@@ -13538,30 +13515,30 @@
       <c r="C461" t="s">
         <v>1459</v>
       </c>
-      <c r="E461" s="2" t="s">
+      <c r="E461" t="s">
         <v>1460</v>
       </c>
-      <c r="H461" s="2" t="s">
+      <c r="H461" t="s">
         <v>1461</v>
       </c>
     </row>
-    <row r="462" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B462">
         <v>4</v>
       </c>
       <c r="C462" t="s">
         <v>1462</v>
       </c>
-      <c r="D462" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E462" s="2" t="s">
+      <c r="D462" t="s">
+        <v>152</v>
+      </c>
+      <c r="E462" t="s">
         <v>1463</v>
       </c>
-      <c r="G462" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H462" s="2" t="s">
+      <c r="G462" t="s">
+        <v>152</v>
+      </c>
+      <c r="H462" t="s">
         <v>1464</v>
       </c>
     </row>
@@ -13572,10 +13549,10 @@
       <c r="C463" t="s">
         <v>1465</v>
       </c>
-      <c r="D463" s="2" t="s">
+      <c r="D463" t="s">
         <v>1466</v>
       </c>
-      <c r="G463" s="2" t="s">
+      <c r="G463" t="s">
         <v>1467</v>
       </c>
     </row>
@@ -13586,10 +13563,10 @@
       <c r="C464" t="s">
         <v>1468</v>
       </c>
-      <c r="E464" s="2" t="s">
+      <c r="E464" t="s">
         <v>1469</v>
       </c>
-      <c r="H464" s="2" t="s">
+      <c r="H464" t="s">
         <v>1470</v>
       </c>
       <c r="J464" t="s">
@@ -13606,10 +13583,10 @@
       <c r="C465" t="s">
         <v>1471</v>
       </c>
-      <c r="E465" s="2" t="s">
+      <c r="E465" t="s">
         <v>1472</v>
       </c>
-      <c r="H465" s="2" t="s">
+      <c r="H465" t="s">
         <v>1473</v>
       </c>
     </row>
@@ -13623,10 +13600,10 @@
       <c r="C466" t="s">
         <v>1474</v>
       </c>
-      <c r="E466" s="2" t="s">
+      <c r="E466" t="s">
         <v>1475</v>
       </c>
-      <c r="H466" s="2" t="s">
+      <c r="H466" t="s">
         <v>1476</v>
       </c>
     </row>
@@ -13640,14 +13617,14 @@
       <c r="C467" t="s">
         <v>1477</v>
       </c>
-      <c r="E467" s="2" t="s">
+      <c r="E467" t="s">
         <v>1478</v>
       </c>
-      <c r="H467" s="2" t="s">
+      <c r="H467" t="s">
         <v>1479</v>
       </c>
     </row>
-    <row r="468" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>87</v>
       </c>
@@ -13657,10 +13634,10 @@
       <c r="C468" t="s">
         <v>1480</v>
       </c>
-      <c r="E468" s="2" t="s">
+      <c r="E468" t="s">
         <v>1481</v>
       </c>
-      <c r="H468" s="2" t="s">
+      <c r="H468" t="s">
         <v>1482</v>
       </c>
     </row>
@@ -13674,10 +13651,10 @@
       <c r="C469" t="s">
         <v>1483</v>
       </c>
-      <c r="E469" s="2" t="s">
+      <c r="E469" t="s">
         <v>1484</v>
       </c>
-      <c r="H469" s="2" t="s">
+      <c r="H469" t="s">
         <v>1485</v>
       </c>
     </row>
@@ -13691,10 +13668,10 @@
       <c r="C470" t="s">
         <v>1486</v>
       </c>
-      <c r="E470" s="2" t="s">
+      <c r="E470" t="s">
         <v>1487</v>
       </c>
-      <c r="H470" s="2" t="s">
+      <c r="H470" t="s">
         <v>1488</v>
       </c>
     </row>
@@ -13708,10 +13685,10 @@
       <c r="C471" t="s">
         <v>1489</v>
       </c>
-      <c r="E471" s="2" t="s">
+      <c r="E471" t="s">
         <v>1490</v>
       </c>
-      <c r="H471" s="2" t="s">
+      <c r="H471" t="s">
         <v>1491</v>
       </c>
     </row>
@@ -13725,10 +13702,10 @@
       <c r="C472" t="s">
         <v>1492</v>
       </c>
-      <c r="E472" s="2" t="s">
+      <c r="E472" t="s">
         <v>1493</v>
       </c>
-      <c r="H472" s="2" t="s">
+      <c r="H472" t="s">
         <v>1494</v>
       </c>
     </row>
@@ -13742,10 +13719,10 @@
       <c r="C473" t="s">
         <v>1495</v>
       </c>
-      <c r="E473" s="2" t="s">
+      <c r="E473" t="s">
         <v>1496</v>
       </c>
-      <c r="H473" s="2" t="s">
+      <c r="H473" t="s">
         <v>1497</v>
       </c>
     </row>
@@ -13759,30 +13736,30 @@
       <c r="C474" t="s">
         <v>1498</v>
       </c>
-      <c r="E474" s="2" t="s">
+      <c r="E474" t="s">
         <v>1499</v>
       </c>
-      <c r="H474" s="2" t="s">
+      <c r="H474" t="s">
         <v>1500</v>
       </c>
     </row>
-    <row r="475" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B475">
         <v>4</v>
       </c>
       <c r="C475" t="s">
         <v>1501</v>
       </c>
-      <c r="D475" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E475" s="2" t="s">
+      <c r="D475" t="s">
+        <v>152</v>
+      </c>
+      <c r="E475" t="s">
         <v>1502</v>
       </c>
-      <c r="G475" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H475" s="2" t="s">
+      <c r="G475" t="s">
+        <v>152</v>
+      </c>
+      <c r="H475" t="s">
         <v>1503</v>
       </c>
     </row>
@@ -13793,14 +13770,14 @@
       <c r="C476" t="s">
         <v>1504</v>
       </c>
-      <c r="D476" s="2" t="s">
+      <c r="D476" t="s">
         <v>1505</v>
       </c>
-      <c r="G476" s="2" t="s">
+      <c r="G476" t="s">
         <v>1506</v>
       </c>
     </row>
-    <row r="477" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>87</v>
       </c>
@@ -13810,10 +13787,10 @@
       <c r="C477" t="s">
         <v>1507</v>
       </c>
-      <c r="E477" s="2" t="s">
+      <c r="E477" t="s">
         <v>1508</v>
       </c>
-      <c r="H477" s="2" t="s">
+      <c r="H477" t="s">
         <v>1509</v>
       </c>
     </row>
@@ -13827,14 +13804,14 @@
       <c r="C478" t="s">
         <v>1510</v>
       </c>
-      <c r="E478" s="2" t="s">
+      <c r="E478" t="s">
         <v>1511</v>
       </c>
-      <c r="H478" s="2" t="s">
+      <c r="H478" t="s">
         <v>1512</v>
       </c>
     </row>
-    <row r="479" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>87</v>
       </c>
@@ -13844,10 +13821,10 @@
       <c r="C479" t="s">
         <v>1513</v>
       </c>
-      <c r="E479" s="2" t="s">
+      <c r="E479" t="s">
         <v>1514</v>
       </c>
-      <c r="H479" s="2" t="s">
+      <c r="H479" t="s">
         <v>1515</v>
       </c>
     </row>
@@ -13861,50 +13838,50 @@
       <c r="C480" t="s">
         <v>1516</v>
       </c>
-      <c r="E480" s="2" t="s">
+      <c r="E480" t="s">
         <v>1517</v>
       </c>
-      <c r="H480" s="2" t="s">
+      <c r="H480" t="s">
         <v>1518</v>
       </c>
     </row>
-    <row r="481" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B481">
         <v>4</v>
       </c>
       <c r="C481" t="s">
         <v>1519</v>
       </c>
-      <c r="D481" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E481" s="2" t="s">
+      <c r="D481" t="s">
+        <v>152</v>
+      </c>
+      <c r="E481" t="s">
         <v>1520</v>
       </c>
-      <c r="G481" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H481" s="2" t="s">
+      <c r="G481" t="s">
+        <v>152</v>
+      </c>
+      <c r="H481" t="s">
         <v>1521</v>
       </c>
     </row>
-    <row r="482" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B482">
         <v>2</v>
       </c>
       <c r="C482" t="s">
         <v>1522</v>
       </c>
-      <c r="D482" s="2" t="s">
+      <c r="D482" t="s">
         <v>1523</v>
       </c>
-      <c r="E482" s="2" t="s">
+      <c r="E482" t="s">
         <v>1524</v>
       </c>
-      <c r="G482" s="2" t="s">
+      <c r="G482" t="s">
         <v>1525</v>
       </c>
-      <c r="H482" s="2" t="s">
+      <c r="H482" t="s">
         <v>1526</v>
       </c>
     </row>
@@ -13915,14 +13892,14 @@
       <c r="C483" t="s">
         <v>1527</v>
       </c>
-      <c r="D483" s="2" t="s">
+      <c r="D483" t="s">
         <v>1528</v>
       </c>
-      <c r="G483" s="2" t="s">
+      <c r="G483" t="s">
         <v>1529</v>
       </c>
     </row>
-    <row r="484" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>87</v>
       </c>
@@ -13932,30 +13909,30 @@
       <c r="C484" t="s">
         <v>1530</v>
       </c>
-      <c r="E484" s="2" t="s">
+      <c r="E484" t="s">
         <v>1531</v>
       </c>
-      <c r="H484" s="2" t="s">
+      <c r="H484" t="s">
         <v>1532</v>
       </c>
     </row>
-    <row r="485" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B485">
         <v>4</v>
       </c>
       <c r="C485" t="s">
         <v>1533</v>
       </c>
-      <c r="D485" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E485" s="2" t="s">
+      <c r="D485" t="s">
+        <v>152</v>
+      </c>
+      <c r="E485" t="s">
         <v>1534</v>
       </c>
-      <c r="G485" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H485" s="2" t="s">
+      <c r="G485" t="s">
+        <v>152</v>
+      </c>
+      <c r="H485" t="s">
         <v>1535</v>
       </c>
     </row>
@@ -13966,10 +13943,10 @@
       <c r="C486" t="s">
         <v>1536</v>
       </c>
-      <c r="D486" s="2" t="s">
+      <c r="D486" t="s">
         <v>1537</v>
       </c>
-      <c r="G486" s="2" t="s">
+      <c r="G486" t="s">
         <v>1538</v>
       </c>
     </row>
@@ -13983,14 +13960,14 @@
       <c r="C487" t="s">
         <v>1539</v>
       </c>
-      <c r="E487" s="2" t="s">
+      <c r="E487" t="s">
         <v>1540</v>
       </c>
-      <c r="H487" s="2" t="s">
+      <c r="H487" t="s">
         <v>1541</v>
       </c>
     </row>
-    <row r="488" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>87</v>
       </c>
@@ -14000,30 +13977,30 @@
       <c r="C488" t="s">
         <v>1542</v>
       </c>
-      <c r="E488" s="2" t="s">
+      <c r="E488" t="s">
         <v>1543</v>
       </c>
-      <c r="H488" s="2" t="s">
+      <c r="H488" t="s">
         <v>1544</v>
       </c>
     </row>
-    <row r="489" spans="1:8" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B489">
         <v>4</v>
       </c>
       <c r="C489" t="s">
         <v>1545</v>
       </c>
-      <c r="D489" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E489" s="2" t="s">
+      <c r="D489" t="s">
+        <v>152</v>
+      </c>
+      <c r="E489" t="s">
         <v>1546</v>
       </c>
-      <c r="G489" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H489" s="2" t="s">
+      <c r="G489" t="s">
+        <v>152</v>
+      </c>
+      <c r="H489" t="s">
         <v>1547</v>
       </c>
     </row>
@@ -14034,14 +14011,14 @@
       <c r="C490" t="s">
         <v>1548</v>
       </c>
-      <c r="D490" s="2" t="s">
+      <c r="D490" t="s">
         <v>1549</v>
       </c>
-      <c r="G490" s="2" t="s">
+      <c r="G490" t="s">
         <v>1550</v>
       </c>
     </row>
-    <row r="491" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>87</v>
       </c>
@@ -14051,14 +14028,14 @@
       <c r="C491" t="s">
         <v>1551</v>
       </c>
-      <c r="E491" s="2" t="s">
+      <c r="E491" t="s">
         <v>1552</v>
       </c>
-      <c r="H491" s="2" t="s">
+      <c r="H491" t="s">
         <v>1553</v>
       </c>
     </row>
-    <row r="492" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>87</v>
       </c>
@@ -14068,14 +14045,14 @@
       <c r="C492" t="s">
         <v>1554</v>
       </c>
-      <c r="E492" s="2" t="s">
+      <c r="E492" t="s">
         <v>1555</v>
       </c>
-      <c r="H492" s="2" t="s">
+      <c r="H492" t="s">
         <v>1556</v>
       </c>
     </row>
-    <row r="493" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>87</v>
       </c>
@@ -14085,68 +14062,68 @@
       <c r="C493" t="s">
         <v>1557</v>
       </c>
-      <c r="E493" s="2" t="s">
+      <c r="E493" t="s">
         <v>1558</v>
       </c>
-      <c r="H493" s="2" t="s">
+      <c r="H493" t="s">
         <v>1559</v>
       </c>
     </row>
-    <row r="494" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B494">
         <v>4</v>
       </c>
       <c r="C494" t="s">
         <v>1560</v>
       </c>
-      <c r="D494" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E494" s="2" t="s">
+      <c r="D494" t="s">
+        <v>152</v>
+      </c>
+      <c r="E494" t="s">
         <v>1561</v>
       </c>
-      <c r="G494" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H494" s="2" t="s">
+      <c r="G494" t="s">
+        <v>152</v>
+      </c>
+      <c r="H494" t="s">
         <v>1562</v>
       </c>
     </row>
-    <row r="495" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B495">
         <v>2</v>
       </c>
       <c r="C495" t="s">
         <v>1563</v>
       </c>
-      <c r="D495" s="2" t="s">
+      <c r="D495" t="s">
         <v>1564</v>
       </c>
-      <c r="E495" s="2" t="s">
+      <c r="E495" t="s">
         <v>1565</v>
       </c>
-      <c r="G495" s="2" t="s">
+      <c r="G495" t="s">
         <v>1566</v>
       </c>
-      <c r="H495" s="2" t="s">
+      <c r="H495" t="s">
         <v>1567</v>
       </c>
     </row>
-    <row r="496" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B496">
         <v>3</v>
       </c>
       <c r="C496" t="s">
         <v>1568</v>
       </c>
-      <c r="D496" s="2" t="s">
+      <c r="D496" t="s">
         <v>1569</v>
       </c>
-      <c r="G496" s="2" t="s">
+      <c r="G496" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="497" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>87</v>
       </c>
@@ -14156,14 +14133,14 @@
       <c r="C497" t="s">
         <v>1571</v>
       </c>
-      <c r="E497" s="2" t="s">
+      <c r="E497" t="s">
         <v>1572</v>
       </c>
-      <c r="H497" s="2" t="s">
+      <c r="H497" t="s">
         <v>1573</v>
       </c>
     </row>
-    <row r="498" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>87</v>
       </c>
@@ -14173,10 +14150,10 @@
       <c r="C498" t="s">
         <v>1574</v>
       </c>
-      <c r="E498" s="2" t="s">
+      <c r="E498" t="s">
         <v>1575</v>
       </c>
-      <c r="H498" s="2" t="s">
+      <c r="H498" t="s">
         <v>1576</v>
       </c>
     </row>
@@ -14190,30 +14167,30 @@
       <c r="C499" t="s">
         <v>1577</v>
       </c>
-      <c r="E499" s="2" t="s">
+      <c r="E499" t="s">
         <v>1578</v>
       </c>
-      <c r="H499" s="2" t="s">
+      <c r="H499" t="s">
         <v>1579</v>
       </c>
     </row>
-    <row r="500" spans="1:8" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B500">
         <v>4</v>
       </c>
       <c r="C500" t="s">
         <v>1580</v>
       </c>
-      <c r="D500" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E500" s="2" t="s">
+      <c r="D500" t="s">
+        <v>152</v>
+      </c>
+      <c r="E500" t="s">
         <v>1581</v>
       </c>
-      <c r="G500" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H500" s="2" t="s">
+      <c r="G500" t="s">
+        <v>152</v>
+      </c>
+      <c r="H500" t="s">
         <v>1582</v>
       </c>
     </row>
@@ -14224,14 +14201,14 @@
       <c r="C501" t="s">
         <v>1583</v>
       </c>
-      <c r="D501" s="2" t="s">
+      <c r="D501" t="s">
         <v>1584</v>
       </c>
-      <c r="G501" s="2" t="s">
+      <c r="G501" t="s">
         <v>1585</v>
       </c>
     </row>
-    <row r="502" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>87</v>
       </c>
@@ -14241,30 +14218,30 @@
       <c r="C502" t="s">
         <v>1586</v>
       </c>
-      <c r="E502" s="2" t="s">
+      <c r="E502" t="s">
         <v>1587</v>
       </c>
-      <c r="H502" s="2" t="s">
+      <c r="H502" t="s">
         <v>1588</v>
       </c>
     </row>
-    <row r="503" spans="1:8" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B503">
         <v>4</v>
       </c>
       <c r="C503" t="s">
         <v>1589</v>
       </c>
-      <c r="D503" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E503" s="2" t="s">
+      <c r="D503" t="s">
+        <v>152</v>
+      </c>
+      <c r="E503" t="s">
         <v>1590</v>
       </c>
-      <c r="G503" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H503" s="2" t="s">
+      <c r="G503" t="s">
+        <v>152</v>
+      </c>
+      <c r="H503" t="s">
         <v>1591</v>
       </c>
     </row>
@@ -14275,14 +14252,14 @@
       <c r="C504" t="s">
         <v>1592</v>
       </c>
-      <c r="D504" s="2" t="s">
+      <c r="D504" t="s">
         <v>1593</v>
       </c>
-      <c r="G504" s="2" t="s">
+      <c r="G504" t="s">
         <v>1594</v>
       </c>
     </row>
-    <row r="505" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>87</v>
       </c>
@@ -14292,14 +14269,14 @@
       <c r="C505" t="s">
         <v>1595</v>
       </c>
-      <c r="E505" s="2" t="s">
+      <c r="E505" t="s">
         <v>1596</v>
       </c>
-      <c r="H505" s="2" t="s">
+      <c r="H505" t="s">
         <v>1597</v>
       </c>
     </row>
-    <row r="506" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>87</v>
       </c>
@@ -14309,30 +14286,30 @@
       <c r="C506" t="s">
         <v>1598</v>
       </c>
-      <c r="E506" s="2" t="s">
+      <c r="E506" t="s">
         <v>1599</v>
       </c>
-      <c r="H506" s="2" t="s">
+      <c r="H506" t="s">
         <v>1600</v>
       </c>
     </row>
-    <row r="507" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B507">
         <v>4</v>
       </c>
       <c r="C507" t="s">
         <v>1601</v>
       </c>
-      <c r="D507" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E507" s="2" t="s">
+      <c r="D507" t="s">
+        <v>152</v>
+      </c>
+      <c r="E507" t="s">
         <v>1602</v>
       </c>
-      <c r="G507" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H507" s="2" t="s">
+      <c r="G507" t="s">
+        <v>152</v>
+      </c>
+      <c r="H507" t="s">
         <v>1603</v>
       </c>
     </row>
